--- a/output/summary_WB_regions_quality_prevalences.xlsx
+++ b/output/summary_WB_regions_quality_prevalences.xlsx
@@ -408,10 +408,10 @@
         </is>
       </c>
       <c r="F2">
-        <v>0.05599416962773597</v>
+        <v>0.06051850666996739</v>
       </c>
       <c r="G2">
-        <v>5.599416962773597</v>
+        <v>6.051850666996739</v>
       </c>
     </row>
     <row r="3">
@@ -436,10 +436,10 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.04650124659940484</v>
+        <v>0.06028275821892356</v>
       </c>
       <c r="G3">
-        <v>4.650124659940484</v>
+        <v>6.028275821892356</v>
       </c>
     </row>
     <row r="4">
@@ -464,10 +464,10 @@
         </is>
       </c>
       <c r="F4">
-        <v>0.04202782423648842</v>
+        <v>0.04123773212648262</v>
       </c>
       <c r="G4">
-        <v>4.202782423648841</v>
+        <v>4.123773212648262</v>
       </c>
     </row>
     <row r="5">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="F5">
-        <v>0.09052823610196913</v>
+        <v>0.08832542851914257</v>
       </c>
       <c r="G5">
-        <v>9.052823610196912</v>
+        <v>8.832542851914257</v>
       </c>
     </row>
     <row r="6">
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="F6">
-        <v>0.07080197672774517</v>
+        <v>0.1241122668266946</v>
       </c>
       <c r="G6">
-        <v>7.080197672774517</v>
+        <v>12.41122668266946</v>
       </c>
     </row>
     <row r="7">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="F7">
-        <v>0.06436164960239742</v>
+        <v>0.02546289237934947</v>
       </c>
       <c r="G7">
-        <v>6.436164960239742</v>
+        <v>2.546289237934947</v>
       </c>
     </row>
     <row r="8">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="F8">
-        <v>0.02862745026864694</v>
+        <v>0.01601671489421109</v>
       </c>
       <c r="G8">
-        <v>2.862745026864694</v>
+        <v>1.601671489421109</v>
       </c>
     </row>
     <row r="9">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="F9">
-        <v>0.1056124298198555</v>
+        <v>0.1219041463914955</v>
       </c>
       <c r="G9">
-        <v>10.56124298198555</v>
+        <v>12.19041463914955</v>
       </c>
     </row>
     <row r="10">
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="F10">
-        <v>0.04882233451860352</v>
+        <v>0.05922490679086505</v>
       </c>
       <c r="G10">
-        <v>4.882233451860351</v>
+        <v>5.922490679086505</v>
       </c>
     </row>
     <row r="11">
@@ -670,10 +670,10 @@
         </is>
       </c>
       <c r="F11">
-        <v>0.04423306187171902</v>
+        <v>0.06131649866168604</v>
       </c>
       <c r="G11">
-        <v>4.423306187171902</v>
+        <v>6.131649866168604</v>
       </c>
     </row>
     <row r="12">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="F12">
-        <v>0.04294492097106639</v>
+        <v>0.0391807022044984</v>
       </c>
       <c r="G12">
-        <v>4.294492097106639</v>
+        <v>3.91807022044984</v>
       </c>
     </row>
     <row r="13">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="F13">
-        <v>0.04105285065351753</v>
+        <v>0.04342457868006675</v>
       </c>
       <c r="G13">
-        <v>4.105285065351754</v>
+        <v>4.342457868006675</v>
       </c>
     </row>
     <row r="14">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F14">
-        <v>0.08604950982901938</v>
+        <v>0.08579026017790298</v>
       </c>
       <c r="G14">
-        <v>8.604950982901938</v>
+        <v>8.579026017790298</v>
       </c>
     </row>
     <row r="15">
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="F15">
-        <v>0.09513174898651458</v>
+        <v>0.09093123191326276</v>
       </c>
       <c r="G15">
-        <v>9.513174898651458</v>
+        <v>9.093123191326276</v>
       </c>
     </row>
     <row r="16">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F16">
-        <v>0.07040439255650731</v>
+        <v>0.1272036916514061</v>
       </c>
       <c r="G16">
-        <v>7.040439255650731</v>
+        <v>12.72036916514061</v>
       </c>
     </row>
     <row r="17">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="F17">
-        <v>0.07116959167120625</v>
+        <v>0.1212538684185983</v>
       </c>
       <c r="G17">
-        <v>7.116959167120624</v>
+        <v>12.12538684185983</v>
       </c>
     </row>
     <row r="18">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="F18">
-        <v>0.05963996869232801</v>
+        <v>0.02268391618866668</v>
       </c>
       <c r="G18">
-        <v>5.963996869232801</v>
+        <v>2.268391618866668</v>
       </c>
     </row>
     <row r="19">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="F19">
-        <v>0.0690467536237462</v>
+        <v>0.02822034100287558</v>
       </c>
       <c r="G19">
-        <v>6.904675362374619</v>
+        <v>2.822034100287558</v>
       </c>
     </row>
     <row r="20">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="F20">
-        <v>0.02789334810618154</v>
+        <v>0.01611569554650623</v>
       </c>
       <c r="G20">
-        <v>2.789334810618155</v>
+        <v>1.611569554650623</v>
       </c>
     </row>
     <row r="21">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="F21">
-        <v>0.0293260925295369</v>
+        <v>0.01592251538051997</v>
       </c>
       <c r="G21">
-        <v>2.93260925295369</v>
+        <v>1.592251538051997</v>
       </c>
     </row>
     <row r="22">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="F22">
-        <v>0.1029575832376918</v>
+        <v>0.120906113512387</v>
       </c>
       <c r="G22">
-        <v>10.29575832376918</v>
+        <v>12.0906113512387</v>
       </c>
     </row>
     <row r="23">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="F23">
-        <v>0.1082906960970416</v>
+        <v>0.1229109834048276</v>
       </c>
       <c r="G23">
-        <v>10.82906960970416</v>
+        <v>12.29109834048277</v>
       </c>
     </row>
     <row r="24">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="F24">
-        <v>0.0558065893586776</v>
+        <v>0.0597750730164151</v>
       </c>
       <c r="G24">
-        <v>5.58065893586776</v>
+        <v>5.97750730164151</v>
       </c>
     </row>
     <row r="25">
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="F25">
-        <v>0.05617928502754035</v>
+        <v>0.06125217134960723</v>
       </c>
       <c r="G25">
-        <v>5.617928502754035</v>
+        <v>6.125217134960724</v>
       </c>
     </row>
     <row r="26">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F26">
-        <v>0.2309559355042556</v>
+        <v>0.1999251239701637</v>
       </c>
       <c r="G26">
-        <v>23.09559355042556</v>
+        <v>19.99251239701637</v>
       </c>
     </row>
     <row r="27">
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="F27">
-        <v>0.2708866757823868</v>
+        <v>0.1964947496222818</v>
       </c>
       <c r="G27">
-        <v>27.08866757823868</v>
+        <v>19.64947496222818</v>
       </c>
     </row>
     <row r="28">
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="F28">
-        <v>0.3651631082670775</v>
+        <v>0.1934867094054999</v>
       </c>
       <c r="G28">
-        <v>36.51631082670775</v>
+        <v>19.34867094054999</v>
       </c>
     </row>
     <row r="29">
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="F29">
-        <v>0.4155475056194739</v>
+        <v>0.2570053292936721</v>
       </c>
       <c r="G29">
-        <v>41.55475056194739</v>
+        <v>25.70053292936721</v>
       </c>
     </row>
     <row r="30">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="F30">
-        <v>0.3159846104169904</v>
+        <v>0.26746047476051</v>
       </c>
       <c r="G30">
-        <v>31.59846104169904</v>
+        <v>26.746047476051</v>
       </c>
     </row>
     <row r="31">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="F31">
-        <v>0.3458449967924015</v>
+        <v>0.1616087077225428</v>
       </c>
       <c r="G31">
-        <v>34.58449967924015</v>
+        <v>16.16087077225428</v>
       </c>
     </row>
     <row r="32">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="F32">
-        <v>0.05621697912419471</v>
+        <v>0.1658428635592543</v>
       </c>
       <c r="G32">
-        <v>5.621697912419471</v>
+        <v>16.58428635592544</v>
       </c>
     </row>
     <row r="33">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="F33">
-        <v>0.1450390813907567</v>
+        <v>0.2218594781115444</v>
       </c>
       <c r="G33">
-        <v>14.50390813907567</v>
+        <v>22.18594781115445</v>
       </c>
     </row>
     <row r="34">
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="F34">
-        <v>0.332893448576264</v>
+        <v>0.198898404129918</v>
       </c>
       <c r="G34">
-        <v>33.2893448576264</v>
+        <v>19.88984041299181</v>
       </c>
     </row>
     <row r="35">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="F35">
-        <v>0.2102931868839952</v>
+        <v>0.1941458801978369</v>
       </c>
       <c r="G35">
-        <v>21.02931868839952</v>
+        <v>19.41458801978369</v>
       </c>
     </row>
     <row r="36">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="F36">
-        <v>0.3848307929039316</v>
+        <v>0.189718567749819</v>
       </c>
       <c r="G36">
-        <v>38.48307929039316</v>
+        <v>18.9718567749819</v>
       </c>
     </row>
     <row r="37">
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="F37">
-        <v>0.3442542202118178</v>
+        <v>0.1974926538524295</v>
       </c>
       <c r="G37">
-        <v>34.42542202118178</v>
+        <v>19.74926538524295</v>
       </c>
     </row>
     <row r="38">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="F38">
-        <v>0.4117042497674017</v>
+        <v>0.2571737393337754</v>
       </c>
       <c r="G38">
-        <v>41.17042497674017</v>
+        <v>25.71737393337753</v>
       </c>
     </row>
     <row r="39">
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="F39">
-        <v>0.4194978425580079</v>
+        <v>0.2568322270002414</v>
       </c>
       <c r="G39">
-        <v>41.94978425580079</v>
+        <v>25.68322270002414</v>
       </c>
     </row>
     <row r="40">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="F40">
-        <v>0.3142307803990058</v>
+        <v>0.2755657104196537</v>
       </c>
       <c r="G40">
-        <v>31.42307803990058</v>
+        <v>27.55657104196537</v>
       </c>
     </row>
     <row r="41">
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="F41">
-        <v>0.3176062396707263</v>
+        <v>0.2599661981667062</v>
       </c>
       <c r="G41">
-        <v>31.76062396707263</v>
+        <v>25.99661981667062</v>
       </c>
     </row>
     <row r="42">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="F42">
-        <v>0.3411625066854608</v>
+        <v>0.1552963499010353</v>
       </c>
       <c r="G42">
-        <v>34.11625066854608</v>
+        <v>15.52963499010353</v>
       </c>
     </row>
     <row r="43">
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="F43">
-        <v>0.3504912136053949</v>
+        <v>0.1678721663460741</v>
       </c>
       <c r="G43">
-        <v>35.04912136053949</v>
+        <v>16.78721663460741</v>
       </c>
     </row>
     <row r="44">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="F44">
-        <v>0.0556109395380866</v>
+        <v>0.1657288619274173</v>
       </c>
       <c r="G44">
-        <v>5.56109395380866</v>
+        <v>16.57288619274173</v>
       </c>
     </row>
     <row r="45">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="F45">
-        <v>0.05679374471388517</v>
+        <v>0.1659513584825554</v>
       </c>
       <c r="G45">
-        <v>5.679374471388518</v>
+        <v>16.59513584825554</v>
       </c>
     </row>
     <row r="46">
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="F46">
-        <v>0.1425107246288842</v>
+        <v>0.2224072183522259</v>
       </c>
       <c r="G46">
-        <v>14.25107246288842</v>
+        <v>22.24072183522259</v>
       </c>
     </row>
     <row r="47">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="F47">
-        <v>0.1475897420193265</v>
+        <v>0.221306905987366</v>
       </c>
       <c r="G47">
-        <v>14.75897420193265</v>
+        <v>22.1306905987366</v>
       </c>
     </row>
     <row r="48">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="F48">
-        <v>0.2523826886158002</v>
+        <v>0.2005329709355732</v>
       </c>
       <c r="G48">
-        <v>25.23826886158002</v>
+        <v>20.05329709355732</v>
       </c>
     </row>
     <row r="49">
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="F49">
-        <v>0.2098107372983576</v>
+        <v>0.1993252643229475</v>
       </c>
       <c r="G49">
-        <v>20.98107372983576</v>
+        <v>19.93252643229475</v>
       </c>
     </row>
     <row r="50">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="F50">
-        <v>0.08892911814377502</v>
+        <v>0.1017995920748739</v>
       </c>
       <c r="G50">
-        <v>8.892911814377502</v>
+        <v>10.17995920748739</v>
       </c>
     </row>
     <row r="51">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="F51">
-        <v>0.08542665271938658</v>
+        <v>0.105495198453494</v>
       </c>
       <c r="G51">
-        <v>8.542665271938658</v>
+        <v>10.5495198453494</v>
       </c>
     </row>
     <row r="52">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="F52">
-        <v>0.0809381823230113</v>
+        <v>0.0956087544497819</v>
       </c>
       <c r="G52">
-        <v>8.09381823230113</v>
+        <v>9.560875444978191</v>
       </c>
     </row>
     <row r="53">
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="F53">
-        <v>0.1796362923758349</v>
+        <v>0.1475718638628156</v>
       </c>
       <c r="G53">
-        <v>17.96362923758349</v>
+        <v>14.75718638628156</v>
       </c>
     </row>
     <row r="54">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="F54">
-        <v>0.1257143161835753</v>
+        <v>0.1734393575943255</v>
       </c>
       <c r="G54">
-        <v>12.57143161835753</v>
+        <v>17.34393575943255</v>
       </c>
     </row>
     <row r="55">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="F55">
-        <v>0.09515657598453804</v>
+        <v>0.07763696665709724</v>
       </c>
       <c r="G55">
-        <v>9.515657598453805</v>
+        <v>7.763696665709724</v>
       </c>
     </row>
     <row r="56">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="F56">
-        <v>0.03892226637195556</v>
+        <v>0.04417268298963928</v>
       </c>
       <c r="G56">
-        <v>3.892226637195556</v>
+        <v>4.417268298963927</v>
       </c>
     </row>
     <row r="57">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="F57">
-        <v>0.1177480805919128</v>
+        <v>0.148281907298118</v>
       </c>
       <c r="G57">
-        <v>11.77480805919128</v>
+        <v>14.8281907298118</v>
       </c>
     </row>
     <row r="58">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="F58">
-        <v>0.1002887883853535</v>
+        <v>0.1043943053920338</v>
       </c>
       <c r="G58">
-        <v>10.02887883853535</v>
+        <v>10.43943053920338</v>
       </c>
     </row>
     <row r="59">
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="F59">
-        <v>0.07090326096868632</v>
+        <v>0.1065709995070284</v>
       </c>
       <c r="G59">
-        <v>7.090326096868632</v>
+        <v>10.65709995070284</v>
       </c>
     </row>
     <row r="60">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="F60">
-        <v>0.08886320011901348</v>
+        <v>0.09241271609510485</v>
       </c>
       <c r="G60">
-        <v>8.886320011901349</v>
+        <v>9.241271609510484</v>
       </c>
     </row>
     <row r="61">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="F61">
-        <v>0.07251302638868989</v>
+        <v>0.09900649085913224</v>
       </c>
       <c r="G61">
-        <v>7.25130263886899</v>
+        <v>9.900649085913225</v>
       </c>
     </row>
     <row r="62">
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="F62">
-        <v>0.1740455728856309</v>
+        <v>0.1454253466398558</v>
       </c>
       <c r="G62">
-        <v>17.40455728856309</v>
+        <v>14.54253466398558</v>
       </c>
     </row>
     <row r="63">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="F63">
-        <v>0.1853827809171144</v>
+        <v>0.149778187511679</v>
       </c>
       <c r="G63">
-        <v>18.53827809171144</v>
+        <v>14.9778187511679</v>
       </c>
     </row>
     <row r="64">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F64">
-        <v>0.1262274503344724</v>
+        <v>0.1787057419133499</v>
       </c>
       <c r="G64">
-        <v>12.62274503344724</v>
+        <v>17.87057419133499</v>
       </c>
     </row>
     <row r="65">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="F65">
-        <v>0.1252398612240569</v>
+        <v>0.1685699444895362</v>
       </c>
       <c r="G65">
-        <v>12.52398612240569</v>
+        <v>16.85699444895362</v>
       </c>
     </row>
     <row r="66">
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F66">
-        <v>0.0895997658879838</v>
+        <v>0.07250025192022146</v>
       </c>
       <c r="G66">
-        <v>8.95997658879838</v>
+        <v>7.250025192022146</v>
       </c>
     </row>
     <row r="67">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F67">
-        <v>0.1006703397955821</v>
+        <v>0.08273388941164751</v>
       </c>
       <c r="G67">
-        <v>10.06703397955821</v>
+        <v>8.273388941164752</v>
       </c>
     </row>
     <row r="68">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F68">
-        <v>0.03820869163477689</v>
+        <v>0.0442609806126249</v>
       </c>
       <c r="G68">
-        <v>3.820869163477689</v>
+        <v>4.42609806126249</v>
       </c>
     </row>
     <row r="69">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F69">
-        <v>0.03960137275957629</v>
+        <v>0.04408865047467343</v>
       </c>
       <c r="G69">
-        <v>3.960137275957629</v>
+        <v>4.408865047467343</v>
       </c>
     </row>
     <row r="70">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F70">
-        <v>0.114860803244578</v>
+        <v>0.1477963270282419</v>
       </c>
       <c r="G70">
-        <v>11.4860803244578</v>
+        <v>14.77963270282419</v>
       </c>
     </row>
     <row r="71">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F71">
-        <v>0.1206608280192788</v>
+        <v>0.1487717711081072</v>
       </c>
       <c r="G71">
-        <v>12.06608280192788</v>
+        <v>14.87717711081072</v>
       </c>
     </row>
     <row r="72">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="F72">
-        <v>0.09344472380443353</v>
+        <v>0.1011200901361545</v>
       </c>
       <c r="G72">
-        <v>9.344472380443353</v>
+        <v>10.11200901361545</v>
       </c>
     </row>
     <row r="73">
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="F73">
-        <v>0.08447284909464678</v>
+        <v>0.1024701651244034</v>
       </c>
       <c r="G73">
-        <v>8.447284909464678</v>
+        <v>10.24701651244034</v>
       </c>
     </row>
     <row r="74">
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="F98">
-        <v>0.04044331882483764</v>
+        <v>0.03926930949901348</v>
       </c>
       <c r="G98">
-        <v>4.044331882483764</v>
+        <v>3.926930949901348</v>
       </c>
     </row>
     <row r="99">
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="F99">
-        <v>0.04433893171830399</v>
+        <v>0.03611514297722701</v>
       </c>
       <c r="G99">
-        <v>4.433893171830399</v>
+        <v>3.611514297722701</v>
       </c>
     </row>
     <row r="100">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="F100">
-        <v>0.0138236261611936</v>
+        <v>0.01057861447465946</v>
       </c>
       <c r="G100">
-        <v>1.38236261611936</v>
+        <v>1.057861447465946</v>
       </c>
     </row>
     <row r="101">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="F101">
-        <v>0.06563767117069616</v>
+        <v>0.0584450097125665</v>
       </c>
       <c r="G101">
-        <v>6.563767117069616</v>
+        <v>5.84450097125665</v>
       </c>
     </row>
     <row r="102">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="F102">
-        <v>0.0317907031136441</v>
+        <v>0.02839315402492439</v>
       </c>
       <c r="G102">
-        <v>3.179070311364411</v>
+        <v>2.839315402492439</v>
       </c>
     </row>
     <row r="103">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="F103">
-        <v>0.01157512972530356</v>
+        <v>0.009087560827504178</v>
       </c>
       <c r="G103">
-        <v>1.157512972530356</v>
+        <v>0.9087560827504177</v>
       </c>
     </row>
     <row r="104">
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="F104">
-        <v>0.01583359589879664</v>
+        <v>0.02203008762684973</v>
       </c>
       <c r="G104">
-        <v>1.583359589879664</v>
+        <v>2.203008762684973</v>
       </c>
     </row>
     <row r="105">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="F105">
-        <v>0.09568649352512404</v>
+        <v>0.1037912978546334</v>
       </c>
       <c r="G105">
-        <v>9.568649352512404</v>
+        <v>10.37912978546334</v>
       </c>
     </row>
     <row r="106">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="F106">
-        <v>0.0550200602901241</v>
+        <v>0.045104925556186</v>
       </c>
       <c r="G106">
-        <v>5.50200602901241</v>
+        <v>4.510492555618599</v>
       </c>
     </row>
     <row r="107">
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="F107">
-        <v>0.03390125182662015</v>
+        <v>0.02733025922415892</v>
       </c>
       <c r="G107">
-        <v>3.390125182662016</v>
+        <v>2.733025922415892</v>
       </c>
     </row>
     <row r="108">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F108">
-        <v>0.01945989042107113</v>
+        <v>0.01478282977174821</v>
       </c>
       <c r="G108">
-        <v>1.945989042107113</v>
+        <v>1.478282977174821</v>
       </c>
     </row>
     <row r="109">
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="F109">
-        <v>0.007831664187245258</v>
+        <v>0.006109076314467658</v>
       </c>
       <c r="G109">
-        <v>0.7831664187245257</v>
+        <v>0.6109076314467659</v>
       </c>
     </row>
     <row r="110">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="F110">
-        <v>0.07746823400907393</v>
+        <v>0.06870436441541562</v>
       </c>
       <c r="G110">
-        <v>7.746823400907394</v>
+        <v>6.870436441541562</v>
       </c>
     </row>
     <row r="111">
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="F111">
-        <v>0.05347748429193253</v>
+        <v>0.04789980808974391</v>
       </c>
       <c r="G111">
-        <v>5.347748429193254</v>
+        <v>4.78998080897439</v>
       </c>
     </row>
     <row r="112">
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="F112">
-        <v>0.04204251163719391</v>
+        <v>0.03788083631774094</v>
       </c>
       <c r="G112">
-        <v>4.20425116371939</v>
+        <v>3.788083631774094</v>
       </c>
     </row>
     <row r="113">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="F113">
-        <v>0.02231165871651695</v>
+        <v>0.01962063730527874</v>
       </c>
       <c r="G113">
-        <v>2.231165871651695</v>
+        <v>1.962063730527874</v>
       </c>
     </row>
     <row r="114">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="F114">
-        <v>0.01445069900019319</v>
+        <v>0.01128431927216694</v>
       </c>
       <c r="G114">
-        <v>1.445069900019319</v>
+        <v>1.128431927216694</v>
       </c>
     </row>
     <row r="115">
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="F115">
-        <v>0.008721836283825666</v>
+        <v>0.006907819752440698</v>
       </c>
       <c r="G115">
-        <v>0.8721836283825666</v>
+        <v>0.6907819752440698</v>
       </c>
     </row>
     <row r="116">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="F116">
-        <v>0.02289267353606879</v>
+        <v>0.03186607465503481</v>
       </c>
       <c r="G116">
-        <v>2.289267353606879</v>
+        <v>3.186607465503481</v>
       </c>
     </row>
     <row r="117">
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="F117">
-        <v>0.009115498319927359</v>
+        <v>0.01266921584794477</v>
       </c>
       <c r="G117">
-        <v>0.9115498319927359</v>
+        <v>1.266921584794477</v>
       </c>
     </row>
     <row r="118">
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="F118">
-        <v>0.1265239978647705</v>
+        <v>0.136509162056313</v>
       </c>
       <c r="G118">
-        <v>12.65239978647705</v>
+        <v>13.6509162056313</v>
       </c>
     </row>
     <row r="119">
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="F119">
-        <v>0.06457695653706144</v>
+        <v>0.07078481343416837</v>
       </c>
       <c r="G119">
-        <v>6.457695653706145</v>
+        <v>7.078481343416837</v>
       </c>
     </row>
     <row r="120">
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="F120">
-        <v>0.05233431093081469</v>
+        <v>0.051162825013622</v>
       </c>
       <c r="G120">
-        <v>5.233431093081469</v>
+        <v>5.1162825013622</v>
       </c>
     </row>
     <row r="121">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="F121">
-        <v>0.02870857844505538</v>
+        <v>0.02753207886905753</v>
       </c>
       <c r="G121">
-        <v>2.870857844505538</v>
+        <v>2.753207886905753</v>
       </c>
     </row>
     <row r="122">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="F122">
-        <v>0.02966685905008926</v>
+        <v>0.02842588831860442</v>
       </c>
       <c r="G122">
-        <v>2.966685905008926</v>
+        <v>2.842588831860442</v>
       </c>
     </row>
     <row r="123">
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="F123">
-        <v>0.02448472459563073</v>
+        <v>0.02271459331426909</v>
       </c>
       <c r="G123">
-        <v>2.448472459563073</v>
+        <v>2.271459331426909</v>
       </c>
     </row>
     <row r="124">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="F124">
-        <v>0.007119907301168128</v>
+        <v>0.005016742671822953</v>
       </c>
       <c r="G124">
-        <v>0.7119907301168128</v>
+        <v>0.5016742671822954</v>
       </c>
     </row>
     <row r="125">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="F125">
-        <v>0.04503893772217432</v>
+        <v>0.04362737824502045</v>
       </c>
       <c r="G125">
-        <v>4.503893772217432</v>
+        <v>4.362737824502045</v>
       </c>
     </row>
     <row r="126">
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="F126">
-        <v>0.0211848017114698</v>
+        <v>0.01985706865674334</v>
       </c>
       <c r="G126">
-        <v>2.11848017114698</v>
+        <v>1.985706865674334</v>
       </c>
     </row>
     <row r="127">
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="F127">
-        <v>0.00729284757105811</v>
+        <v>0.002539472188490489</v>
       </c>
       <c r="G127">
-        <v>0.729284757105811</v>
+        <v>0.2539472188490489</v>
       </c>
     </row>
     <row r="128">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="F128">
-        <v>0.01223608295934234</v>
+        <v>0.01218307941871122</v>
       </c>
       <c r="G128">
-        <v>1.223608295934234</v>
+        <v>1.218307941871122</v>
       </c>
     </row>
     <row r="129">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="F129">
-        <v>0.09214263228037435</v>
+        <v>0.09209676429057735</v>
       </c>
       <c r="G129">
-        <v>9.214263228037435</v>
+        <v>9.209676429057735</v>
       </c>
     </row>
     <row r="130">
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="F130">
-        <v>0.03088836521305803</v>
+        <v>0.02875340823970646</v>
       </c>
       <c r="G130">
-        <v>3.088836521305803</v>
+        <v>2.875340823970646</v>
       </c>
     </row>
     <row r="131">
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="F131">
-        <v>0.01822703839171855</v>
+        <v>0.01681341754496579</v>
       </c>
       <c r="G131">
-        <v>1.822703839171855</v>
+        <v>1.681341754496579</v>
       </c>
     </row>
     <row r="132">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="F132">
-        <v>0.009836686519257362</v>
+        <v>0.006850856205196139</v>
       </c>
       <c r="G132">
-        <v>0.9836686519257362</v>
+        <v>0.6850856205196139</v>
       </c>
     </row>
     <row r="133">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="F133">
-        <v>0.004231675483812296</v>
+        <v>0.003066880486313039</v>
       </c>
       <c r="G133">
-        <v>0.4231675483812296</v>
+        <v>0.3066880486313039</v>
       </c>
     </row>
     <row r="134">
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="F134">
-        <v>0.05354838523740608</v>
+        <v>0.05183850791757347</v>
       </c>
       <c r="G134">
-        <v>5.354838523740608</v>
+        <v>5.183850791757346</v>
       </c>
     </row>
     <row r="135">
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="F135">
-        <v>0.03629239933394342</v>
+        <v>0.03518746945385937</v>
       </c>
       <c r="G135">
-        <v>3.629239933394342</v>
+        <v>3.518746945385937</v>
       </c>
     </row>
     <row r="136">
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="F136">
-        <v>0.02843140612901324</v>
+        <v>0.02686224256885786</v>
       </c>
       <c r="G136">
-        <v>2.843140612901324</v>
+        <v>2.686224256885786</v>
       </c>
     </row>
     <row r="137">
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="F137">
-        <v>0.01448443417685186</v>
+        <v>0.01337993300111775</v>
       </c>
       <c r="G137">
-        <v>1.448443417685186</v>
+        <v>1.337993300111775</v>
       </c>
     </row>
     <row r="138">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="F138">
-        <v>0.009004458269545669</v>
+        <v>0.003018840375127131</v>
       </c>
       <c r="G138">
-        <v>0.9004458269545669</v>
+        <v>0.3018840375127131</v>
       </c>
     </row>
     <row r="139">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="F139">
-        <v>0.005594496005333651</v>
+        <v>0.00206381746685768</v>
       </c>
       <c r="G139">
-        <v>0.5594496005333651</v>
+        <v>0.2063817466857681</v>
       </c>
     </row>
     <row r="140">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="F140">
-        <v>0.01786455355444232</v>
+        <v>0.01779433134403176</v>
       </c>
       <c r="G140">
-        <v>1.786455355444232</v>
+        <v>1.779433134403176</v>
       </c>
     </row>
     <row r="141">
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="F141">
-        <v>0.006879488709970958</v>
+        <v>0.006842872112464779</v>
       </c>
       <c r="G141">
-        <v>0.6879488709970958</v>
+        <v>0.6842872112464778</v>
       </c>
     </row>
     <row r="142">
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="F142">
-        <v>0.1222734159400399</v>
+        <v>0.1222179463109025</v>
       </c>
       <c r="G142">
-        <v>12.22734159400399</v>
+        <v>12.22179463109025</v>
       </c>
     </row>
     <row r="143">
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="F143">
-        <v>0.06174605029969295</v>
+        <v>0.06170986864997433</v>
       </c>
       <c r="G143">
-        <v>6.174605029969295</v>
+        <v>6.170986864997433</v>
       </c>
     </row>
     <row r="144">
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="F144">
-        <v>0.03893906761235304</v>
+        <v>0.03736507421033941</v>
       </c>
       <c r="G144">
-        <v>3.893906761235304</v>
+        <v>3.736507421033941</v>
       </c>
     </row>
     <row r="145">
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="F145">
-        <v>0.02051649049752179</v>
+        <v>0.01960416640413155</v>
       </c>
       <c r="G145">
-        <v>2.051649049752179</v>
+        <v>1.960416640413155</v>
       </c>
     </row>
     <row r="146">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="F146">
-        <v>0.07303200422716384</v>
+        <v>0.06189668889138116</v>
       </c>
       <c r="G146">
-        <v>7.303200422716384</v>
+        <v>6.189668889138116</v>
       </c>
     </row>
     <row r="147">
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="F147">
-        <v>0.1012896990648706</v>
+        <v>0.05973551278715122</v>
       </c>
       <c r="G147">
-        <v>10.12896990648706</v>
+        <v>5.973551278715123</v>
       </c>
     </row>
     <row r="148">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="F148">
-        <v>0.05371203901996168</v>
+        <v>0.02243892081455268</v>
       </c>
       <c r="G148">
-        <v>5.371203901996168</v>
+        <v>2.243892081455268</v>
       </c>
     </row>
     <row r="149">
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="F149">
-        <v>0.1197003022779469</v>
+        <v>0.0836203756842395</v>
       </c>
       <c r="G149">
-        <v>11.97003022779469</v>
+        <v>8.362037568423949</v>
       </c>
     </row>
     <row r="150">
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="F150">
-        <v>0.0590806523463857</v>
+        <v>0.04312226976075047</v>
       </c>
       <c r="G150">
-        <v>5.90806523463857</v>
+        <v>4.312226976075046</v>
       </c>
     </row>
     <row r="151">
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="F151">
-        <v>0.06226882047646117</v>
+        <v>0.02228222515152268</v>
       </c>
       <c r="G151">
-        <v>6.226882047646117</v>
+        <v>2.228222515152268</v>
       </c>
     </row>
     <row r="152">
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="F152">
-        <v>0.02086803085644806</v>
+        <v>0.05107923608951422</v>
       </c>
       <c r="G152">
-        <v>2.086803085644806</v>
+        <v>5.107923608951421</v>
       </c>
     </row>
     <row r="153">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="F153">
-        <v>0.1001457533047702</v>
+        <v>0.1276607923958629</v>
       </c>
       <c r="G153">
-        <v>10.01457533047702</v>
+        <v>12.7660792395863</v>
       </c>
     </row>
     <row r="154">
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="F154">
-        <v>0.1203030396408181</v>
+        <v>0.0731236844673447</v>
       </c>
       <c r="G154">
-        <v>12.03030396408181</v>
+        <v>7.31236844673447</v>
       </c>
     </row>
     <row r="155">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="F155">
-        <v>0.08270971837566841</v>
+        <v>0.04665248982818723</v>
       </c>
       <c r="G155">
-        <v>8.270971837566842</v>
+        <v>4.665248982818722</v>
       </c>
     </row>
     <row r="156">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="F156">
-        <v>0.07666526854731141</v>
+        <v>0.03173822243251822</v>
       </c>
       <c r="G156">
-        <v>7.666526854731141</v>
+        <v>3.173822243251822</v>
       </c>
     </row>
     <row r="157">
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="F157">
-        <v>0.02931025937200425</v>
+        <v>0.01255275169438144</v>
       </c>
       <c r="G157">
-        <v>2.931025937200425</v>
+        <v>1.255275169438144</v>
       </c>
     </row>
     <row r="158">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="F158">
-        <v>0.1425969769321769</v>
+        <v>0.09859753993178492</v>
       </c>
       <c r="G158">
-        <v>14.25969769321769</v>
+        <v>9.859753993178492</v>
       </c>
     </row>
     <row r="159">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="F159">
-        <v>0.09616567873539773</v>
+        <v>0.06822591654884771</v>
       </c>
       <c r="G159">
-        <v>9.616567873539774</v>
+        <v>6.822591654884771</v>
       </c>
     </row>
     <row r="160">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="F160">
-        <v>0.07651851486890318</v>
+        <v>0.05707611635105599</v>
       </c>
       <c r="G160">
-        <v>7.651851486890318</v>
+        <v>5.707611635105599</v>
       </c>
     </row>
     <row r="161">
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="F161">
-        <v>0.0429572266442532</v>
+        <v>0.03022024071520499</v>
       </c>
       <c r="G161">
-        <v>4.29572266442532</v>
+        <v>3.022024071520499</v>
       </c>
     </row>
     <row r="162">
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="F162">
-        <v>0.07910409250828919</v>
+        <v>0.02816547485280046</v>
       </c>
       <c r="G162">
-        <v>7.910409250828919</v>
+        <v>2.816547485280046</v>
       </c>
     </row>
     <row r="163">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="F163">
-        <v>0.04556396426124972</v>
+        <v>0.01644455052694698</v>
       </c>
       <c r="G163">
-        <v>4.556396426124972</v>
+        <v>1.644455052694698</v>
       </c>
     </row>
     <row r="164">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="F164">
-        <v>0.02980470584857054</v>
+        <v>0.07222782993829287</v>
       </c>
       <c r="G164">
-        <v>2.980470584857054</v>
+        <v>7.222782993829287</v>
       </c>
     </row>
     <row r="165">
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="F165">
-        <v>0.0123630309523926</v>
+        <v>0.03095219904124725</v>
       </c>
       <c r="G165">
-        <v>1.23630309523926</v>
+        <v>3.095219904124725</v>
       </c>
     </row>
     <row r="166">
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="F166">
-        <v>0.1319672104157374</v>
+        <v>0.1658115017246514</v>
       </c>
       <c r="G166">
-        <v>13.19672104157374</v>
+        <v>16.58115017246514</v>
       </c>
     </row>
     <row r="167">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="F167">
-        <v>0.06804358361865337</v>
+        <v>0.08917353707478654</v>
       </c>
       <c r="G167">
-        <v>6.804358361865336</v>
+        <v>8.917353707478654</v>
       </c>
     </row>
     <row r="168">
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="F168">
-        <v>0.09235856442098045</v>
+        <v>0.08000033625236824</v>
       </c>
       <c r="G168">
-        <v>9.235856442098045</v>
+        <v>8.000033625236824</v>
       </c>
     </row>
     <row r="169">
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="F169">
-        <v>0.05395940168168958</v>
+        <v>0.04403092968349031</v>
       </c>
       <c r="G169">
-        <v>5.395940168168957</v>
+        <v>4.403092968349031</v>
       </c>
     </row>
     <row r="170">
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="F170">
-        <v>0.04044331882483764</v>
+        <v>0.03926930949901348</v>
       </c>
       <c r="G170">
-        <v>4.044331882483764</v>
+        <v>3.926930949901348</v>
       </c>
     </row>
     <row r="171">
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="F171">
-        <v>0.04433893171830399</v>
+        <v>0.03611514297722701</v>
       </c>
       <c r="G171">
-        <v>4.433893171830399</v>
+        <v>3.611514297722701</v>
       </c>
     </row>
     <row r="172">
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="F172">
-        <v>0.0138236261611936</v>
+        <v>0.01057861447465946</v>
       </c>
       <c r="G172">
-        <v>1.38236261611936</v>
+        <v>1.057861447465946</v>
       </c>
     </row>
     <row r="173">
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="F173">
-        <v>0.06563767117069616</v>
+        <v>0.0584450097125665</v>
       </c>
       <c r="G173">
-        <v>6.563767117069616</v>
+        <v>5.84450097125665</v>
       </c>
     </row>
     <row r="174">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="F174">
-        <v>0.0317907031136441</v>
+        <v>0.02839315402492439</v>
       </c>
       <c r="G174">
-        <v>3.179070311364411</v>
+        <v>2.839315402492439</v>
       </c>
     </row>
     <row r="175">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="F175">
-        <v>0.01157512972530356</v>
+        <v>0.009087560827504178</v>
       </c>
       <c r="G175">
-        <v>1.157512972530356</v>
+        <v>0.9087560827504177</v>
       </c>
     </row>
     <row r="176">
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="F176">
-        <v>0.01583359589879664</v>
+        <v>0.02203008762684973</v>
       </c>
       <c r="G176">
-        <v>1.583359589879664</v>
+        <v>2.203008762684973</v>
       </c>
     </row>
     <row r="177">
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="F177">
-        <v>0.09568649352512404</v>
+        <v>0.1037912978546334</v>
       </c>
       <c r="G177">
-        <v>9.568649352512404</v>
+        <v>10.37912978546334</v>
       </c>
     </row>
     <row r="178">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="F178">
-        <v>0.0550200602901241</v>
+        <v>0.045104925556186</v>
       </c>
       <c r="G178">
-        <v>5.50200602901241</v>
+        <v>4.510492555618599</v>
       </c>
     </row>
     <row r="179">
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="F179">
-        <v>0.03390125182662015</v>
+        <v>0.02733025922415892</v>
       </c>
       <c r="G179">
-        <v>3.390125182662016</v>
+        <v>2.733025922415892</v>
       </c>
     </row>
     <row r="180">
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="F180">
-        <v>0.01945989042107113</v>
+        <v>0.01478282977174821</v>
       </c>
       <c r="G180">
-        <v>1.945989042107113</v>
+        <v>1.478282977174821</v>
       </c>
     </row>
     <row r="181">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="F181">
-        <v>0.007831664187245258</v>
+        <v>0.006109076314467658</v>
       </c>
       <c r="G181">
-        <v>0.7831664187245257</v>
+        <v>0.6109076314467659</v>
       </c>
     </row>
     <row r="182">
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="F182">
-        <v>0.07746823400907393</v>
+        <v>0.06870436441541562</v>
       </c>
       <c r="G182">
-        <v>7.746823400907394</v>
+        <v>6.870436441541562</v>
       </c>
     </row>
     <row r="183">
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="F183">
-        <v>0.05347748429193253</v>
+        <v>0.04789980808974391</v>
       </c>
       <c r="G183">
-        <v>5.347748429193254</v>
+        <v>4.78998080897439</v>
       </c>
     </row>
     <row r="184">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="F184">
-        <v>0.04204251163719391</v>
+        <v>0.03788083631774094</v>
       </c>
       <c r="G184">
-        <v>4.20425116371939</v>
+        <v>3.788083631774094</v>
       </c>
     </row>
     <row r="185">
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="F185">
-        <v>0.02231165871651695</v>
+        <v>0.01962063730527874</v>
       </c>
       <c r="G185">
-        <v>2.231165871651695</v>
+        <v>1.962063730527874</v>
       </c>
     </row>
     <row r="186">
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="F186">
-        <v>0.01445069900019319</v>
+        <v>0.01128431927216694</v>
       </c>
       <c r="G186">
-        <v>1.445069900019319</v>
+        <v>1.128431927216694</v>
       </c>
     </row>
     <row r="187">
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="F187">
-        <v>0.008721836283825666</v>
+        <v>0.006907819752440698</v>
       </c>
       <c r="G187">
-        <v>0.8721836283825666</v>
+        <v>0.6907819752440698</v>
       </c>
     </row>
     <row r="188">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="F188">
-        <v>0.02289267353606879</v>
+        <v>0.03186607465503481</v>
       </c>
       <c r="G188">
-        <v>2.289267353606879</v>
+        <v>3.186607465503481</v>
       </c>
     </row>
     <row r="189">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="F189">
-        <v>0.009115498319927359</v>
+        <v>0.01266921584794477</v>
       </c>
       <c r="G189">
-        <v>0.9115498319927359</v>
+        <v>1.266921584794477</v>
       </c>
     </row>
     <row r="190">
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="F190">
-        <v>0.1265239978647705</v>
+        <v>0.136509162056313</v>
       </c>
       <c r="G190">
-        <v>12.65239978647705</v>
+        <v>13.6509162056313</v>
       </c>
     </row>
     <row r="191">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="F191">
-        <v>0.06457695653706144</v>
+        <v>0.07078481343416837</v>
       </c>
       <c r="G191">
-        <v>6.457695653706145</v>
+        <v>7.078481343416837</v>
       </c>
     </row>
     <row r="192">
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="F192">
-        <v>0.05233431093081469</v>
+        <v>0.051162825013622</v>
       </c>
       <c r="G192">
-        <v>5.233431093081469</v>
+        <v>5.1162825013622</v>
       </c>
     </row>
     <row r="193">
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="F193">
-        <v>0.02870857844505538</v>
+        <v>0.02753207886905753</v>
       </c>
       <c r="G193">
-        <v>2.870857844505538</v>
+        <v>2.753207886905753</v>
       </c>
     </row>
     <row r="194">
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="F218">
-        <v>0.04876168642466041</v>
+        <v>0.04993374344867897</v>
       </c>
       <c r="G218">
-        <v>4.876168642466041</v>
+        <v>4.993374344867897</v>
       </c>
     </row>
     <row r="219">
@@ -7069,10 +7069,10 @@
         </is>
       </c>
       <c r="F219">
-        <v>0.04433893171830399</v>
+        <v>0.03611514297722701</v>
       </c>
       <c r="G219">
-        <v>4.433893171830399</v>
+        <v>3.611514297722701</v>
       </c>
     </row>
     <row r="220">
@@ -7097,10 +7097,10 @@
         </is>
       </c>
       <c r="F220">
-        <v>0.0138236261611936</v>
+        <v>0.01057861447465946</v>
       </c>
       <c r="G220">
-        <v>1.38236261611936</v>
+        <v>1.057861447465946</v>
       </c>
     </row>
     <row r="221">
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="F221">
-        <v>0.06563767117069616</v>
+        <v>0.0584450097125665</v>
       </c>
       <c r="G221">
-        <v>6.563767117069616</v>
+        <v>5.84450097125665</v>
       </c>
     </row>
     <row r="222">
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="F222">
-        <v>0.04089883324201402</v>
+        <v>0.03617244774055502</v>
       </c>
       <c r="G222">
-        <v>4.089883324201401</v>
+        <v>3.617244774055502</v>
       </c>
     </row>
     <row r="223">
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="F223">
-        <v>0.01157512972530356</v>
+        <v>0.009087560827504178</v>
       </c>
       <c r="G223">
-        <v>1.157512972530356</v>
+        <v>0.9087560827504177</v>
       </c>
     </row>
     <row r="224">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="F224">
-        <v>0.04401996788242409</v>
+        <v>0.0596592725312483</v>
       </c>
       <c r="G224">
-        <v>4.40199678824241</v>
+        <v>5.96592725312483</v>
       </c>
     </row>
     <row r="225">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="F225">
-        <v>0.102483595510856</v>
+        <v>0.111633117879921</v>
       </c>
       <c r="G225">
-        <v>10.2483595510856</v>
+        <v>11.1633117879921</v>
       </c>
     </row>
     <row r="226">
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="F226">
-        <v>0.0550200602901241</v>
+        <v>0.045104925556186</v>
       </c>
       <c r="G226">
-        <v>5.50200602901241</v>
+        <v>4.510492555618599</v>
       </c>
     </row>
     <row r="227">
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="F227">
-        <v>0.03390125182662015</v>
+        <v>0.02733025922415892</v>
       </c>
       <c r="G227">
-        <v>3.390125182662016</v>
+        <v>2.733025922415892</v>
       </c>
     </row>
     <row r="228">
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="F228">
-        <v>0.01945989042107113</v>
+        <v>0.01478282977174821</v>
       </c>
       <c r="G228">
-        <v>1.945989042107113</v>
+        <v>1.478282977174821</v>
       </c>
     </row>
     <row r="229">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="F229">
-        <v>0.007831664187245258</v>
+        <v>0.006109076314467658</v>
       </c>
       <c r="G229">
-        <v>0.7831664187245257</v>
+        <v>0.6109076314467659</v>
       </c>
     </row>
     <row r="230">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="F230">
-        <v>0.07746823400907393</v>
+        <v>0.06870436441541562</v>
       </c>
       <c r="G230">
-        <v>7.746823400907394</v>
+        <v>6.870436441541562</v>
       </c>
     </row>
     <row r="231">
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="F231">
-        <v>0.05347748429193253</v>
+        <v>0.04789980808974391</v>
       </c>
       <c r="G231">
-        <v>5.347748429193254</v>
+        <v>4.78998080897439</v>
       </c>
     </row>
     <row r="232">
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="F232">
-        <v>0.05313059475334407</v>
+        <v>0.04750620104973372</v>
       </c>
       <c r="G232">
-        <v>5.313059475334407</v>
+        <v>4.750620104973372</v>
       </c>
     </row>
     <row r="233">
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="F233">
-        <v>0.02958908139143809</v>
+        <v>0.02569301374049508</v>
       </c>
       <c r="G233">
-        <v>2.958908139143809</v>
+        <v>2.569301374049508</v>
       </c>
     </row>
     <row r="234">
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="F234">
-        <v>0.01445069900019319</v>
+        <v>0.01128431927216694</v>
       </c>
       <c r="G234">
-        <v>1.445069900019319</v>
+        <v>1.128431927216694</v>
       </c>
     </row>
     <row r="235">
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="F235">
-        <v>0.008721836283825666</v>
+        <v>0.006907819752440698</v>
       </c>
       <c r="G235">
-        <v>0.8721836283825666</v>
+        <v>0.6907819752440698</v>
       </c>
     </row>
     <row r="236">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="F236">
-        <v>0.06245353905084892</v>
+        <v>0.08393355223684634</v>
       </c>
       <c r="G236">
-        <v>6.245353905084892</v>
+        <v>8.393355223684635</v>
       </c>
     </row>
     <row r="237">
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="F237">
-        <v>0.02647680768502972</v>
+        <v>0.03655753203502225</v>
       </c>
       <c r="G237">
-        <v>2.647680768502972</v>
+        <v>3.655753203502225</v>
       </c>
     </row>
     <row r="238">
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="F238">
-        <v>0.136176630786602</v>
+        <v>0.1476860360879277</v>
       </c>
       <c r="G238">
-        <v>13.6176630786602</v>
+        <v>14.76860360879277</v>
       </c>
     </row>
     <row r="239">
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="F239">
-        <v>0.06849333755722072</v>
+        <v>0.07526215931705166</v>
       </c>
       <c r="G239">
-        <v>6.849333755722071</v>
+        <v>7.526215931705166</v>
       </c>
     </row>
     <row r="240">
@@ -7727,10 +7727,10 @@
         </is>
       </c>
       <c r="F240">
-        <v>0.06374111673332256</v>
+        <v>0.06566505959574979</v>
       </c>
       <c r="G240">
-        <v>6.374111673332256</v>
+        <v>6.56650595957498</v>
       </c>
     </row>
     <row r="241">
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="F241">
-        <v>0.03397909098244856</v>
+        <v>0.03440914220658778</v>
       </c>
       <c r="G241">
-        <v>3.397909098244857</v>
+        <v>3.440914220658778</v>
       </c>
     </row>
     <row r="242">
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="F242">
-        <v>0.03647712752127422</v>
+        <v>0.03521240923158307</v>
       </c>
       <c r="G242">
-        <v>3.647712752127422</v>
+        <v>3.521240923158307</v>
       </c>
     </row>
     <row r="243">
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="F243">
-        <v>0.02448472459563073</v>
+        <v>0.02271459331426909</v>
       </c>
       <c r="G243">
-        <v>2.448472459563073</v>
+        <v>2.271459331426909</v>
       </c>
     </row>
     <row r="244">
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="F244">
-        <v>0.007119907301168128</v>
+        <v>0.005016742671822953</v>
       </c>
       <c r="G244">
-        <v>0.7119907301168128</v>
+        <v>0.5016742671822954</v>
       </c>
     </row>
     <row r="245">
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="F245">
-        <v>0.04503893772217432</v>
+        <v>0.04362737824502045</v>
       </c>
       <c r="G245">
-        <v>4.503893772217432</v>
+        <v>4.362737824502045</v>
       </c>
     </row>
     <row r="246">
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="F246">
-        <v>0.02685696914411996</v>
+        <v>0.02537283349490771</v>
       </c>
       <c r="G246">
-        <v>2.685696914411996</v>
+        <v>2.537283349490771</v>
       </c>
     </row>
     <row r="247">
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="F247">
-        <v>0.00729284757105811</v>
+        <v>0.002539472188490489</v>
       </c>
       <c r="G247">
-        <v>0.729284757105811</v>
+        <v>0.2539472188490489</v>
       </c>
     </row>
     <row r="248">
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="F248">
-        <v>0.03540671103498692</v>
+        <v>0.03529881287744488</v>
       </c>
       <c r="G248">
-        <v>3.540671103498692</v>
+        <v>3.529881287744488</v>
       </c>
     </row>
     <row r="249">
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="F249">
-        <v>0.09831303639722322</v>
+        <v>0.09826016448454415</v>
       </c>
       <c r="G249">
-        <v>9.831303639722321</v>
+        <v>9.826016448454416</v>
       </c>
     </row>
     <row r="250">
@@ -8007,10 +8007,10 @@
         </is>
       </c>
       <c r="F250">
-        <v>0.03088836521305803</v>
+        <v>0.02875340823970646</v>
       </c>
       <c r="G250">
-        <v>3.088836521305803</v>
+        <v>2.875340823970646</v>
       </c>
     </row>
     <row r="251">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="F251">
-        <v>0.01822703839171855</v>
+        <v>0.01681341754496579</v>
       </c>
       <c r="G251">
-        <v>1.822703839171855</v>
+        <v>1.681341754496579</v>
       </c>
     </row>
     <row r="252">
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="F252">
-        <v>0.009836686519257362</v>
+        <v>0.006850856205196139</v>
       </c>
       <c r="G252">
-        <v>0.9836686519257362</v>
+        <v>0.6850856205196139</v>
       </c>
     </row>
     <row r="253">
@@ -8106,10 +8106,10 @@
         </is>
       </c>
       <c r="F253">
-        <v>0.004231675483812296</v>
+        <v>0.003066880486313039</v>
       </c>
       <c r="G253">
-        <v>0.4231675483812296</v>
+        <v>0.3066880486313039</v>
       </c>
     </row>
     <row r="254">
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="F254">
-        <v>0.05354838523740608</v>
+        <v>0.05183850791757347</v>
       </c>
       <c r="G254">
-        <v>5.354838523740608</v>
+        <v>5.183850791757346</v>
       </c>
     </row>
     <row r="255">
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="F255">
-        <v>0.03629239933394342</v>
+        <v>0.03518746945385937</v>
       </c>
       <c r="G255">
-        <v>3.629239933394342</v>
+        <v>3.518746945385937</v>
       </c>
     </row>
     <row r="256">
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="F256">
-        <v>0.03565490373111992</v>
+        <v>0.03390280721166983</v>
       </c>
       <c r="G256">
-        <v>3.565490373111992</v>
+        <v>3.390280721166984</v>
       </c>
     </row>
     <row r="257">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="F257">
-        <v>0.01872220810545824</v>
+        <v>0.01748583488565943</v>
       </c>
       <c r="G257">
-        <v>1.872220810545824</v>
+        <v>1.748583488565943</v>
       </c>
     </row>
     <row r="258">
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="F258">
-        <v>0.009004458269545669</v>
+        <v>0.003018840375127131</v>
       </c>
       <c r="G258">
-        <v>0.9004458269545669</v>
+        <v>0.3018840375127131</v>
       </c>
     </row>
     <row r="259">
@@ -8304,10 +8304,10 @@
         </is>
       </c>
       <c r="F259">
-        <v>0.005594496005333651</v>
+        <v>0.00206381746685768</v>
       </c>
       <c r="G259">
-        <v>0.5594496005333651</v>
+        <v>0.2063817466857681</v>
       </c>
     </row>
     <row r="260">
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="F260">
-        <v>0.05070149110799613</v>
+        <v>0.05055813230454051</v>
       </c>
       <c r="G260">
-        <v>5.070149110799614</v>
+        <v>5.055813230454051</v>
       </c>
     </row>
     <row r="261">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="F261">
-        <v>0.02085072649172474</v>
+        <v>0.02077657609723308</v>
       </c>
       <c r="G261">
-        <v>2.085072649172474</v>
+        <v>2.077657609723309</v>
       </c>
     </row>
     <row r="262">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="F262">
-        <v>0.1309858666450688</v>
+        <v>0.1309195319135099</v>
       </c>
       <c r="G262">
-        <v>13.09858666450688</v>
+        <v>13.09195319135099</v>
       </c>
     </row>
     <row r="263">
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="F263">
-        <v>0.06535198319703735</v>
+        <v>0.06531269286532193</v>
       </c>
       <c r="G263">
-        <v>6.535198319703735</v>
+        <v>6.531269286532194</v>
       </c>
     </row>
     <row r="264">
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="F264">
-        <v>0.04839093749228565</v>
+        <v>0.0467873042596604</v>
       </c>
       <c r="G264">
-        <v>4.839093749228565</v>
+        <v>4.67873042596604</v>
       </c>
     </row>
     <row r="265">
@@ -8492,10 +8492,10 @@
         </is>
       </c>
       <c r="F265">
-        <v>0.02471986911105236</v>
+        <v>0.02378961230537494</v>
       </c>
       <c r="G265">
-        <v>2.471986911105235</v>
+        <v>2.378961230537494</v>
       </c>
     </row>
     <row r="266">
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="F266">
-        <v>0.08332574334267445</v>
+        <v>0.08145531957093886</v>
       </c>
       <c r="G266">
-        <v>8.332574334267445</v>
+        <v>8.145531957093887</v>
       </c>
     </row>
     <row r="267">
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="F267">
-        <v>0.1012896990648706</v>
+        <v>0.05973551278715122</v>
       </c>
       <c r="G267">
-        <v>10.12896990648706</v>
+        <v>5.973551278715123</v>
       </c>
     </row>
     <row r="268">
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="F268">
-        <v>0.05371203901996168</v>
+        <v>0.02243892081455268</v>
       </c>
       <c r="G268">
-        <v>5.371203901996168</v>
+        <v>2.243892081455268</v>
       </c>
     </row>
     <row r="269">
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="F269">
-        <v>0.1197003022779469</v>
+        <v>0.0836203756842395</v>
       </c>
       <c r="G269">
-        <v>11.97003022779469</v>
+        <v>8.362037568423949</v>
       </c>
     </row>
     <row r="270">
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="F270">
-        <v>0.07400666053239024</v>
+        <v>0.05409395204762179</v>
       </c>
       <c r="G270">
-        <v>7.400666053239025</v>
+        <v>5.409395204762179</v>
       </c>
     </row>
     <row r="271">
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="F271">
-        <v>0.06226882047646117</v>
+        <v>0.02228222515152268</v>
       </c>
       <c r="G271">
-        <v>6.226882047646117</v>
+        <v>2.228222515152268</v>
       </c>
     </row>
     <row r="272">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="F272">
-        <v>0.05525956797623844</v>
+        <v>0.1225409538322441</v>
       </c>
       <c r="G272">
-        <v>5.525956797623844</v>
+        <v>12.25409538322441</v>
       </c>
     </row>
     <row r="273">
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="F273">
-        <v>0.1078197711826775</v>
+        <v>0.1392811640997764</v>
       </c>
       <c r="G273">
-        <v>10.78197711826775</v>
+        <v>13.92811640997764</v>
       </c>
     </row>
     <row r="274">
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="F274">
-        <v>0.1203030396408181</v>
+        <v>0.0731236844673447</v>
       </c>
       <c r="G274">
-        <v>12.03030396408181</v>
+        <v>7.31236844673447</v>
       </c>
     </row>
     <row r="275">
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="F275">
-        <v>0.08270971837566841</v>
+        <v>0.04665248982818723</v>
       </c>
       <c r="G275">
-        <v>8.270971837566842</v>
+        <v>4.665248982818722</v>
       </c>
     </row>
     <row r="276">
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="F276">
-        <v>0.07666526854731141</v>
+        <v>0.03173822243251822</v>
       </c>
       <c r="G276">
-        <v>7.666526854731141</v>
+        <v>3.173822243251822</v>
       </c>
     </row>
     <row r="277">
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="F277">
-        <v>0.02931025937200425</v>
+        <v>0.01255275169438144</v>
       </c>
       <c r="G277">
-        <v>2.931025937200425</v>
+        <v>1.255275169438144</v>
       </c>
     </row>
     <row r="278">
@@ -8876,10 +8876,10 @@
         </is>
       </c>
       <c r="F278">
-        <v>0.1425969769321769</v>
+        <v>0.09859753993178492</v>
       </c>
       <c r="G278">
-        <v>14.25969769321769</v>
+        <v>9.859753993178492</v>
       </c>
     </row>
     <row r="279">
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="F279">
-        <v>0.09616567873539773</v>
+        <v>0.06822591654884771</v>
       </c>
       <c r="G279">
-        <v>9.616567873539774</v>
+        <v>6.822591654884771</v>
       </c>
     </row>
     <row r="280">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="F280">
-        <v>0.09359232661344168</v>
+        <v>0.07015041423476166</v>
       </c>
       <c r="G280">
-        <v>9.359232661344167</v>
+        <v>7.015041423476166</v>
       </c>
     </row>
     <row r="281">
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="F281">
-        <v>0.05589732910046546</v>
+        <v>0.03924779904124542</v>
       </c>
       <c r="G281">
-        <v>5.589732910046546</v>
+        <v>3.924779904124542</v>
       </c>
     </row>
     <row r="282">
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="F282">
-        <v>0.07910409250828919</v>
+        <v>0.02816547485280046</v>
       </c>
       <c r="G282">
-        <v>7.910409250828919</v>
+        <v>2.816547485280046</v>
       </c>
     </row>
     <row r="283">
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="F283">
-        <v>0.04556396426124972</v>
+        <v>0.01644455052694698</v>
       </c>
       <c r="G283">
-        <v>4.556396426124972</v>
+        <v>1.644455052694698</v>
       </c>
     </row>
     <row r="284">
@@ -9074,10 +9074,10 @@
         </is>
       </c>
       <c r="F284">
-        <v>0.07754951187410379</v>
+        <v>0.1669038555737332</v>
       </c>
       <c r="G284">
-        <v>7.754951187410379</v>
+        <v>16.69038555737332</v>
       </c>
     </row>
     <row r="285">
@@ -9107,10 +9107,10 @@
         </is>
       </c>
       <c r="F285">
-        <v>0.0340463123884661</v>
+        <v>0.08032094746661304</v>
       </c>
       <c r="G285">
-        <v>3.40463123884661</v>
+        <v>8.032094746661304</v>
       </c>
     </row>
     <row r="286">
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="F286">
-        <v>0.1428360247782401</v>
+        <v>0.1821727208459095</v>
       </c>
       <c r="G286">
-        <v>14.28360247782401</v>
+        <v>18.21727208459095</v>
       </c>
     </row>
     <row r="287">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="F287">
-        <v>0.07249462215581455</v>
+        <v>0.09601124003676006</v>
       </c>
       <c r="G287">
-        <v>7.249462215581455</v>
+        <v>9.601124003676006</v>
       </c>
     </row>
     <row r="288">
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="F288">
-        <v>0.1062304556132187</v>
+        <v>0.1055429023394026</v>
       </c>
       <c r="G288">
-        <v>10.62304556132187</v>
+        <v>10.55429023394026</v>
       </c>
     </row>
     <row r="289">
@@ -9229,10 +9229,10 @@
         </is>
       </c>
       <c r="F289">
-        <v>0.06072200686947126</v>
+        <v>0.0576842559250081</v>
       </c>
       <c r="G289">
-        <v>6.072200686947126</v>
+        <v>5.76842559250081</v>
       </c>
     </row>
     <row r="290">
@@ -9252,10 +9252,10 @@
         </is>
       </c>
       <c r="F290">
-        <v>0.04876168642466041</v>
+        <v>0.04993374344867897</v>
       </c>
       <c r="G290">
-        <v>4.876168642466041</v>
+        <v>4.993374344867897</v>
       </c>
     </row>
     <row r="291">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="F291">
-        <v>0.04433893171830399</v>
+        <v>0.03611514297722701</v>
       </c>
       <c r="G291">
-        <v>4.433893171830399</v>
+        <v>3.611514297722701</v>
       </c>
     </row>
     <row r="292">
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="F292">
-        <v>0.0138236261611936</v>
+        <v>0.01057861447465946</v>
       </c>
       <c r="G292">
-        <v>1.38236261611936</v>
+        <v>1.057861447465946</v>
       </c>
     </row>
     <row r="293">
@@ -9336,10 +9336,10 @@
         </is>
       </c>
       <c r="F293">
-        <v>0.06563767117069616</v>
+        <v>0.0584450097125665</v>
       </c>
       <c r="G293">
-        <v>6.563767117069616</v>
+        <v>5.84450097125665</v>
       </c>
     </row>
     <row r="294">
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="F294">
-        <v>0.04089883324201402</v>
+        <v>0.03617244774055502</v>
       </c>
       <c r="G294">
-        <v>4.089883324201401</v>
+        <v>3.617244774055502</v>
       </c>
     </row>
     <row r="295">
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="F295">
-        <v>0.01157512972530356</v>
+        <v>0.009087560827504178</v>
       </c>
       <c r="G295">
-        <v>1.157512972530356</v>
+        <v>0.9087560827504177</v>
       </c>
     </row>
     <row r="296">
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="F296">
-        <v>0.04401996788242409</v>
+        <v>0.0596592725312483</v>
       </c>
       <c r="G296">
-        <v>4.40199678824241</v>
+        <v>5.96592725312483</v>
       </c>
     </row>
     <row r="297">
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="F297">
-        <v>0.102483595510856</v>
+        <v>0.111633117879921</v>
       </c>
       <c r="G297">
-        <v>10.2483595510856</v>
+        <v>11.1633117879921</v>
       </c>
     </row>
     <row r="298">
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="F298">
-        <v>0.0550200602901241</v>
+        <v>0.045104925556186</v>
       </c>
       <c r="G298">
-        <v>5.50200602901241</v>
+        <v>4.510492555618599</v>
       </c>
     </row>
     <row r="299">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="F299">
-        <v>0.03390125182662015</v>
+        <v>0.02733025922415892</v>
       </c>
       <c r="G299">
-        <v>3.390125182662016</v>
+        <v>2.733025922415892</v>
       </c>
     </row>
     <row r="300">
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="F300">
-        <v>0.01945989042107113</v>
+        <v>0.01478282977174821</v>
       </c>
       <c r="G300">
-        <v>1.945989042107113</v>
+        <v>1.478282977174821</v>
       </c>
     </row>
     <row r="301">
@@ -9580,10 +9580,10 @@
         </is>
       </c>
       <c r="F301">
-        <v>0.007831664187245258</v>
+        <v>0.006109076314467658</v>
       </c>
       <c r="G301">
-        <v>0.7831664187245257</v>
+        <v>0.6109076314467659</v>
       </c>
     </row>
     <row r="302">
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="F302">
-        <v>0.07746823400907393</v>
+        <v>0.06870436441541562</v>
       </c>
       <c r="G302">
-        <v>7.746823400907394</v>
+        <v>6.870436441541562</v>
       </c>
     </row>
     <row r="303">
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="F303">
-        <v>0.05347748429193253</v>
+        <v>0.04789980808974391</v>
       </c>
       <c r="G303">
-        <v>5.347748429193254</v>
+        <v>4.78998080897439</v>
       </c>
     </row>
     <row r="304">
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="F304">
-        <v>0.05313059475334407</v>
+        <v>0.04750620104973372</v>
       </c>
       <c r="G304">
-        <v>5.313059475334407</v>
+        <v>4.750620104973372</v>
       </c>
     </row>
     <row r="305">
@@ -9712,10 +9712,10 @@
         </is>
       </c>
       <c r="F305">
-        <v>0.02958908139143809</v>
+        <v>0.02569301374049508</v>
       </c>
       <c r="G305">
-        <v>2.958908139143809</v>
+        <v>2.569301374049508</v>
       </c>
     </row>
     <row r="306">
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="F306">
-        <v>0.01445069900019319</v>
+        <v>0.01128431927216694</v>
       </c>
       <c r="G306">
-        <v>1.445069900019319</v>
+        <v>1.128431927216694</v>
       </c>
     </row>
     <row r="307">
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="F307">
-        <v>0.008721836283825666</v>
+        <v>0.006907819752440698</v>
       </c>
       <c r="G307">
-        <v>0.8721836283825666</v>
+        <v>0.6907819752440698</v>
       </c>
     </row>
     <row r="308">
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="F308">
-        <v>0.06245353905084892</v>
+        <v>0.08393355223684634</v>
       </c>
       <c r="G308">
-        <v>6.245353905084892</v>
+        <v>8.393355223684635</v>
       </c>
     </row>
     <row r="309">
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="F309">
-        <v>0.02647680768502972</v>
+        <v>0.03655753203502225</v>
       </c>
       <c r="G309">
-        <v>2.647680768502972</v>
+        <v>3.655753203502225</v>
       </c>
     </row>
     <row r="310">
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="F310">
-        <v>0.136176630786602</v>
+        <v>0.1476860360879277</v>
       </c>
       <c r="G310">
-        <v>13.6176630786602</v>
+        <v>14.76860360879277</v>
       </c>
     </row>
     <row r="311">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="F311">
-        <v>0.06849333755722072</v>
+        <v>0.07526215931705166</v>
       </c>
       <c r="G311">
-        <v>6.849333755722071</v>
+        <v>7.526215931705166</v>
       </c>
     </row>
     <row r="312">
@@ -9938,10 +9938,10 @@
         </is>
       </c>
       <c r="F312">
-        <v>0.06374111673332256</v>
+        <v>0.06566505959574979</v>
       </c>
       <c r="G312">
-        <v>6.374111673332256</v>
+        <v>6.56650595957498</v>
       </c>
     </row>
     <row r="313">
@@ -9966,10 +9966,10 @@
         </is>
       </c>
       <c r="F313">
-        <v>0.03397909098244856</v>
+        <v>0.03440914220658778</v>
       </c>
       <c r="G313">
-        <v>3.397909098244857</v>
+        <v>3.440914220658778</v>
       </c>
     </row>
     <row r="314">
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="F338">
-        <v>0.3475610681057797</v>
+        <v>0.3433566235539107</v>
       </c>
       <c r="G338">
-        <v>34.75610681057798</v>
+        <v>34.33566235539107</v>
       </c>
     </row>
     <row r="339">
@@ -10754,10 +10754,10 @@
         </is>
       </c>
       <c r="F339">
-        <v>0.3122907443003341</v>
+        <v>0.278861911862859</v>
       </c>
       <c r="G339">
-        <v>31.22907443003341</v>
+        <v>27.8861911862859</v>
       </c>
     </row>
     <row r="340">
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="F340">
-        <v>0.2865948079296014</v>
+        <v>0.2485369912438195</v>
       </c>
       <c r="G340">
-        <v>28.65948079296014</v>
+        <v>24.85369912438195</v>
       </c>
     </row>
     <row r="341">
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="F341">
-        <v>0.3459211383520389</v>
+        <v>0.3099102209332963</v>
       </c>
       <c r="G341">
-        <v>34.59211383520389</v>
+        <v>30.99102209332963</v>
       </c>
     </row>
     <row r="342">
@@ -10838,10 +10838,10 @@
         </is>
       </c>
       <c r="F342">
-        <v>0.2361062945046069</v>
+        <v>0.2154190916664193</v>
       </c>
       <c r="G342">
-        <v>23.61062945046069</v>
+        <v>21.54190916664193</v>
       </c>
     </row>
     <row r="343">
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="F343">
-        <v>0.3064664979213187</v>
+        <v>0.2750481468146767</v>
       </c>
       <c r="G343">
-        <v>30.64664979213187</v>
+        <v>27.50481468146767</v>
       </c>
     </row>
     <row r="344">
@@ -10894,10 +10894,10 @@
         </is>
       </c>
       <c r="F344">
-        <v>0.4619019254226725</v>
+        <v>0.518319392590284</v>
       </c>
       <c r="G344">
-        <v>46.19019254226725</v>
+        <v>51.8319392590284</v>
       </c>
     </row>
     <row r="345">
@@ -10922,10 +10922,10 @@
         </is>
       </c>
       <c r="F345">
-        <v>0.343388888486726</v>
+        <v>0.3625155209131835</v>
       </c>
       <c r="G345">
-        <v>34.3388888486726</v>
+        <v>36.25155209131835</v>
       </c>
     </row>
     <row r="346">
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="F346">
-        <v>0.3467016542171353</v>
+        <v>0.312651593402253</v>
       </c>
       <c r="G346">
-        <v>34.67016542171353</v>
+        <v>31.2651593402253</v>
       </c>
     </row>
     <row r="347">
@@ -10988,10 +10988,10 @@
         </is>
       </c>
       <c r="F347">
-        <v>0.278664142010315</v>
+        <v>0.2458423786572918</v>
       </c>
       <c r="G347">
-        <v>27.8664142010315</v>
+        <v>24.58423786572918</v>
       </c>
     </row>
     <row r="348">
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="F348">
-        <v>0.3774408442091069</v>
+        <v>0.3316699492227745</v>
       </c>
       <c r="G348">
-        <v>37.74408442091069</v>
+        <v>33.16699492227745</v>
       </c>
     </row>
     <row r="349">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="F349">
-        <v>0.190015589892269</v>
+        <v>0.1601576144041381</v>
       </c>
       <c r="G349">
-        <v>19.0015589892269</v>
+        <v>16.01576144041381</v>
       </c>
     </row>
     <row r="350">
@@ -11087,10 +11087,10 @@
         </is>
       </c>
       <c r="F350">
-        <v>0.3978605790467997</v>
+        <v>0.3587004213154761</v>
       </c>
       <c r="G350">
-        <v>39.78605790467996</v>
+        <v>35.87004213154761</v>
       </c>
     </row>
     <row r="351">
@@ -11120,10 +11120,10 @@
         </is>
       </c>
       <c r="F351">
-        <v>0.2925345570156126</v>
+        <v>0.2597606242822372</v>
       </c>
       <c r="G351">
-        <v>29.25345570156126</v>
+        <v>25.97606242822372</v>
       </c>
     </row>
     <row r="352">
@@ -11153,10 +11153,10 @@
         </is>
       </c>
       <c r="F352">
-        <v>0.3138443999756038</v>
+        <v>0.2879802062812883</v>
       </c>
       <c r="G352">
-        <v>31.38443999756038</v>
+        <v>28.79802062812884</v>
       </c>
     </row>
     <row r="353">
@@ -11186,10 +11186,10 @@
         </is>
       </c>
       <c r="F353">
-        <v>0.1642279569980659</v>
+        <v>0.1483275121310245</v>
       </c>
       <c r="G353">
-        <v>16.42279569980659</v>
+        <v>14.83275121310245</v>
       </c>
     </row>
     <row r="354">
@@ -11219,10 +11219,10 @@
         </is>
       </c>
       <c r="F354">
-        <v>0.3684296971119385</v>
+        <v>0.3332228259063935</v>
       </c>
       <c r="G354">
-        <v>36.84296971119385</v>
+        <v>33.32228259063935</v>
       </c>
     </row>
     <row r="355">
@@ -11252,10 +11252,10 @@
         </is>
       </c>
       <c r="F355">
-        <v>0.2449833017391058</v>
+        <v>0.2173241226494622</v>
       </c>
       <c r="G355">
-        <v>24.49833017391058</v>
+        <v>21.73241226494622</v>
       </c>
     </row>
     <row r="356">
@@ -11285,10 +11285,10 @@
         </is>
       </c>
       <c r="F356">
-        <v>0.5477483865755651</v>
+        <v>0.6040355638704691</v>
       </c>
       <c r="G356">
-        <v>54.77483865755651</v>
+        <v>60.4035563870469</v>
       </c>
     </row>
     <row r="357">
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="F357">
-        <v>0.3802021719335443</v>
+        <v>0.4367436354818985</v>
       </c>
       <c r="G357">
-        <v>38.02021719335443</v>
+        <v>43.67436354818985</v>
       </c>
     </row>
     <row r="358">
@@ -11351,10 +11351,10 @@
         </is>
       </c>
       <c r="F358">
-        <v>0.408483438853192</v>
+        <v>0.4291325269838704</v>
       </c>
       <c r="G358">
-        <v>40.8483438853192</v>
+        <v>42.91325269838705</v>
       </c>
     </row>
     <row r="359">
@@ -11384,10 +11384,10 @@
         </is>
       </c>
       <c r="F359">
-        <v>0.2777201073803593</v>
+        <v>0.2953108537791562</v>
       </c>
       <c r="G359">
-        <v>27.77201073803593</v>
+        <v>29.53108537791562</v>
       </c>
     </row>
     <row r="360">
@@ -11412,10 +11412,10 @@
         </is>
       </c>
       <c r="F360">
-        <v>0.4104584897040802</v>
+        <v>0.4041697615290319</v>
       </c>
       <c r="G360">
-        <v>41.04584897040802</v>
+        <v>40.4169761529032</v>
       </c>
     </row>
     <row r="361">
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="F361">
-        <v>0.2854901402609288</v>
+        <v>0.2833425911285414</v>
       </c>
       <c r="G361">
-        <v>28.54901402609288</v>
+        <v>28.33425911285414</v>
       </c>
     </row>
     <row r="362">
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="F362">
-        <v>0.2831096136746807</v>
+        <v>0.2648091114892482</v>
       </c>
       <c r="G362">
-        <v>28.31096136746807</v>
+        <v>26.48091114892483</v>
       </c>
     </row>
     <row r="363">
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="F363">
-        <v>0.2205141363389377</v>
+        <v>0.2038175384425567</v>
       </c>
       <c r="G363">
-        <v>22.05141363389377</v>
+        <v>20.38175384425567</v>
       </c>
     </row>
     <row r="364">
@@ -11519,10 +11519,10 @@
         </is>
       </c>
       <c r="F364">
-        <v>0.2030221842473232</v>
+        <v>0.147344007592442</v>
       </c>
       <c r="G364">
-        <v>20.30221842473232</v>
+        <v>14.7344007592442</v>
       </c>
     </row>
     <row r="365">
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="F365">
-        <v>0.2439731451033546</v>
+        <v>0.2340794457317354</v>
       </c>
       <c r="G365">
-        <v>24.39731451033546</v>
+        <v>23.40794457317354</v>
       </c>
     </row>
     <row r="366">
@@ -11575,10 +11575,10 @@
         </is>
       </c>
       <c r="F366">
-        <v>0.1610849375259628</v>
+        <v>0.1529969393818713</v>
       </c>
       <c r="G366">
-        <v>16.10849375259627</v>
+        <v>15.29969393818713</v>
       </c>
     </row>
     <row r="367">
@@ -11603,10 +11603,10 @@
         </is>
       </c>
       <c r="F367">
-        <v>0.2483897764922595</v>
+        <v>0.1447481709591939</v>
       </c>
       <c r="G367">
-        <v>24.83897764922595</v>
+        <v>14.47481709591939</v>
       </c>
     </row>
     <row r="368">
@@ -11631,10 +11631,10 @@
         </is>
       </c>
       <c r="F368">
-        <v>0.4251364137006842</v>
+        <v>0.4246996406969265</v>
       </c>
       <c r="G368">
-        <v>42.51364137006842</v>
+        <v>42.46996406969265</v>
       </c>
     </row>
     <row r="369">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="F369">
-        <v>0.3309908529911759</v>
+        <v>0.3307544695065041</v>
       </c>
       <c r="G369">
-        <v>33.09908529911759</v>
+        <v>33.0754469506504</v>
       </c>
     </row>
     <row r="370">
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="F370">
-        <v>0.2510684615357067</v>
+        <v>0.2332851108390843</v>
       </c>
       <c r="G370">
-        <v>25.10684615357067</v>
+        <v>23.32851108390843</v>
       </c>
     </row>
     <row r="371">
@@ -11725,10 +11725,10 @@
         </is>
       </c>
       <c r="F371">
-        <v>0.1906562179021469</v>
+        <v>0.1750216030887366</v>
       </c>
       <c r="G371">
-        <v>19.06562179021469</v>
+        <v>17.50216030887366</v>
       </c>
     </row>
     <row r="372">
@@ -11758,10 +11758,10 @@
         </is>
       </c>
       <c r="F372">
-        <v>0.2756299368826099</v>
+        <v>0.2028437650408863</v>
       </c>
       <c r="G372">
-        <v>27.562993688261</v>
+        <v>20.28437650408863</v>
       </c>
     </row>
     <row r="373">
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="F373">
-        <v>0.1258322455317908</v>
+        <v>0.08834172862519141</v>
       </c>
       <c r="G373">
-        <v>12.58322455317908</v>
+        <v>8.834172862519141</v>
       </c>
     </row>
     <row r="374">
@@ -11824,10 +11824,10 @@
         </is>
       </c>
       <c r="F374">
-        <v>0.2857076702934101</v>
+        <v>0.2742287050724087</v>
       </c>
       <c r="G374">
-        <v>28.57076702934101</v>
+        <v>27.42287050724087</v>
       </c>
     </row>
     <row r="375">
@@ -11857,10 +11857,10 @@
         </is>
       </c>
       <c r="F375">
-        <v>0.2010758094025335</v>
+        <v>0.1928115446777992</v>
       </c>
       <c r="G375">
-        <v>20.10758094025335</v>
+        <v>19.28115446777992</v>
       </c>
     </row>
     <row r="376">
@@ -11890,10 +11890,10 @@
         </is>
       </c>
       <c r="F376">
-        <v>0.2159564351365713</v>
+        <v>0.2070365324556894</v>
       </c>
       <c r="G376">
-        <v>21.59564351365713</v>
+        <v>20.70365324556894</v>
       </c>
     </row>
     <row r="377">
@@ -11923,10 +11923,10 @@
         </is>
       </c>
       <c r="F377">
-        <v>0.1103495613439933</v>
+        <v>0.1030307601684461</v>
       </c>
       <c r="G377">
-        <v>11.03495613439933</v>
+        <v>10.30307601684461</v>
       </c>
     </row>
     <row r="378">
@@ -11956,10 +11956,10 @@
         </is>
       </c>
       <c r="F378">
-        <v>0.3029290724891325</v>
+        <v>0.1811890695504882</v>
       </c>
       <c r="G378">
-        <v>30.29290724891325</v>
+        <v>18.11890695504882</v>
       </c>
     </row>
     <row r="379">
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="F379">
-        <v>0.1942729736283561</v>
+        <v>0.1085895647798689</v>
       </c>
       <c r="G379">
-        <v>19.42729736283561</v>
+        <v>10.85895647798689</v>
       </c>
     </row>
     <row r="380">
@@ -12022,10 +12022,10 @@
         </is>
       </c>
       <c r="F380">
-        <v>0.5093952847684318</v>
+        <v>0.5089299090414948</v>
       </c>
       <c r="G380">
-        <v>50.93952847684318</v>
+        <v>50.89299090414949</v>
       </c>
     </row>
     <row r="381">
@@ -12055,10 +12055,10 @@
         </is>
       </c>
       <c r="F381">
-        <v>0.3449475637113198</v>
+        <v>0.3445380118113955</v>
       </c>
       <c r="G381">
-        <v>34.49475637113198</v>
+        <v>34.45380118113955</v>
       </c>
     </row>
     <row r="382">
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="F382">
-        <v>0.3944008199581841</v>
+        <v>0.3941178110701279</v>
       </c>
       <c r="G382">
-        <v>39.44008199581841</v>
+        <v>39.41178110701279</v>
       </c>
     </row>
     <row r="383">
@@ -12121,10 +12121,10 @@
         </is>
       </c>
       <c r="F383">
-        <v>0.2670215158150853</v>
+        <v>0.2668321690391942</v>
       </c>
       <c r="G383">
-        <v>26.70215158150853</v>
+        <v>26.68321690391942</v>
       </c>
     </row>
     <row r="384">
@@ -12149,10 +12149,10 @@
         </is>
       </c>
       <c r="F384">
-        <v>0.33924727603963</v>
+        <v>0.3171577488853852</v>
       </c>
       <c r="G384">
-        <v>33.92472760396299</v>
+        <v>31.71577488853852</v>
       </c>
     </row>
     <row r="385">
@@ -12177,10 +12177,10 @@
         </is>
       </c>
       <c r="F385">
-        <v>0.2277096195018292</v>
+        <v>0.2131483531938795</v>
       </c>
       <c r="G385">
-        <v>22.77096195018292</v>
+        <v>21.31483531938795</v>
       </c>
     </row>
     <row r="386">
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="F386">
-        <v>0.4723764158599881</v>
+        <v>0.4473922002630948</v>
       </c>
       <c r="G386">
-        <v>47.23764158599882</v>
+        <v>44.73922002630948</v>
       </c>
     </row>
     <row r="387">
@@ -12228,10 +12228,10 @@
         </is>
       </c>
       <c r="F387">
-        <v>0.4704507018787932</v>
+        <v>0.3728059957790312</v>
       </c>
       <c r="G387">
-        <v>47.04507018787932</v>
+        <v>37.28059957790312</v>
       </c>
     </row>
     <row r="388">
@@ -12256,10 +12256,10 @@
         </is>
       </c>
       <c r="F388">
-        <v>0.523833010216578</v>
+        <v>0.3629839607394832</v>
       </c>
       <c r="G388">
-        <v>52.3833010216578</v>
+        <v>36.29839607394832</v>
       </c>
     </row>
     <row r="389">
@@ -12284,10 +12284,10 @@
         </is>
       </c>
       <c r="F389">
-        <v>0.5112974159873388</v>
+        <v>0.405957951985268</v>
       </c>
       <c r="G389">
-        <v>51.12974159873388</v>
+        <v>40.59579519852679</v>
       </c>
     </row>
     <row r="390">
@@ -12312,10 +12312,10 @@
         </is>
       </c>
       <c r="F390">
-        <v>0.3783456912177819</v>
+        <v>0.312449478127471</v>
       </c>
       <c r="G390">
-        <v>37.83456912177819</v>
+        <v>31.2449478127471</v>
       </c>
     </row>
     <row r="391">
@@ -12340,10 +12340,10 @@
         </is>
       </c>
       <c r="F391">
-        <v>0.582260971256455</v>
+        <v>0.4029232097031061</v>
       </c>
       <c r="G391">
-        <v>58.2260971256455</v>
+        <v>40.29232097031061</v>
       </c>
     </row>
     <row r="392">
@@ -12368,10 +12368,10 @@
         </is>
       </c>
       <c r="F392">
-        <v>0.5011368472944275</v>
+        <v>0.6556704010773048</v>
       </c>
       <c r="G392">
-        <v>50.11368472944275</v>
+        <v>65.56704010773048</v>
       </c>
     </row>
     <row r="393">
@@ -12396,10 +12396,10 @@
         </is>
       </c>
       <c r="F393">
-        <v>0.3634753024099048</v>
+        <v>0.4220306318992985</v>
       </c>
       <c r="G393">
-        <v>36.34753024099048</v>
+        <v>42.20306318992985</v>
       </c>
     </row>
     <row r="394">
@@ -12429,10 +12429,10 @@
         </is>
       </c>
       <c r="F394">
-        <v>0.5057510871942466</v>
+        <v>0.4098483064980182</v>
       </c>
       <c r="G394">
-        <v>50.57510871942466</v>
+        <v>40.98483064980182</v>
       </c>
     </row>
     <row r="395">
@@ -12462,10 +12462,10 @@
         </is>
       </c>
       <c r="F395">
-        <v>0.4359548974796317</v>
+        <v>0.3366079686573361</v>
       </c>
       <c r="G395">
-        <v>43.59548974796317</v>
+        <v>33.66079686573361</v>
       </c>
     </row>
     <row r="396">
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="F396">
-        <v>0.6338111015870482</v>
+        <v>0.4652299409927666</v>
       </c>
       <c r="G396">
-        <v>63.38111015870482</v>
+        <v>46.52299409927666</v>
       </c>
     </row>
     <row r="397">
@@ -12528,10 +12528,10 @@
         </is>
       </c>
       <c r="F397">
-        <v>0.4069143365925722</v>
+        <v>0.2542853622674425</v>
       </c>
       <c r="G397">
-        <v>40.69143365925722</v>
+        <v>25.42853622674425</v>
       </c>
     </row>
     <row r="398">
@@ -12561,10 +12561,10 @@
         </is>
       </c>
       <c r="F398">
-        <v>0.5707671200552784</v>
+        <v>0.4613442900632316</v>
       </c>
       <c r="G398">
-        <v>57.07671200552784</v>
+        <v>46.13442900632316</v>
       </c>
     </row>
     <row r="399">
@@ -12594,10 +12594,10 @@
         </is>
       </c>
       <c r="F399">
-        <v>0.4501707625076727</v>
+        <v>0.3490284355489401</v>
       </c>
       <c r="G399">
-        <v>45.01707625076727</v>
+        <v>34.90284355489401</v>
       </c>
     </row>
     <row r="400">
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="F400">
-        <v>0.4774504495842445</v>
+        <v>0.40806030666741</v>
       </c>
       <c r="G400">
-        <v>47.74504495842445</v>
+        <v>40.806030666741</v>
       </c>
     </row>
     <row r="401">
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="F401">
-        <v>0.2867112832629041</v>
+        <v>0.224045633430771</v>
       </c>
       <c r="G401">
-        <v>28.67112832629041</v>
+        <v>22.4045633430771</v>
       </c>
     </row>
     <row r="402">
@@ -12693,10 +12693,10 @@
         </is>
       </c>
       <c r="F402">
-        <v>0.6555475372507342</v>
+        <v>0.4732321979902833</v>
       </c>
       <c r="G402">
-        <v>65.55475372507343</v>
+        <v>47.32321979902833</v>
       </c>
     </row>
     <row r="403">
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="F403">
-        <v>0.5095421256609374</v>
+        <v>0.3331588757645854</v>
       </c>
       <c r="G403">
-        <v>50.95421256609374</v>
+        <v>33.31588757645854</v>
       </c>
     </row>
     <row r="404">
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="F404">
-        <v>0.5871969145251007</v>
+        <v>0.7279422468048973</v>
       </c>
       <c r="G404">
-        <v>58.71969145251007</v>
+        <v>72.79422468048973</v>
       </c>
     </row>
     <row r="405">
@@ -12792,10 +12792,10 @@
         </is>
       </c>
       <c r="F405">
-        <v>0.4192338057062437</v>
+        <v>0.586889557920213</v>
       </c>
       <c r="G405">
-        <v>41.92338057062437</v>
+        <v>58.6889557920213</v>
       </c>
     </row>
     <row r="406">
@@ -12825,10 +12825,10 @@
         </is>
       </c>
       <c r="F406">
-        <v>0.4325541380559864</v>
+        <v>0.4941732502116358</v>
       </c>
       <c r="G406">
-        <v>43.25541380559864</v>
+        <v>49.41732502116358</v>
       </c>
     </row>
     <row r="407">
@@ -12858,10 +12858,10 @@
         </is>
       </c>
       <c r="F407">
-        <v>0.2937870887025057</v>
+        <v>0.3492516084062092</v>
       </c>
       <c r="G407">
-        <v>29.37870887025057</v>
+        <v>34.92516084062092</v>
       </c>
     </row>
     <row r="408">
@@ -12886,10 +12886,10 @@
         </is>
       </c>
       <c r="F408">
-        <v>0.541724491365884</v>
+        <v>0.5115394182995467</v>
       </c>
       <c r="G408">
-        <v>54.1724491365884</v>
+        <v>51.15394182995468</v>
       </c>
     </row>
     <row r="409">
@@ -12914,10 +12914,10 @@
         </is>
       </c>
       <c r="F409">
-        <v>0.4039395979185942</v>
+        <v>0.3840878987351569</v>
       </c>
       <c r="G409">
-        <v>40.39395979185942</v>
+        <v>38.40878987351569</v>
       </c>
     </row>
     <row r="410">
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="F410">
-        <v>0.3475610681057797</v>
+        <v>0.3433566235539107</v>
       </c>
       <c r="G410">
-        <v>34.75610681057798</v>
+        <v>34.33566235539107</v>
       </c>
     </row>
     <row r="411">
@@ -12965,10 +12965,10 @@
         </is>
       </c>
       <c r="F411">
-        <v>0.3122907443003341</v>
+        <v>0.278861911862859</v>
       </c>
       <c r="G411">
-        <v>31.22907443003341</v>
+        <v>27.8861911862859</v>
       </c>
     </row>
     <row r="412">
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="F412">
-        <v>0.2865948079296014</v>
+        <v>0.2485369912438195</v>
       </c>
       <c r="G412">
-        <v>28.65948079296014</v>
+        <v>24.85369912438195</v>
       </c>
     </row>
     <row r="413">
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="F413">
-        <v>0.3459211383520389</v>
+        <v>0.3099102209332963</v>
       </c>
       <c r="G413">
-        <v>34.59211383520389</v>
+        <v>30.99102209332963</v>
       </c>
     </row>
     <row r="414">
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="F414">
-        <v>0.2361062945046069</v>
+        <v>0.2154190916664193</v>
       </c>
       <c r="G414">
-        <v>23.61062945046069</v>
+        <v>21.54190916664193</v>
       </c>
     </row>
     <row r="415">
@@ -13077,10 +13077,10 @@
         </is>
       </c>
       <c r="F415">
-        <v>0.3064664979213187</v>
+        <v>0.2750481468146767</v>
       </c>
       <c r="G415">
-        <v>30.64664979213187</v>
+        <v>27.50481468146767</v>
       </c>
     </row>
     <row r="416">
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="F416">
-        <v>0.4619019254226725</v>
+        <v>0.518319392590284</v>
       </c>
       <c r="G416">
-        <v>46.19019254226725</v>
+        <v>51.8319392590284</v>
       </c>
     </row>
     <row r="417">
@@ -13133,10 +13133,10 @@
         </is>
       </c>
       <c r="F417">
-        <v>0.343388888486726</v>
+        <v>0.3625155209131835</v>
       </c>
       <c r="G417">
-        <v>34.3388888486726</v>
+        <v>36.25155209131835</v>
       </c>
     </row>
     <row r="418">
@@ -13166,10 +13166,10 @@
         </is>
       </c>
       <c r="F418">
-        <v>0.3467016542171353</v>
+        <v>0.312651593402253</v>
       </c>
       <c r="G418">
-        <v>34.67016542171353</v>
+        <v>31.2651593402253</v>
       </c>
     </row>
     <row r="419">
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="F419">
-        <v>0.278664142010315</v>
+        <v>0.2458423786572918</v>
       </c>
       <c r="G419">
-        <v>27.8664142010315</v>
+        <v>24.58423786572918</v>
       </c>
     </row>
     <row r="420">
@@ -13232,10 +13232,10 @@
         </is>
       </c>
       <c r="F420">
-        <v>0.3774408442091069</v>
+        <v>0.3316699492227745</v>
       </c>
       <c r="G420">
-        <v>37.74408442091069</v>
+        <v>33.16699492227745</v>
       </c>
     </row>
     <row r="421">
@@ -13265,10 +13265,10 @@
         </is>
       </c>
       <c r="F421">
-        <v>0.190015589892269</v>
+        <v>0.1601576144041381</v>
       </c>
       <c r="G421">
-        <v>19.0015589892269</v>
+        <v>16.01576144041381</v>
       </c>
     </row>
     <row r="422">
@@ -13298,10 +13298,10 @@
         </is>
       </c>
       <c r="F422">
-        <v>0.3978605790467997</v>
+        <v>0.3587004213154761</v>
       </c>
       <c r="G422">
-        <v>39.78605790467996</v>
+        <v>35.87004213154761</v>
       </c>
     </row>
     <row r="423">
@@ -13331,10 +13331,10 @@
         </is>
       </c>
       <c r="F423">
-        <v>0.2925345570156126</v>
+        <v>0.2597606242822372</v>
       </c>
       <c r="G423">
-        <v>29.25345570156126</v>
+        <v>25.97606242822372</v>
       </c>
     </row>
     <row r="424">
@@ -13364,10 +13364,10 @@
         </is>
       </c>
       <c r="F424">
-        <v>0.3138443999756038</v>
+        <v>0.2879802062812883</v>
       </c>
       <c r="G424">
-        <v>31.38443999756038</v>
+        <v>28.79802062812884</v>
       </c>
     </row>
     <row r="425">
@@ -13397,10 +13397,10 @@
         </is>
       </c>
       <c r="F425">
-        <v>0.1642279569980659</v>
+        <v>0.1483275121310245</v>
       </c>
       <c r="G425">
-        <v>16.42279569980659</v>
+        <v>14.83275121310245</v>
       </c>
     </row>
     <row r="426">
@@ -13430,10 +13430,10 @@
         </is>
       </c>
       <c r="F426">
-        <v>0.3684296971119385</v>
+        <v>0.3332228259063935</v>
       </c>
       <c r="G426">
-        <v>36.84296971119385</v>
+        <v>33.32228259063935</v>
       </c>
     </row>
     <row r="427">
@@ -13463,10 +13463,10 @@
         </is>
       </c>
       <c r="F427">
-        <v>0.2449833017391058</v>
+        <v>0.2173241226494622</v>
       </c>
       <c r="G427">
-        <v>24.49833017391058</v>
+        <v>21.73241226494622</v>
       </c>
     </row>
     <row r="428">
@@ -13496,10 +13496,10 @@
         </is>
       </c>
       <c r="F428">
-        <v>0.5477483865755651</v>
+        <v>0.6040355638704691</v>
       </c>
       <c r="G428">
-        <v>54.77483865755651</v>
+        <v>60.4035563870469</v>
       </c>
     </row>
     <row r="429">
@@ -13529,10 +13529,10 @@
         </is>
       </c>
       <c r="F429">
-        <v>0.3802021719335443</v>
+        <v>0.4367436354818985</v>
       </c>
       <c r="G429">
-        <v>38.02021719335443</v>
+        <v>43.67436354818985</v>
       </c>
     </row>
     <row r="430">
@@ -13562,10 +13562,10 @@
         </is>
       </c>
       <c r="F430">
-        <v>0.408483438853192</v>
+        <v>0.4291325269838704</v>
       </c>
       <c r="G430">
-        <v>40.8483438853192</v>
+        <v>42.91325269838705</v>
       </c>
     </row>
     <row r="431">
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="F431">
-        <v>0.2777201073803593</v>
+        <v>0.2953108537791562</v>
       </c>
       <c r="G431">
-        <v>27.77201073803593</v>
+        <v>29.53108537791562</v>
       </c>
     </row>
     <row r="432">
@@ -13623,10 +13623,10 @@
         </is>
       </c>
       <c r="F432">
-        <v>0.4104584897040802</v>
+        <v>0.4041697615290319</v>
       </c>
       <c r="G432">
-        <v>41.04584897040802</v>
+        <v>40.4169761529032</v>
       </c>
     </row>
     <row r="433">
@@ -13651,10 +13651,10 @@
         </is>
       </c>
       <c r="F433">
-        <v>0.2854901402609288</v>
+        <v>0.2833425911285414</v>
       </c>
       <c r="G433">
-        <v>28.54901402609288</v>
+        <v>28.33425911285414</v>
       </c>
     </row>
   </sheetData>

--- a/output/summary_WB_regions_quality_prevalences.xlsx
+++ b/output/summary_WB_regions_quality_prevalences.xlsx
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="G254">
-        <v>0.0916307719718862</v>
+        <v>0.0913084243531764</v>
       </c>
       <c r="H254">
-        <v>9.16307719718862</v>
+        <v>9.130842435317641</v>
       </c>
     </row>
     <row r="255">
@@ -8017,10 +8017,10 @@
         </is>
       </c>
       <c r="G255">
-        <v>0.07279644080015522</v>
+        <v>0.07362617179275245</v>
       </c>
       <c r="H255">
-        <v>7.279644080015522</v>
+        <v>7.362617179275246</v>
       </c>
     </row>
     <row r="256">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="G256">
-        <v>0.01951331141863899</v>
+        <v>0.01951879683630452</v>
       </c>
       <c r="H256">
-        <v>1.951331141863899</v>
+        <v>1.951879683630452</v>
       </c>
     </row>
     <row r="257">
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="G257">
-        <v>0.08677971438863964</v>
+        <v>0.08707326035626158</v>
       </c>
       <c r="H257">
-        <v>8.677971438863965</v>
+        <v>8.707326035626158</v>
       </c>
     </row>
     <row r="258">
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="G258">
-        <v>0.05129207266478216</v>
+        <v>0.05072446781729328</v>
       </c>
       <c r="H258">
-        <v>5.129207266478216</v>
+        <v>5.072446781729328</v>
       </c>
     </row>
     <row r="259">
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="G260">
-        <v>0.1511647516803503</v>
+        <v>0.1467807881028241</v>
       </c>
       <c r="H260">
-        <v>15.11647516803503</v>
+        <v>14.67807881028241</v>
       </c>
     </row>
     <row r="261">
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="G261">
-        <v>0.1310075535751049</v>
+        <v>0.1344883408232813</v>
       </c>
       <c r="H261">
-        <v>13.10075535751048</v>
+        <v>13.44883408232813</v>
       </c>
     </row>
     <row r="262">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="G262">
-        <v>0.08794124519799029</v>
+        <v>0.08896325756343239</v>
       </c>
       <c r="H262">
-        <v>8.794124519799029</v>
+        <v>8.89632575634324</v>
       </c>
     </row>
     <row r="263">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="G263">
-        <v>0.05799682301970644</v>
+        <v>0.05863865519567614</v>
       </c>
       <c r="H263">
-        <v>5.799682301970644</v>
+        <v>5.863865519567614</v>
       </c>
     </row>
     <row r="264">
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="G264">
-        <v>0.02827417433608785</v>
+        <v>0.02828273766013877</v>
       </c>
       <c r="H264">
-        <v>2.827417433608785</v>
+        <v>2.828273766013877</v>
       </c>
     </row>
     <row r="265">
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="G265">
-        <v>0.0101995612039766</v>
+        <v>0.01020177447236553</v>
       </c>
       <c r="H265">
-        <v>1.01995612039766</v>
+        <v>1.020177447236553</v>
       </c>
     </row>
     <row r="266">
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="G266">
-        <v>0.1033363768695572</v>
+        <v>0.1036659422475905</v>
       </c>
       <c r="H266">
-        <v>10.33363768695572</v>
+        <v>10.36659422475905</v>
       </c>
     </row>
     <row r="267">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="G267">
-        <v>0.06976174892012778</v>
+        <v>0.0700182719017895</v>
       </c>
       <c r="H267">
-        <v>6.976174892012778</v>
+        <v>7.00182719017895</v>
       </c>
     </row>
     <row r="268">
@@ -8416,10 +8416,10 @@
         </is>
       </c>
       <c r="G268">
-        <v>0.06920509253133324</v>
+        <v>0.06874659717791619</v>
       </c>
       <c r="H268">
-        <v>6.920509253133324</v>
+        <v>6.874659717791618</v>
       </c>
     </row>
     <row r="269">
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="G269">
-        <v>0.03472930618200875</v>
+        <v>0.03406081633105155</v>
       </c>
       <c r="H269">
-        <v>3.472930618200875</v>
+        <v>3.406081633105155</v>
       </c>
     </row>
     <row r="270">
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="G272">
-        <v>0.2044166817908636</v>
+        <v>0.1990722269711983</v>
       </c>
       <c r="H272">
-        <v>20.44166817908636</v>
+        <v>19.90722269711983</v>
       </c>
     </row>
     <row r="273">
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="G273">
-        <v>0.1004850905222672</v>
+        <v>0.09701522283940414</v>
       </c>
       <c r="H273">
-        <v>10.04850905222672</v>
+        <v>9.701522283940415</v>
       </c>
     </row>
     <row r="274">
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="G274">
-        <v>0.1748168609673628</v>
+        <v>0.1776508659365985</v>
       </c>
       <c r="H274">
-        <v>17.48168609673629</v>
+        <v>17.76508659365984</v>
       </c>
     </row>
     <row r="275">
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="G275">
-        <v>0.08681178294042823</v>
+        <v>0.0909450580491105</v>
       </c>
       <c r="H275">
-        <v>8.681178294042823</v>
+        <v>9.09450580491105</v>
       </c>
     </row>
     <row r="276">
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="G276">
-        <v>0.1187005818022016</v>
+        <v>0.1181513743821153</v>
       </c>
       <c r="H276">
-        <v>11.87005818022016</v>
+        <v>11.81513743821153</v>
       </c>
     </row>
     <row r="277">
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="G277">
-        <v>0.06491666875343731</v>
+        <v>0.06481819992028583</v>
       </c>
       <c r="H277">
-        <v>6.491666875343731</v>
+        <v>6.481819992028583</v>
       </c>
     </row>
     <row r="278">
@@ -8726,10 +8726,10 @@
         </is>
       </c>
       <c r="G278">
-        <v>0.04744231901660394</v>
+        <v>0.04750778707163263</v>
       </c>
       <c r="H278">
-        <v>4.744231901660394</v>
+        <v>4.750778707163263</v>
       </c>
     </row>
     <row r="279">
@@ -8754,10 +8754,10 @@
         </is>
       </c>
       <c r="G279">
-        <v>0.03388750155880806</v>
+        <v>0.0343557309636072</v>
       </c>
       <c r="H279">
-        <v>3.388750155880806</v>
+        <v>3.43557309636072</v>
       </c>
     </row>
     <row r="280">
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="G280">
-        <v>0.008728377953952095</v>
+        <v>0.008730930299107013</v>
       </c>
       <c r="H280">
-        <v>0.8728377953952096</v>
+        <v>0.8730930299107013</v>
       </c>
     </row>
     <row r="281">
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="G281">
-        <v>0.05717150888083796</v>
+        <v>0.05756918221863314</v>
       </c>
       <c r="H281">
-        <v>5.717150888083796</v>
+        <v>5.756918221863313</v>
       </c>
     </row>
     <row r="282">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="G282">
-        <v>0.03518250539600514</v>
+        <v>0.03403666033504212</v>
       </c>
       <c r="H282">
-        <v>3.518250539600514</v>
+        <v>3.403666033504212</v>
       </c>
     </row>
     <row r="283">
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="G284">
-        <v>0.05529613241564461</v>
+        <v>0.05282520542482209</v>
       </c>
       <c r="H284">
-        <v>5.52961324156446</v>
+        <v>5.282520542482209</v>
       </c>
     </row>
     <row r="285">
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="G285">
-        <v>0.1095606442581611</v>
+        <v>0.1134874232142641</v>
       </c>
       <c r="H285">
-        <v>10.95606442581611</v>
+        <v>11.34874232142641</v>
       </c>
     </row>
     <row r="286">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="G286">
-        <v>0.04234815795013871</v>
+        <v>0.04295726567883017</v>
       </c>
       <c r="H286">
-        <v>4.234815795013871</v>
+        <v>4.295726567883017</v>
       </c>
     </row>
     <row r="287">
@@ -8988,10 +8988,10 @@
         </is>
       </c>
       <c r="G287">
-        <v>0.02561968393144362</v>
+        <v>0.02595024596911234</v>
       </c>
       <c r="H287">
-        <v>2.561968393144362</v>
+        <v>2.595024596911234</v>
       </c>
     </row>
     <row r="288">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="G288">
-        <v>0.01194028438730371</v>
+        <v>0.01194438878145985</v>
       </c>
       <c r="H288">
-        <v>1.194028438730371</v>
+        <v>1.194438878145985</v>
       </c>
     </row>
     <row r="289">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="G289">
-        <v>0.005313772050973845</v>
+        <v>0.005314674399221534</v>
       </c>
       <c r="H289">
-        <v>0.5313772050973845</v>
+        <v>0.5314674399221534</v>
       </c>
     </row>
     <row r="290">
@@ -9087,10 +9087,10 @@
         </is>
       </c>
       <c r="G290">
-        <v>0.06707905998295503</v>
+        <v>0.06751413719402284</v>
       </c>
       <c r="H290">
-        <v>6.707905998295503</v>
+        <v>6.751413719402284</v>
       </c>
     </row>
     <row r="291">
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="G291">
-        <v>0.046987912837392</v>
+        <v>0.04734714015235641</v>
       </c>
       <c r="H291">
-        <v>4.698791283739199</v>
+        <v>4.734714015235641</v>
       </c>
     </row>
     <row r="292">
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="G292">
-        <v>0.04628114450428331</v>
+        <v>0.0450219555376129</v>
       </c>
       <c r="H292">
-        <v>4.62811445042833</v>
+        <v>4.50219555376129</v>
       </c>
     </row>
     <row r="293">
@@ -9186,10 +9186,10 @@
         </is>
       </c>
       <c r="G293">
-        <v>0.02492046308284719</v>
+        <v>0.02387941825414331</v>
       </c>
       <c r="H293">
-        <v>2.492046308284719</v>
+        <v>2.387941825414331</v>
       </c>
     </row>
     <row r="294">
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="G296">
-        <v>0.07852334399695854</v>
+        <v>0.07520741449204843</v>
       </c>
       <c r="H296">
-        <v>7.852334399695854</v>
+        <v>7.520741449204843</v>
       </c>
     </row>
     <row r="297">
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="G297">
-        <v>0.03319088270647588</v>
+        <v>0.03152414142315379</v>
       </c>
       <c r="H297">
-        <v>3.319088270647588</v>
+        <v>3.152414142315379</v>
       </c>
     </row>
     <row r="298">
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="G298">
-        <v>0.1451143784464539</v>
+        <v>0.1486211886445423</v>
       </c>
       <c r="H298">
-        <v>14.51143784464539</v>
+        <v>14.86211886445423</v>
       </c>
     </row>
     <row r="299">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="G299">
-        <v>0.07369327326042359</v>
+        <v>0.07804372572354543</v>
       </c>
       <c r="H299">
-        <v>7.369327326042359</v>
+        <v>7.804372572354542</v>
       </c>
     </row>
     <row r="300">
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="G300">
-        <v>0.06251580004378578</v>
+        <v>0.06237962804588216</v>
       </c>
       <c r="H300">
-        <v>6.251580004378578</v>
+        <v>6.237962804588216</v>
       </c>
     </row>
     <row r="301">
@@ -9440,10 +9440,10 @@
         </is>
       </c>
       <c r="G301">
-        <v>0.03256690871466305</v>
+        <v>0.03283136720297412</v>
       </c>
       <c r="H301">
-        <v>3.256690871466305</v>
+        <v>3.283136720297412</v>
       </c>
     </row>
     <row r="302">
@@ -9463,10 +9463,10 @@
         </is>
       </c>
       <c r="G302">
-        <v>0.03347930361193563</v>
+        <v>0.0336599775919482</v>
       </c>
       <c r="H302">
-        <v>3.347930361193563</v>
+        <v>3.36599775919482</v>
       </c>
     </row>
     <row r="303">
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="G303">
-        <v>0.02130604022887199</v>
+        <v>0.02152074427822405</v>
       </c>
       <c r="H303">
-        <v>2.130604022887199</v>
+        <v>2.152074427822405</v>
       </c>
     </row>
     <row r="304">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="G304">
-        <v>0.004207010377073076</v>
+        <v>0.004208681453276632</v>
       </c>
       <c r="H304">
-        <v>0.4207010377073075</v>
+        <v>0.4208681453276632</v>
       </c>
     </row>
     <row r="305">
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="G305">
-        <v>0.04281679429638805</v>
+        <v>0.04317302692724207</v>
       </c>
       <c r="H305">
-        <v>4.281679429638805</v>
+        <v>4.317302692724208</v>
       </c>
     </row>
     <row r="306">
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="G306">
-        <v>0.02462395845945278</v>
+        <v>0.0238363114122485</v>
       </c>
       <c r="H306">
-        <v>2.462395845945278</v>
+        <v>2.38363114122485</v>
       </c>
     </row>
     <row r="307">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="G308">
-        <v>0.03196417126703811</v>
+        <v>0.03017396219004481</v>
       </c>
       <c r="H308">
-        <v>3.196417126703811</v>
+        <v>3.017396219004481</v>
       </c>
     </row>
     <row r="309">
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="G309">
-        <v>0.09640077129655433</v>
+        <v>0.1003973229077323</v>
       </c>
       <c r="H309">
-        <v>9.640077129655433</v>
+        <v>10.03973229077323</v>
       </c>
     </row>
     <row r="310">
@@ -9692,10 +9692,10 @@
         </is>
       </c>
       <c r="G310">
-        <v>0.0269784117064889</v>
+        <v>0.02726940398476657</v>
       </c>
       <c r="H310">
-        <v>2.69784117064889</v>
+        <v>2.726940398476657</v>
       </c>
     </row>
     <row r="311">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="G311">
-        <v>0.01576295577745114</v>
+        <v>0.01590311039060131</v>
       </c>
       <c r="H311">
-        <v>1.576295577745114</v>
+        <v>1.590311039060131</v>
       </c>
     </row>
     <row r="312">
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="G312">
-        <v>0.00560028715462868</v>
+        <v>0.005603008959978933</v>
       </c>
       <c r="H312">
-        <v>0.560028715462868</v>
+        <v>0.5603008959978932</v>
       </c>
     </row>
     <row r="313">
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="G313">
-        <v>0.002725805613533484</v>
+        <v>0.002726359650364568</v>
       </c>
       <c r="H313">
-        <v>0.2725805613533484</v>
+        <v>0.2726359650364568</v>
       </c>
     </row>
     <row r="314">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="G314">
-        <v>0.05083429840704313</v>
+        <v>0.05122787150397955</v>
       </c>
       <c r="H314">
-        <v>5.083429840704313</v>
+        <v>5.122787150397955</v>
       </c>
     </row>
     <row r="315">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="G315">
-        <v>0.0345759058772373</v>
+        <v>0.03489375765910677</v>
       </c>
       <c r="H315">
-        <v>3.45759058772373</v>
+        <v>3.489375765910677</v>
       </c>
     </row>
     <row r="316">
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="G316">
-        <v>0.03297750100405082</v>
+        <v>0.03208302916585584</v>
       </c>
       <c r="H316">
-        <v>3.297750100405082</v>
+        <v>3.208302916585584</v>
       </c>
     </row>
     <row r="317">
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="G317">
-        <v>0.01690009193662021</v>
+        <v>0.0162112174068882</v>
       </c>
       <c r="H317">
-        <v>1.690009193662021</v>
+        <v>1.62112174068882</v>
       </c>
     </row>
     <row r="318">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="G320">
-        <v>0.0462813097051644</v>
+        <v>0.04380848933467273</v>
       </c>
       <c r="H320">
-        <v>4.62813097051644</v>
+        <v>4.380848933467274</v>
       </c>
     </row>
     <row r="321">
@@ -10055,10 +10055,10 @@
         </is>
       </c>
       <c r="G321">
-        <v>0.01833860458256666</v>
+        <v>0.0171980341005573</v>
       </c>
       <c r="H321">
-        <v>1.833860458256666</v>
+        <v>1.71980341005573</v>
       </c>
     </row>
     <row r="322">
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="G322">
-        <v>0.1285832674886867</v>
+        <v>0.1323639937523842</v>
       </c>
       <c r="H322">
-        <v>12.85832674886867</v>
+        <v>13.23639937523842</v>
       </c>
     </row>
     <row r="323">
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="G323">
-        <v>0.06393437762765573</v>
+        <v>0.06814865848684466</v>
       </c>
       <c r="H323">
-        <v>6.393437762765573</v>
+        <v>6.814865848684466</v>
       </c>
     </row>
     <row r="324">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="G324">
-        <v>0.04457495116217539</v>
+        <v>0.04459912215554464</v>
       </c>
       <c r="H324">
-        <v>4.457495116217539</v>
+        <v>4.459912215554464</v>
       </c>
     </row>
     <row r="325">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="G325">
-        <v>0.02252945668686835</v>
+        <v>0.02286457715045045</v>
       </c>
       <c r="H325">
-        <v>2.252945668686835</v>
+        <v>2.286457715045045</v>
       </c>
     </row>
     <row r="326">
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="G326">
-        <v>0.07791785925761051</v>
+        <v>0.07771601800788747</v>
       </c>
       <c r="H326">
-        <v>7.791785925761051</v>
+        <v>7.771601800788747</v>
       </c>
     </row>
     <row r="327">
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="G327">
-        <v>0.05638977562872927</v>
+        <v>0.05725253111171315</v>
       </c>
       <c r="H327">
-        <v>5.638977562872928</v>
+        <v>5.725253111171315</v>
       </c>
     </row>
     <row r="328">
@@ -10256,10 +10256,10 @@
         </is>
       </c>
       <c r="G328">
-        <v>0.01877875404150122</v>
+        <v>0.01878373620974255</v>
       </c>
       <c r="H328">
-        <v>1.877875404150122</v>
+        <v>1.878373620974255</v>
       </c>
     </row>
     <row r="329">
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="G329">
-        <v>0.08156243583876231</v>
+        <v>0.0820436746313319</v>
       </c>
       <c r="H329">
-        <v>8.156243583876231</v>
+        <v>8.20436746313319</v>
       </c>
     </row>
     <row r="330">
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="G330">
-        <v>0.05270930320187914</v>
+        <v>0.05114473509538969</v>
       </c>
       <c r="H330">
-        <v>5.270930320187914</v>
+        <v>5.11447350953897</v>
       </c>
     </row>
     <row r="331">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="G332">
-        <v>0.1171425805838145</v>
+        <v>0.1133345417062603</v>
       </c>
       <c r="H332">
-        <v>11.71425805838145</v>
+        <v>11.33345417062603</v>
       </c>
     </row>
     <row r="333">
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="G333">
-        <v>0.1367479509906803</v>
+        <v>0.1403463143588518</v>
       </c>
       <c r="H333">
-        <v>13.67479509906803</v>
+        <v>14.03463143588518</v>
       </c>
     </row>
     <row r="334">
@@ -10429,10 +10429,10 @@
         </is>
       </c>
       <c r="G334">
-        <v>0.06906927778012494</v>
+        <v>0.07012947919815625</v>
       </c>
       <c r="H334">
-        <v>6.906927778012493</v>
+        <v>7.012947919815625</v>
       </c>
     </row>
     <row r="335">
@@ -10462,10 +10462,10 @@
         </is>
       </c>
       <c r="G335">
-        <v>0.04399926991088317</v>
+        <v>0.0446690797278653</v>
       </c>
       <c r="H335">
-        <v>4.399926991088317</v>
+        <v>4.46690797278653</v>
       </c>
     </row>
     <row r="336">
@@ -10495,10 +10495,10 @@
         </is>
       </c>
       <c r="G336">
-        <v>0.02614313465130089</v>
+        <v>0.02615094604227567</v>
       </c>
       <c r="H336">
-        <v>2.614313465130089</v>
+        <v>2.615094604227568</v>
       </c>
     </row>
     <row r="337">
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="G337">
-        <v>0.0109496164175387</v>
+        <v>0.01095159081427515</v>
       </c>
       <c r="H337">
-        <v>1.09496164175387</v>
+        <v>1.095159081427515</v>
       </c>
     </row>
     <row r="338">
@@ -10561,10 +10561,10 @@
         </is>
       </c>
       <c r="G338">
-        <v>0.09597607541142522</v>
+        <v>0.09649297419004679</v>
       </c>
       <c r="H338">
-        <v>9.597607541142523</v>
+        <v>9.649297419004679</v>
       </c>
     </row>
     <row r="339">
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="G339">
-        <v>0.06674720234554705</v>
+        <v>0.06719178759082467</v>
       </c>
       <c r="H339">
-        <v>6.674720234554705</v>
+        <v>6.719178759082467</v>
       </c>
     </row>
     <row r="340">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="G340">
-        <v>0.06841630401798666</v>
+        <v>0.06678801549198317</v>
       </c>
       <c r="H340">
-        <v>6.841630401798667</v>
+        <v>6.678801549198317</v>
       </c>
     </row>
     <row r="341">
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="G341">
-        <v>0.03818626975469922</v>
+        <v>0.03668061892940835</v>
       </c>
       <c r="H341">
-        <v>3.818626975469922</v>
+        <v>3.668061892940835</v>
       </c>
     </row>
     <row r="342">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="G344">
-        <v>0.160616759029978</v>
+        <v>0.1558150763613848</v>
       </c>
       <c r="H344">
-        <v>16.06167590299779</v>
+        <v>15.58150763613848</v>
       </c>
     </row>
     <row r="345">
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="G345">
-        <v>0.07576836882838674</v>
+        <v>0.07290597700131868</v>
       </c>
       <c r="H345">
-        <v>7.576836882838673</v>
+        <v>7.290597700131868</v>
       </c>
     </row>
     <row r="346">
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="G346">
-        <v>0.1790961009508806</v>
+        <v>0.1820193721886232</v>
       </c>
       <c r="H346">
-        <v>17.90961009508806</v>
+        <v>18.20193721886232</v>
       </c>
     </row>
     <row r="347">
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="G347">
-        <v>0.09402622736957915</v>
+        <v>0.09830563818473599</v>
       </c>
       <c r="H347">
-        <v>9.402622736957914</v>
+        <v>9.8305638184736</v>
       </c>
     </row>
     <row r="348">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="G348">
-        <v>0.1011508860205781</v>
+        <v>0.1007015180208867</v>
       </c>
       <c r="H348">
-        <v>10.11508860205782</v>
+        <v>10.07015180208867</v>
       </c>
     </row>
     <row r="349">
@@ -10914,10 +10914,10 @@
         </is>
       </c>
       <c r="G349">
-        <v>0.05499012245733793</v>
+        <v>0.05503255537095115</v>
       </c>
       <c r="H349">
-        <v>5.499012245733793</v>
+        <v>5.503255537095115</v>
       </c>
     </row>
     <row r="350">
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="G350">
-        <v>0.04744231901660394</v>
+        <v>0.04750778707163263</v>
       </c>
       <c r="H350">
-        <v>4.744231901660394</v>
+        <v>4.750778707163263</v>
       </c>
     </row>
     <row r="351">
@@ -10965,10 +10965,10 @@
         </is>
       </c>
       <c r="G351">
-        <v>0.03388750155880806</v>
+        <v>0.0343557309636072</v>
       </c>
       <c r="H351">
-        <v>3.388750155880806</v>
+        <v>3.43557309636072</v>
       </c>
     </row>
     <row r="352">
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="G352">
-        <v>0.008728377953952095</v>
+        <v>0.008730930299107013</v>
       </c>
       <c r="H352">
-        <v>0.8728377953952096</v>
+        <v>0.8730930299107013</v>
       </c>
     </row>
     <row r="353">
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="G353">
-        <v>0.05717150888083796</v>
+        <v>0.05756918221863314</v>
       </c>
       <c r="H353">
-        <v>5.717150888083796</v>
+        <v>5.756918221863313</v>
       </c>
     </row>
     <row r="354">
@@ -11049,10 +11049,10 @@
         </is>
       </c>
       <c r="G354">
-        <v>0.03518250539600514</v>
+        <v>0.03403666033504212</v>
       </c>
       <c r="H354">
-        <v>3.518250539600514</v>
+        <v>3.403666033504212</v>
       </c>
     </row>
     <row r="355">
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="G356">
-        <v>0.05529613241564461</v>
+        <v>0.05282520542482209</v>
       </c>
       <c r="H356">
-        <v>5.52961324156446</v>
+        <v>5.282520542482209</v>
       </c>
     </row>
     <row r="357">
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="G357">
-        <v>0.1095606442581611</v>
+        <v>0.1134874232142641</v>
       </c>
       <c r="H357">
-        <v>10.95606442581611</v>
+        <v>11.34874232142641</v>
       </c>
     </row>
     <row r="358">
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="G358">
-        <v>0.04234815795013871</v>
+        <v>0.04295726567883017</v>
       </c>
       <c r="H358">
-        <v>4.234815795013871</v>
+        <v>4.295726567883017</v>
       </c>
     </row>
     <row r="359">
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="G359">
-        <v>0.02561968393144362</v>
+        <v>0.02595024596911234</v>
       </c>
       <c r="H359">
-        <v>2.561968393144362</v>
+        <v>2.595024596911234</v>
       </c>
     </row>
     <row r="360">
@@ -11232,10 +11232,10 @@
         </is>
       </c>
       <c r="G360">
-        <v>0.01194028438730371</v>
+        <v>0.01194438878145985</v>
       </c>
       <c r="H360">
-        <v>1.194028438730371</v>
+        <v>1.194438878145985</v>
       </c>
     </row>
     <row r="361">
@@ -11265,10 +11265,10 @@
         </is>
       </c>
       <c r="G361">
-        <v>0.005313772050973845</v>
+        <v>0.005314674399221534</v>
       </c>
       <c r="H361">
-        <v>0.5313772050973845</v>
+        <v>0.5314674399221534</v>
       </c>
     </row>
     <row r="362">
@@ -11298,10 +11298,10 @@
         </is>
       </c>
       <c r="G362">
-        <v>0.06707905998295503</v>
+        <v>0.06751413719402284</v>
       </c>
       <c r="H362">
-        <v>6.707905998295503</v>
+        <v>6.751413719402284</v>
       </c>
     </row>
     <row r="363">
@@ -11331,10 +11331,10 @@
         </is>
       </c>
       <c r="G363">
-        <v>0.046987912837392</v>
+        <v>0.04734714015235641</v>
       </c>
       <c r="H363">
-        <v>4.698791283739199</v>
+        <v>4.734714015235641</v>
       </c>
     </row>
     <row r="364">
@@ -11364,10 +11364,10 @@
         </is>
       </c>
       <c r="G364">
-        <v>0.04628114450428331</v>
+        <v>0.0450219555376129</v>
       </c>
       <c r="H364">
-        <v>4.62811445042833</v>
+        <v>4.50219555376129</v>
       </c>
     </row>
     <row r="365">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="G365">
-        <v>0.02492046308284719</v>
+        <v>0.02387941825414331</v>
       </c>
       <c r="H365">
-        <v>2.492046308284719</v>
+        <v>2.387941825414331</v>
       </c>
     </row>
     <row r="366">
@@ -11496,10 +11496,10 @@
         </is>
       </c>
       <c r="G368">
-        <v>0.07852334399695854</v>
+        <v>0.07520741449204843</v>
       </c>
       <c r="H368">
-        <v>7.852334399695854</v>
+        <v>7.520741449204843</v>
       </c>
     </row>
     <row r="369">
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="G369">
-        <v>0.03319088270647588</v>
+        <v>0.03152414142315379</v>
       </c>
       <c r="H369">
-        <v>3.319088270647588</v>
+        <v>3.152414142315379</v>
       </c>
     </row>
     <row r="370">
@@ -11562,10 +11562,10 @@
         </is>
       </c>
       <c r="G370">
-        <v>0.1451143784464539</v>
+        <v>0.1486211886445423</v>
       </c>
       <c r="H370">
-        <v>14.51143784464539</v>
+        <v>14.86211886445423</v>
       </c>
     </row>
     <row r="371">
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="G371">
-        <v>0.07369327326042359</v>
+        <v>0.07804372572354543</v>
       </c>
       <c r="H371">
-        <v>7.369327326042359</v>
+        <v>7.804372572354542</v>
       </c>
     </row>
     <row r="372">
@@ -11623,10 +11623,10 @@
         </is>
       </c>
       <c r="G372">
-        <v>0.06251580004378578</v>
+        <v>0.06237962804588216</v>
       </c>
       <c r="H372">
-        <v>6.251580004378578</v>
+        <v>6.237962804588216</v>
       </c>
     </row>
     <row r="373">
@@ -11651,10 +11651,10 @@
         </is>
       </c>
       <c r="G373">
-        <v>0.03256690871466305</v>
+        <v>0.03283136720297412</v>
       </c>
       <c r="H373">
-        <v>3.256690871466305</v>
+        <v>3.283136720297412</v>
       </c>
     </row>
     <row r="374">

--- a/output/summary_WB_regions_quality_prevalences.xlsx
+++ b/output/summary_WB_regions_quality_prevalences.xlsx
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="G26">
-        <v>0.1999251239701637</v>
+        <v>0.1999251301363954</v>
       </c>
       <c r="H26">
-        <v>19.99251239701637</v>
+        <v>19.99251301363954</v>
       </c>
     </row>
     <row r="27">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="G28">
-        <v>0.1934867094054999</v>
+        <v>0.1934867602224036</v>
       </c>
       <c r="H28">
-        <v>19.34867094054999</v>
+        <v>19.34867602224036</v>
       </c>
     </row>
     <row r="29">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="G30">
-        <v>0.26746047476051</v>
+        <v>0.2674604754531948</v>
       </c>
       <c r="H30">
-        <v>26.746047476051</v>
+        <v>26.74604754531948</v>
       </c>
     </row>
     <row r="31">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.189718567749819</v>
+        <v>0.1897186186205689</v>
       </c>
       <c r="H36">
-        <v>18.9718567749819</v>
+        <v>18.97186186205689</v>
       </c>
     </row>
     <row r="37">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="G37">
-        <v>0.1974926538524295</v>
+        <v>0.1974927046120887</v>
       </c>
       <c r="H37">
-        <v>19.74926538524295</v>
+        <v>19.74927046120887</v>
       </c>
     </row>
     <row r="38">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="G40">
-        <v>0.2755657104196537</v>
+        <v>0.2755657111252798</v>
       </c>
       <c r="H40">
-        <v>27.55657104196537</v>
+        <v>27.55657111252798</v>
       </c>
     </row>
     <row r="41">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="G41">
-        <v>0.2599661981667062</v>
+        <v>0.2599661988474252</v>
       </c>
       <c r="H41">
-        <v>25.99661981667062</v>
+        <v>25.99661988474252</v>
       </c>
     </row>
     <row r="42">
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="G48">
-        <v>0.2005329709355732</v>
+        <v>0.2005329773372695</v>
       </c>
       <c r="H48">
-        <v>20.05329709355732</v>
+        <v>20.05329773372695</v>
       </c>
     </row>
     <row r="49">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="G49">
-        <v>0.1993252643229475</v>
+        <v>0.1993252702568082</v>
       </c>
       <c r="H49">
-        <v>19.93252643229475</v>
+        <v>19.93252702568082</v>
       </c>
     </row>
     <row r="50">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="G50">
-        <v>0.1017995920748739</v>
+        <v>0.1017995951892782</v>
       </c>
       <c r="H50">
-        <v>10.17995920748739</v>
+        <v>10.17995951892782</v>
       </c>
     </row>
     <row r="51">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="G52">
-        <v>0.0956087544497819</v>
+        <v>0.09560878009201318</v>
       </c>
       <c r="H52">
-        <v>9.560875444978191</v>
+        <v>9.560878009201318</v>
       </c>
     </row>
     <row r="53">
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="G54">
-        <v>0.1734393575943255</v>
+        <v>0.1734393579919085</v>
       </c>
       <c r="H54">
-        <v>17.34393575943255</v>
+        <v>17.34393579919085</v>
       </c>
     </row>
     <row r="55">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="G60">
-        <v>0.09241271609510485</v>
+        <v>0.09241274123966112</v>
       </c>
       <c r="H60">
-        <v>9.241271609510484</v>
+        <v>9.241274123966111</v>
       </c>
     </row>
     <row r="61">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="G61">
-        <v>0.09900649085913224</v>
+        <v>0.09900651703044649</v>
       </c>
       <c r="H61">
-        <v>9.900649085913225</v>
+        <v>9.90065170304465</v>
       </c>
     </row>
     <row r="62">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="G64">
-        <v>0.1787057419133499</v>
+        <v>0.1787057423021692</v>
       </c>
       <c r="H64">
-        <v>17.87057419133499</v>
+        <v>17.87057423021692</v>
       </c>
     </row>
     <row r="65">
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="G65">
-        <v>0.1685699444895362</v>
+        <v>0.1685699448952221</v>
       </c>
       <c r="H65">
-        <v>16.85699444895362</v>
+        <v>16.85699448952221</v>
       </c>
     </row>
     <row r="66">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="G72">
-        <v>0.1011200901361545</v>
+        <v>0.1011200933027596</v>
       </c>
       <c r="H72">
-        <v>10.11200901361545</v>
+        <v>10.11200933027596</v>
       </c>
     </row>
     <row r="73">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="G73">
-        <v>0.1024701651244034</v>
+        <v>0.1024701681872929</v>
       </c>
       <c r="H73">
-        <v>10.24701651244034</v>
+        <v>10.24701681872929</v>
       </c>
     </row>
     <row r="74">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="G74">
-        <v>0.06825458730330247</v>
+        <v>0.0717746149844271</v>
       </c>
       <c r="H74">
-        <v>6.825458730330247</v>
+        <v>7.177461498442709</v>
       </c>
     </row>
     <row r="75">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="G75">
-        <v>0.07279644080015522</v>
+        <v>0.07626889343031257</v>
       </c>
       <c r="H75">
-        <v>7.279644080015522</v>
+        <v>7.626889343031257</v>
       </c>
     </row>
     <row r="76">
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="G76">
-        <v>0.01951331141863899</v>
+        <v>0.02365576371796077</v>
       </c>
       <c r="H76">
-        <v>1.951331141863899</v>
+        <v>2.365576371796077</v>
       </c>
     </row>
     <row r="77">
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="G77">
-        <v>0.08677971438863964</v>
+        <v>0.08902703615446936</v>
       </c>
       <c r="H77">
-        <v>8.677971438863965</v>
+        <v>8.902703615446935</v>
       </c>
     </row>
     <row r="78">
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="G78">
-        <v>0.04267690706273979</v>
+        <v>0.0439326297108886</v>
       </c>
       <c r="H78">
-        <v>4.267690706273979</v>
+        <v>4.39326297108886</v>
       </c>
     </row>
     <row r="79">
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="G79">
-        <v>0.03709329159414409</v>
+        <v>0.0424891100749981</v>
       </c>
       <c r="H79">
-        <v>3.709329159414409</v>
+        <v>4.24891100749981</v>
       </c>
     </row>
     <row r="80">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="G80">
-        <v>0.06375806414233076</v>
+        <v>0.06840665737020725</v>
       </c>
       <c r="H80">
-        <v>6.375806414233076</v>
+        <v>6.840665737020725</v>
       </c>
     </row>
     <row r="81">
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="G81">
-        <v>0.1185919228790557</v>
+        <v>0.1208269451347536</v>
       </c>
       <c r="H81">
-        <v>11.85919228790557</v>
+        <v>12.08269451347536</v>
       </c>
     </row>
     <row r="82">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="G82">
-        <v>0.08794124519799029</v>
+        <v>0.09216787333211314</v>
       </c>
       <c r="H82">
-        <v>8.794124519799029</v>
+        <v>9.216787333211315</v>
       </c>
     </row>
     <row r="83">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="G83">
-        <v>0.05799682301970644</v>
+        <v>0.06073228962450041</v>
       </c>
       <c r="H83">
-        <v>5.799682301970644</v>
+        <v>6.073228962450041</v>
       </c>
     </row>
     <row r="84">
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="G84">
-        <v>0.02827417433608785</v>
+        <v>0.03470715845983965</v>
       </c>
       <c r="H84">
-        <v>2.827417433608785</v>
+        <v>3.470715845983965</v>
       </c>
     </row>
     <row r="85">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="G85">
-        <v>0.0101995612039766</v>
+        <v>0.01190692902902969</v>
       </c>
       <c r="H85">
-        <v>1.01995612039766</v>
+        <v>1.190692902902969</v>
       </c>
     </row>
     <row r="86">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="G86">
-        <v>0.1033363768695572</v>
+        <v>0.1061934363467913</v>
       </c>
       <c r="H86">
-        <v>10.33363768695572</v>
+        <v>10.61934363467913</v>
       </c>
     </row>
     <row r="87">
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="G87">
-        <v>0.06976174892012778</v>
+        <v>0.0713823444161258</v>
       </c>
       <c r="H87">
-        <v>6.976174892012778</v>
+        <v>7.13823444161258</v>
       </c>
     </row>
     <row r="88">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="G88">
-        <v>0.05865590836460104</v>
+        <v>0.0603096769735454</v>
       </c>
       <c r="H88">
-        <v>5.865590836460104</v>
+        <v>6.03096769735454</v>
       </c>
     </row>
     <row r="89">
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="G89">
-        <v>0.02790237607007045</v>
+        <v>0.0287900567941227</v>
       </c>
       <c r="H89">
-        <v>2.790237607007044</v>
+        <v>2.87900567941227</v>
       </c>
     </row>
     <row r="90">
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="G90">
-        <v>0.04699553990576575</v>
+        <v>0.05407553836426892</v>
       </c>
       <c r="H90">
-        <v>4.699553990576575</v>
+        <v>5.407553836426892</v>
       </c>
     </row>
     <row r="91">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="G91">
-        <v>0.02726775186183486</v>
+        <v>0.03099243700347237</v>
       </c>
       <c r="H91">
-        <v>2.726775186183486</v>
+        <v>3.099243700347237</v>
       </c>
     </row>
     <row r="92">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="G92">
-        <v>0.0901085123115478</v>
+        <v>0.09581521414751075</v>
       </c>
       <c r="H92">
-        <v>9.010851231154779</v>
+        <v>9.581521414751075</v>
       </c>
     </row>
     <row r="93">
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="G93">
-        <v>0.03868044194519817</v>
+        <v>0.0423220371991987</v>
       </c>
       <c r="H93">
-        <v>3.868044194519817</v>
+        <v>4.23220371991987</v>
       </c>
     </row>
     <row r="94">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="G94">
-        <v>0.1567158727269675</v>
+        <v>0.1594837706292158</v>
       </c>
       <c r="H94">
-        <v>15.67158727269675</v>
+        <v>15.94837706292159</v>
       </c>
     </row>
     <row r="95">
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="G95">
-        <v>0.0801316630972726</v>
+        <v>0.08182910895074867</v>
       </c>
       <c r="H95">
-        <v>8.013166309727261</v>
+        <v>8.182910895074867</v>
       </c>
     </row>
     <row r="96">
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="G96">
-        <v>0.08840589106574606</v>
+        <v>0.09292345970431357</v>
       </c>
       <c r="H96">
-        <v>8.840589106574607</v>
+        <v>9.292345970431356</v>
       </c>
     </row>
     <row r="97">
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="G97">
-        <v>0.04836807860336361</v>
+        <v>0.05090367335833201</v>
       </c>
       <c r="H97">
-        <v>4.836807860336361</v>
+        <v>5.090367335833202</v>
       </c>
     </row>
     <row r="98">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="G98">
-        <v>0.03725649280446817</v>
+        <v>0.03926930999109422</v>
       </c>
       <c r="H98">
-        <v>3.725649280446818</v>
+        <v>3.926930999109421</v>
       </c>
     </row>
     <row r="99">
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="G99">
-        <v>0.03388750155880806</v>
+        <v>0.03611514297722701</v>
       </c>
       <c r="H99">
-        <v>3.388750155880806</v>
+        <v>3.611514297722701</v>
       </c>
     </row>
     <row r="100">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="G100">
-        <v>0.008728377953952095</v>
+        <v>0.01057861853615269</v>
       </c>
       <c r="H100">
-        <v>0.8728377953952096</v>
+        <v>1.057861853615269</v>
       </c>
     </row>
     <row r="101">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="G101">
-        <v>0.05717150888083796</v>
+        <v>0.0584450097125665</v>
       </c>
       <c r="H101">
-        <v>5.717150888083796</v>
+        <v>5.84450097125665</v>
       </c>
     </row>
     <row r="102">
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="G102">
-        <v>0.0275430167485498</v>
+        <v>0.02839315406795614</v>
       </c>
       <c r="H102">
-        <v>2.75430167485498</v>
+        <v>2.839315406795615</v>
       </c>
     </row>
     <row r="103">
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="G103">
-        <v>0.007479596948654875</v>
+        <v>0.009087560827504178</v>
       </c>
       <c r="H103">
-        <v>0.7479596948654875</v>
+        <v>0.9087560827504177</v>
       </c>
     </row>
     <row r="104">
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="G104">
-        <v>0.01953583063011212</v>
+        <v>0.02203008762684973</v>
       </c>
       <c r="H104">
-        <v>1.953583063011212</v>
+        <v>2.203008762684973</v>
       </c>
     </row>
     <row r="105">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="G105">
-        <v>0.1018535061005337</v>
+        <v>0.1037912978546334</v>
       </c>
       <c r="H105">
-        <v>10.18535061005337</v>
+        <v>10.37912978546334</v>
       </c>
     </row>
     <row r="106">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="G106">
-        <v>0.04234815795013871</v>
+        <v>0.045104925556186</v>
       </c>
       <c r="H106">
-        <v>4.234815795013871</v>
+        <v>4.510492555618599</v>
       </c>
     </row>
     <row r="107">
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="G107">
-        <v>0.02561968393144362</v>
+        <v>0.02733025922415892</v>
       </c>
       <c r="H107">
-        <v>2.561968393144362</v>
+        <v>2.733025922415892</v>
       </c>
     </row>
     <row r="108">
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="G108">
-        <v>0.01194028438730371</v>
+        <v>0.01478283529901539</v>
       </c>
       <c r="H108">
-        <v>1.194028438730371</v>
+        <v>1.478283529901539</v>
       </c>
     </row>
     <row r="109">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="G109">
-        <v>0.005313772050973845</v>
+        <v>0.006109078817683722</v>
       </c>
       <c r="H109">
-        <v>0.5313772050973845</v>
+        <v>0.6109078817683722</v>
       </c>
     </row>
     <row r="110">
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="G110">
-        <v>0.06707905998295503</v>
+        <v>0.06870436441541562</v>
       </c>
       <c r="H110">
-        <v>6.707905998295503</v>
+        <v>6.870436441541562</v>
       </c>
     </row>
     <row r="111">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="G111">
-        <v>0.046987912837392</v>
+        <v>0.04789980808974391</v>
       </c>
       <c r="H111">
-        <v>4.698791283739199</v>
+        <v>4.78998080897439</v>
       </c>
     </row>
     <row r="112">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="G112">
-        <v>0.03681499321970169</v>
+        <v>0.03788083636903412</v>
       </c>
       <c r="H112">
-        <v>3.681499321970169</v>
+        <v>3.788083636903413</v>
       </c>
     </row>
     <row r="113">
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="G113">
-        <v>0.0189699463076345</v>
+        <v>0.01962063734067179</v>
       </c>
       <c r="H113">
-        <v>1.89699463076345</v>
+        <v>1.962063734067179</v>
       </c>
     </row>
     <row r="114">
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="G114">
-        <v>0.00924617356803667</v>
+        <v>0.01128431927216694</v>
       </c>
       <c r="H114">
-        <v>0.924617356803667</v>
+        <v>1.128431927216694</v>
       </c>
     </row>
     <row r="115">
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="G115">
-        <v>0.005726705260053935</v>
+        <v>0.006907819752440698</v>
       </c>
       <c r="H115">
-        <v>0.5726705260053935</v>
+        <v>0.6907819752440698</v>
       </c>
     </row>
     <row r="116">
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="G116">
-        <v>0.02858422880109536</v>
+        <v>0.03186607465503481</v>
       </c>
       <c r="H116">
-        <v>2.858422880109536</v>
+        <v>3.186607465503481</v>
       </c>
     </row>
     <row r="117">
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="G117">
-        <v>0.01092450419786477</v>
+        <v>0.01266921584794477</v>
       </c>
       <c r="H117">
-        <v>1.092450419786477</v>
+        <v>1.266921584794477</v>
       </c>
     </row>
     <row r="118">
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="G118">
-        <v>0.1341134733852655</v>
+        <v>0.136509162056313</v>
       </c>
       <c r="H118">
-        <v>13.41134733852655</v>
+        <v>13.6509162056313</v>
       </c>
     </row>
     <row r="119">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="G119">
-        <v>0.06930895792878752</v>
+        <v>0.07078481343416837</v>
       </c>
       <c r="H119">
-        <v>6.930895792878752</v>
+        <v>7.078481343416837</v>
       </c>
     </row>
     <row r="120">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="G120">
-        <v>0.04855240159174905</v>
+        <v>0.05116282570769443</v>
       </c>
       <c r="H120">
-        <v>4.855240159174905</v>
+        <v>5.116282570769443</v>
       </c>
     </row>
     <row r="121">
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="G121">
-        <v>0.02610901614389487</v>
+        <v>0.02753207916180073</v>
       </c>
       <c r="H121">
-        <v>2.610901614389487</v>
+        <v>2.753207916180073</v>
       </c>
     </row>
     <row r="122">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="G122">
-        <v>0.02021555704429582</v>
+        <v>0.02351151365222936</v>
       </c>
       <c r="H122">
-        <v>2.021555704429582</v>
+        <v>2.351151365222936</v>
       </c>
     </row>
     <row r="123">
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="G137">
-        <v>0.02653781486810821</v>
+        <v>0.05410797739246851</v>
       </c>
       <c r="H137">
-        <v>2.653781486810821</v>
+        <v>5.410797739246851</v>
       </c>
     </row>
     <row r="138">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="G138">
-        <v>0.03099952909625187</v>
+        <v>0.06327414434791882</v>
       </c>
       <c r="H138">
-        <v>3.099952909625187</v>
+        <v>6.327414434791883</v>
       </c>
     </row>
     <row r="139">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="G139">
-        <v>0.03139216746998123</v>
+        <v>0.06352199771807732</v>
       </c>
       <c r="H139">
-        <v>3.139216746998123</v>
+        <v>6.352199771807731</v>
       </c>
     </row>
     <row r="140">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="G140">
-        <v>0.02829247208819375</v>
+        <v>0.06202197957505113</v>
       </c>
       <c r="H140">
-        <v>2.829247208819375</v>
+        <v>6.202197957505113</v>
       </c>
     </row>
     <row r="141">
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="G141">
-        <v>0.02383941407212798</v>
+        <v>0.0556613771259922</v>
       </c>
       <c r="H141">
-        <v>2.383941407212798</v>
+        <v>5.56613771259922</v>
       </c>
     </row>
     <row r="142">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="G142">
-        <v>0.02713025119409336</v>
+        <v>0.02842588831860442</v>
       </c>
       <c r="H142">
-        <v>2.713025119409336</v>
+        <v>2.842588831860442</v>
       </c>
     </row>
     <row r="143">
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="G143">
-        <v>0.02130604022887199</v>
+        <v>0.02271459331426909</v>
       </c>
       <c r="H143">
-        <v>2.130604022887199</v>
+        <v>2.271459331426909</v>
       </c>
     </row>
     <row r="144">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="G144">
-        <v>0.004207010377073076</v>
+        <v>0.005016742671822953</v>
       </c>
       <c r="H144">
-        <v>0.4207010377073075</v>
+        <v>0.5016742671822954</v>
       </c>
     </row>
     <row r="145">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="G145">
-        <v>0.04281679429638805</v>
+        <v>0.04362737824502045</v>
       </c>
       <c r="H145">
-        <v>4.281679429638805</v>
+        <v>4.362737824502045</v>
       </c>
     </row>
     <row r="146">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="G146">
-        <v>0.01922360428552519</v>
+        <v>0.01985706865674334</v>
       </c>
       <c r="H146">
-        <v>1.922360428552519</v>
+        <v>1.985706865674334</v>
       </c>
     </row>
     <row r="147">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="G147">
-        <v>0.00200225595833365</v>
+        <v>0.002539472188490489</v>
       </c>
       <c r="H147">
-        <v>0.200225595833365</v>
+        <v>0.2539472188490489</v>
       </c>
     </row>
     <row r="148">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="G148">
-        <v>0.01057164499097501</v>
+        <v>0.01218307941871122</v>
       </c>
       <c r="H148">
-        <v>1.0571644990975</v>
+        <v>1.218307941871122</v>
       </c>
     </row>
     <row r="149">
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="G149">
-        <v>0.09034027244059073</v>
+        <v>0.09209676429057735</v>
       </c>
       <c r="H149">
-        <v>9.034027244059073</v>
+        <v>9.209676429057735</v>
       </c>
     </row>
     <row r="150">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="G150">
-        <v>0.0269784117064889</v>
+        <v>0.02875340823970646</v>
       </c>
       <c r="H150">
-        <v>2.69784117064889</v>
+        <v>2.875340823970646</v>
       </c>
     </row>
     <row r="151">
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="G151">
-        <v>0.01576295577745114</v>
+        <v>0.01681341754496579</v>
       </c>
       <c r="H151">
-        <v>1.576295577745114</v>
+        <v>1.681341754496579</v>
       </c>
     </row>
     <row r="152">
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="G152">
-        <v>0.00560028715462868</v>
+        <v>0.006850856205196139</v>
       </c>
       <c r="H152">
-        <v>0.560028715462868</v>
+        <v>0.6850856205196139</v>
       </c>
     </row>
     <row r="153">
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="G153">
-        <v>0.002725805613533484</v>
+        <v>0.003066880486313039</v>
       </c>
       <c r="H153">
-        <v>0.2725805613533484</v>
+        <v>0.3066880486313039</v>
       </c>
     </row>
     <row r="154">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="G154">
-        <v>0.05083429840704313</v>
+        <v>0.05183850791757347</v>
       </c>
       <c r="H154">
-        <v>5.083429840704313</v>
+        <v>5.183850791757346</v>
       </c>
     </row>
     <row r="155">
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="G155">
-        <v>0.0345759058772373</v>
+        <v>0.03518746945385937</v>
       </c>
       <c r="H155">
-        <v>3.45759058772373</v>
+        <v>3.518746945385937</v>
       </c>
     </row>
     <row r="156">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="G156">
-        <v>0.02607159750921067</v>
+        <v>0.02686224256885786</v>
       </c>
       <c r="H156">
-        <v>2.607159750921067</v>
+        <v>2.686224256885786</v>
       </c>
     </row>
     <row r="157">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="G157">
-        <v>0.01289180130174643</v>
+        <v>0.01337993300111775</v>
       </c>
       <c r="H157">
-        <v>1.289180130174643</v>
+        <v>1.337993300111775</v>
       </c>
     </row>
     <row r="158">
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="G158">
-        <v>0.002374727376448203</v>
+        <v>0.003018840375127131</v>
       </c>
       <c r="H158">
-        <v>0.2374727376448204</v>
+        <v>0.3018840375127131</v>
       </c>
     </row>
     <row r="159">
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="G159">
-        <v>0.001632669920631596</v>
+        <v>0.00206381746685768</v>
       </c>
       <c r="H159">
-        <v>0.1632669920631596</v>
+        <v>0.2063817466857681</v>
       </c>
     </row>
     <row r="160">
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="G160">
-        <v>0.01561775122398257</v>
+        <v>0.01779433134403176</v>
       </c>
       <c r="H160">
-        <v>1.561775122398257</v>
+        <v>1.779433134403176</v>
       </c>
     </row>
     <row r="161">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="G161">
-        <v>0.005769284709839824</v>
+        <v>0.006842872112464779</v>
       </c>
       <c r="H161">
-        <v>0.5769284709839825</v>
+        <v>0.6842872112464778</v>
       </c>
     </row>
     <row r="162">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="G162">
-        <v>0.1200176323416254</v>
+        <v>0.1222179463109025</v>
       </c>
       <c r="H162">
-        <v>12.00176323416254</v>
+        <v>12.22179463109025</v>
       </c>
     </row>
     <row r="163">
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="G163">
-        <v>0.06040111409040257</v>
+        <v>0.06170986864997433</v>
       </c>
       <c r="H163">
-        <v>6.040111409040256</v>
+        <v>6.170986864997433</v>
       </c>
     </row>
     <row r="164">
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="G164">
-        <v>0.03567772413725288</v>
+        <v>0.03736507421033941</v>
       </c>
       <c r="H164">
-        <v>3.567772413725288</v>
+        <v>3.736507421033941</v>
       </c>
     </row>
     <row r="165">
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="G165">
-        <v>0.01869509498532144</v>
+        <v>0.01960416640413155</v>
       </c>
       <c r="H165">
-        <v>1.869509498532145</v>
+        <v>1.960416640413155</v>
       </c>
     </row>
     <row r="166">
@@ -5400,10 +5400,10 @@
         </is>
       </c>
       <c r="G166">
-        <v>0.0302139697005494</v>
+        <v>0.03522357990898254</v>
       </c>
       <c r="H166">
-        <v>3.02139697005494</v>
+        <v>3.522357990898254</v>
       </c>
     </row>
     <row r="167">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="G167">
-        <v>0.05716277496932892</v>
+        <v>0.05716277509163305</v>
       </c>
       <c r="H167">
-        <v>5.716277496932892</v>
+        <v>5.716277509163305</v>
       </c>
     </row>
     <row r="168">
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="G168">
-        <v>0.05463091033551071</v>
+        <v>0.05463091042338429</v>
       </c>
       <c r="H168">
-        <v>5.463091033551072</v>
+        <v>5.463091042338429</v>
       </c>
     </row>
     <row r="169">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="G169">
-        <v>0.03767425561512276</v>
+        <v>0.0376742556759257</v>
       </c>
       <c r="H169">
-        <v>3.767425561512276</v>
+        <v>3.76742556759257</v>
       </c>
     </row>
     <row r="170">
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="G170">
-        <v>0.03789413124388836</v>
+        <v>0.0378941313520877</v>
       </c>
       <c r="H170">
-        <v>3.789413124388836</v>
+        <v>3.789413135208771</v>
       </c>
     </row>
     <row r="171">
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="G171">
-        <v>0.04201532838616029</v>
+        <v>0.04201532857356976</v>
       </c>
       <c r="H171">
-        <v>4.201532838616028</v>
+        <v>4.201532857356976</v>
       </c>
     </row>
     <row r="172">
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="G172">
-        <v>0.0487492730316435</v>
+        <v>0.04874927338675352</v>
       </c>
       <c r="H172">
-        <v>4.87492730316435</v>
+        <v>4.874927338675352</v>
       </c>
     </row>
     <row r="173">
@@ -5596,10 +5596,10 @@
         </is>
       </c>
       <c r="G173">
-        <v>0.05754344105212167</v>
+        <v>0.05754344172049539</v>
       </c>
       <c r="H173">
-        <v>5.754344105212167</v>
+        <v>5.75434417204954</v>
       </c>
     </row>
     <row r="174">
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="G174">
-        <v>0.06733981014976287</v>
+        <v>0.06733981112807021</v>
       </c>
       <c r="H174">
-        <v>6.733981014976287</v>
+        <v>6.733981112807021</v>
       </c>
     </row>
     <row r="175">
@@ -5652,10 +5652,10 @@
         </is>
       </c>
       <c r="G175">
-        <v>0.0342723516420019</v>
+        <v>0.03427235165467395</v>
       </c>
       <c r="H175">
-        <v>3.42723516420019</v>
+        <v>3.427235165467394</v>
       </c>
     </row>
     <row r="176">
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="G176">
-        <v>0.08091808908435445</v>
+        <v>0.08091809049411172</v>
       </c>
       <c r="H176">
-        <v>8.091808908435445</v>
+        <v>8.091809049411172</v>
       </c>
     </row>
     <row r="177">
@@ -5708,10 +5708,10 @@
         </is>
       </c>
       <c r="G177">
-        <v>0.08853124345981242</v>
+        <v>0.0885312456682414</v>
       </c>
       <c r="H177">
-        <v>8.853124345981241</v>
+        <v>8.853124566824141</v>
       </c>
     </row>
     <row r="178">
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="G178">
-        <v>0.1108664012358</v>
+        <v>0.1108664046595919</v>
       </c>
       <c r="H178">
-        <v>11.08664012358</v>
+        <v>11.08664046595919</v>
       </c>
     </row>
     <row r="179">
@@ -5764,10 +5764,10 @@
         </is>
       </c>
       <c r="G179">
-        <v>0.1188119212027272</v>
+        <v>0.1188119260484721</v>
       </c>
       <c r="H179">
-        <v>11.88119212027272</v>
+        <v>11.88119260484721</v>
       </c>
     </row>
     <row r="180">
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="G180">
-        <v>0.1397511460174981</v>
+        <v>0.1397511527840104</v>
       </c>
       <c r="H180">
-        <v>13.97511460174981</v>
+        <v>13.97511527840104</v>
       </c>
     </row>
     <row r="181">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="G181">
-        <v>0.07525134779024739</v>
+        <v>0.1507059976355044</v>
       </c>
       <c r="H181">
-        <v>7.525134779024739</v>
+        <v>15.07059976355044</v>
       </c>
     </row>
     <row r="182">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="G182">
-        <v>0.08934945027494355</v>
+        <v>0.1730813980385594</v>
       </c>
       <c r="H182">
-        <v>8.934945027494354</v>
+        <v>17.30813980385594</v>
       </c>
     </row>
     <row r="183">
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="G183">
-        <v>0.09162645372257629</v>
+        <v>0.1752307178237823</v>
       </c>
       <c r="H183">
-        <v>9.162645372257629</v>
+        <v>17.52307178237823</v>
       </c>
     </row>
     <row r="184">
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="G184">
-        <v>0.09501683810227916</v>
+        <v>0.1849822405648992</v>
       </c>
       <c r="H184">
-        <v>9.501683810227917</v>
+        <v>18.49822405648992</v>
       </c>
     </row>
     <row r="185">
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="G185">
-        <v>0.0911474960974029</v>
+        <v>0.1846391279904773</v>
       </c>
       <c r="H185">
-        <v>9.11474960974029</v>
+        <v>18.46391279904773</v>
       </c>
     </row>
     <row r="186">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="G186">
-        <v>0.05871783639123752</v>
+        <v>0.06189669002686849</v>
       </c>
       <c r="H186">
-        <v>5.871783639123752</v>
+        <v>6.189669002686849</v>
       </c>
     </row>
     <row r="187">
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="G187">
-        <v>0.05638977562872927</v>
+        <v>0.05973551278715122</v>
       </c>
       <c r="H187">
-        <v>5.638977562872928</v>
+        <v>5.973551278715123</v>
       </c>
     </row>
     <row r="188">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="G188">
-        <v>0.01877875404150122</v>
+        <v>0.02243893019813848</v>
       </c>
       <c r="H188">
-        <v>1.877875404150122</v>
+        <v>2.243893019813848</v>
       </c>
     </row>
     <row r="189">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="G189">
-        <v>0.08156243583876231</v>
+        <v>0.0836203756842395</v>
       </c>
       <c r="H189">
-        <v>8.156243583876231</v>
+        <v>8.362037568423949</v>
       </c>
     </row>
     <row r="190">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="G190">
-        <v>0.04190027131581015</v>
+        <v>0.04312226983705394</v>
       </c>
       <c r="H190">
-        <v>4.190027131581015</v>
+        <v>4.312226983705394</v>
       </c>
     </row>
     <row r="191">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="G191">
-        <v>0.01896026205588284</v>
+        <v>0.02228222515152268</v>
       </c>
       <c r="H191">
-        <v>1.896026205588284</v>
+        <v>2.228222515152268</v>
       </c>
     </row>
     <row r="192">
@@ -6123,10 +6123,10 @@
         </is>
       </c>
       <c r="G192">
-        <v>0.04699841423863416</v>
+        <v>0.05107923608951422</v>
       </c>
       <c r="H192">
-        <v>4.699841423863417</v>
+        <v>5.107923608951421</v>
       </c>
     </row>
     <row r="193">
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="G193">
-        <v>0.1253447342219677</v>
+        <v>0.1276607923958629</v>
       </c>
       <c r="H193">
-        <v>12.53447342219677</v>
+        <v>12.7660792395863</v>
       </c>
     </row>
     <row r="194">
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="G194">
-        <v>0.06906927778012494</v>
+        <v>0.0731236844673447</v>
       </c>
       <c r="H194">
-        <v>6.906927778012493</v>
+        <v>7.31236844673447</v>
       </c>
     </row>
     <row r="195">
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="G195">
-        <v>0.04399926991088317</v>
+        <v>0.04665248982818723</v>
       </c>
       <c r="H195">
-        <v>4.399926991088317</v>
+        <v>4.665248982818722</v>
       </c>
     </row>
     <row r="196">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="G196">
-        <v>0.02614313465130089</v>
+        <v>0.03173823494126878</v>
       </c>
       <c r="H196">
-        <v>2.614313465130089</v>
+        <v>3.173823494126878</v>
       </c>
     </row>
     <row r="197">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="G197">
-        <v>0.0109496164175387</v>
+        <v>0.01255275775557716</v>
       </c>
       <c r="H197">
-        <v>1.09496164175387</v>
+        <v>1.255275775557716</v>
       </c>
     </row>
     <row r="198">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="G198">
-        <v>0.09597607541142522</v>
+        <v>0.09859753993178492</v>
       </c>
       <c r="H198">
-        <v>9.597607541142523</v>
+        <v>9.859753993178492</v>
       </c>
     </row>
     <row r="199">
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="G199">
-        <v>0.06674720234554705</v>
+        <v>0.06822591654884771</v>
       </c>
       <c r="H199">
-        <v>6.674720234554705</v>
+        <v>6.822591654884771</v>
       </c>
     </row>
     <row r="200">
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="G200">
-        <v>0.0555218634725187</v>
+        <v>0.05707611644362565</v>
       </c>
       <c r="H200">
-        <v>5.552186347251871</v>
+        <v>5.707611644362565</v>
       </c>
     </row>
     <row r="201">
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="G201">
-        <v>0.02930545192210063</v>
+        <v>0.03022024077646851</v>
       </c>
       <c r="H201">
-        <v>2.930545192210063</v>
+        <v>3.022024077646851</v>
       </c>
     </row>
     <row r="202">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="G202">
-        <v>0.02384749124212585</v>
+        <v>0.02816547485280046</v>
       </c>
       <c r="H202">
-        <v>2.384749124212584</v>
+        <v>2.816547485280046</v>
       </c>
     </row>
     <row r="203">
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="G203">
-        <v>0.01411089219166985</v>
+        <v>0.01644455052694698</v>
       </c>
       <c r="H203">
-        <v>1.411089219166985</v>
+        <v>1.644455052694698</v>
       </c>
     </row>
     <row r="204">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="G204">
-        <v>0.06711295239731975</v>
+        <v>0.07222782993829287</v>
       </c>
       <c r="H204">
-        <v>6.711295239731975</v>
+        <v>7.222782993829287</v>
       </c>
     </row>
     <row r="205">
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="G205">
-        <v>0.02785548409285413</v>
+        <v>0.03095219904124725</v>
       </c>
       <c r="H205">
-        <v>2.785548409285413</v>
+        <v>3.095219904124725</v>
       </c>
     </row>
     <row r="206">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="G206">
-        <v>0.1630077811914998</v>
+        <v>0.1658115017246514</v>
       </c>
       <c r="H206">
-        <v>16.30077811914998</v>
+        <v>16.58115017246514</v>
       </c>
     </row>
     <row r="207">
@@ -6613,10 +6613,10 @@
         </is>
       </c>
       <c r="G207">
-        <v>0.08734944316738595</v>
+        <v>0.08917353707478654</v>
       </c>
       <c r="H207">
-        <v>8.734944316738595</v>
+        <v>8.917353707478654</v>
       </c>
     </row>
     <row r="208">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="G208">
-        <v>0.0759356928054607</v>
+        <v>0.08000033782174015</v>
       </c>
       <c r="H208">
-        <v>7.593569280546069</v>
+        <v>8.000033782174015</v>
       </c>
     </row>
     <row r="209">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="G209">
-        <v>0.04172622853240108</v>
+        <v>0.04403093039079441</v>
       </c>
       <c r="H209">
-        <v>4.172622853240108</v>
+        <v>4.403093039079441</v>
       </c>
     </row>
     <row r="210">
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="G210">
-        <v>0.02373019478943805</v>
+        <v>0.02761298505355356</v>
       </c>
       <c r="H210">
-        <v>2.373019478943805</v>
+        <v>2.761298505355356</v>
       </c>
     </row>
     <row r="211">
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="G211">
-        <v>0.04086304916754228</v>
+        <v>0.04086304919609659</v>
       </c>
       <c r="H211">
-        <v>4.086304916754228</v>
+        <v>4.086304919609659</v>
       </c>
     </row>
     <row r="212">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="G212">
-        <v>0.03825171413691481</v>
+        <v>0.03825171415692859</v>
       </c>
       <c r="H212">
-        <v>3.82517141369148</v>
+        <v>3.825171415692859</v>
       </c>
     </row>
     <row r="213">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="G213">
-        <v>0.0267534146478954</v>
+        <v>0.02675341466231494</v>
       </c>
       <c r="H213">
-        <v>2.67534146478954</v>
+        <v>2.675341466231494</v>
       </c>
     </row>
     <row r="214">
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="G214">
-        <v>0.02573535232072353</v>
+        <v>0.02573535234685875</v>
       </c>
       <c r="H214">
-        <v>2.573535232072353</v>
+        <v>2.573535234685875</v>
       </c>
     </row>
     <row r="215">
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="G215">
-        <v>0.0271430458838086</v>
+        <v>0.02714304592818516</v>
       </c>
       <c r="H215">
-        <v>2.71430458838086</v>
+        <v>2.714304592818516</v>
       </c>
     </row>
     <row r="216">
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="G216">
-        <v>0.03020705621098012</v>
+        <v>0.03020705630446369</v>
       </c>
       <c r="H216">
-        <v>3.020705621098012</v>
+        <v>3.020705630446368</v>
       </c>
     </row>
     <row r="217">
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="G217">
-        <v>0.034671844233398</v>
+        <v>0.03467184441774496</v>
       </c>
       <c r="H217">
-        <v>3.4671844233398</v>
+        <v>3.467184441774497</v>
       </c>
     </row>
     <row r="218">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="G218">
-        <v>0.03951585143027059</v>
+        <v>0.03951585172327406</v>
       </c>
       <c r="H218">
-        <v>3.951585143027059</v>
+        <v>3.951585172327406</v>
       </c>
     </row>
     <row r="219">
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="G219">
-        <v>0.02644451463979858</v>
+        <v>0.02644451464240929</v>
       </c>
       <c r="H219">
-        <v>2.644451463979858</v>
+        <v>2.644451464240929</v>
       </c>
     </row>
     <row r="220">
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="G220">
-        <v>0.04698704158778386</v>
+        <v>0.04698704205335375</v>
       </c>
       <c r="H220">
-        <v>4.698704158778386</v>
+        <v>4.698704205335376</v>
       </c>
     </row>
     <row r="221">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="G221">
-        <v>0.05045832021221739</v>
+        <v>0.05045832099530437</v>
       </c>
       <c r="H221">
-        <v>5.045832021221739</v>
+        <v>5.045832099530437</v>
       </c>
     </row>
     <row r="222">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="G222">
-        <v>0.0632500640078011</v>
+        <v>0.06325006536186599</v>
       </c>
       <c r="H222">
-        <v>6.325006400780111</v>
+        <v>6.325006536186599</v>
       </c>
     </row>
     <row r="223">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="G223">
-        <v>0.06799544926403284</v>
+        <v>0.06799545137146754</v>
       </c>
       <c r="H223">
-        <v>6.799544926403284</v>
+        <v>6.799545137146754</v>
       </c>
     </row>
     <row r="224">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="G224">
-        <v>0.08064768742198059</v>
+        <v>0.08064769078896229</v>
       </c>
       <c r="H224">
-        <v>8.064768742198059</v>
+        <v>8.06476907889623</v>
       </c>
     </row>
     <row r="225">
@@ -7117,10 +7117,10 @@
         </is>
       </c>
       <c r="G225">
-        <v>0.04225632773665726</v>
+        <v>0.08747072666737538</v>
       </c>
       <c r="H225">
-        <v>4.225632773665726</v>
+        <v>8.747072666737537</v>
       </c>
     </row>
     <row r="226">
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="G226">
-        <v>0.0502704802534335</v>
+        <v>0.1025755545306593</v>
       </c>
       <c r="H226">
-        <v>5.027048025343349</v>
+        <v>10.25755545306593</v>
       </c>
     </row>
     <row r="227">
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="G227">
-        <v>0.05159673968511933</v>
+        <v>0.104215764145723</v>
       </c>
       <c r="H227">
-        <v>5.159673968511933</v>
+        <v>10.4215764145723</v>
       </c>
     </row>
     <row r="228">
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="G228">
-        <v>0.05079050933690082</v>
+        <v>0.1076821386111352</v>
       </c>
       <c r="H228">
-        <v>5.079050933690082</v>
+        <v>10.76821386111352</v>
       </c>
     </row>
     <row r="229">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="G229">
-        <v>0.04611579420677507</v>
+        <v>0.1034922818537901</v>
       </c>
       <c r="H229">
-        <v>4.611579420677507</v>
+        <v>10.34922818537901</v>
       </c>
     </row>
     <row r="230">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="G230">
-        <v>0.03725649280446817</v>
+        <v>0.03926930999109422</v>
       </c>
       <c r="H230">
-        <v>3.725649280446818</v>
+        <v>3.926930999109421</v>
       </c>
     </row>
     <row r="231">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="G231">
-        <v>0.03388750155880806</v>
+        <v>0.03611514297722701</v>
       </c>
       <c r="H231">
-        <v>3.388750155880806</v>
+        <v>3.611514297722701</v>
       </c>
     </row>
     <row r="232">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="G232">
-        <v>0.008728377953952095</v>
+        <v>0.01057861853615269</v>
       </c>
       <c r="H232">
-        <v>0.8728377953952096</v>
+        <v>1.057861853615269</v>
       </c>
     </row>
     <row r="233">
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="G233">
-        <v>0.05717150888083796</v>
+        <v>0.0584450097125665</v>
       </c>
       <c r="H233">
-        <v>5.717150888083796</v>
+        <v>5.84450097125665</v>
       </c>
     </row>
     <row r="234">
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="G234">
-        <v>0.0275430167485498</v>
+        <v>0.02839315406795614</v>
       </c>
       <c r="H234">
-        <v>2.75430167485498</v>
+        <v>2.839315406795615</v>
       </c>
     </row>
     <row r="235">
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="G235">
-        <v>0.007479596948654875</v>
+        <v>0.009087560827504178</v>
       </c>
       <c r="H235">
-        <v>0.7479596948654875</v>
+        <v>0.9087560827504177</v>
       </c>
     </row>
     <row r="236">
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="G236">
-        <v>0.01953583063011212</v>
+        <v>0.02203008762684973</v>
       </c>
       <c r="H236">
-        <v>1.953583063011212</v>
+        <v>2.203008762684973</v>
       </c>
     </row>
     <row r="237">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="G237">
-        <v>0.1018535061005337</v>
+        <v>0.1037912978546334</v>
       </c>
       <c r="H237">
-        <v>10.18535061005337</v>
+        <v>10.37912978546334</v>
       </c>
     </row>
     <row r="238">
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="G238">
-        <v>0.04234815795013871</v>
+        <v>0.045104925556186</v>
       </c>
       <c r="H238">
-        <v>4.234815795013871</v>
+        <v>4.510492555618599</v>
       </c>
     </row>
     <row r="239">
@@ -7514,10 +7514,10 @@
         </is>
       </c>
       <c r="G239">
-        <v>0.02561968393144362</v>
+        <v>0.02733025922415892</v>
       </c>
       <c r="H239">
-        <v>2.561968393144362</v>
+        <v>2.733025922415892</v>
       </c>
     </row>
     <row r="240">
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="G240">
-        <v>0.01194028438730371</v>
+        <v>0.01478283529901539</v>
       </c>
       <c r="H240">
-        <v>1.194028438730371</v>
+        <v>1.478283529901539</v>
       </c>
     </row>
     <row r="241">
@@ -7580,10 +7580,10 @@
         </is>
       </c>
       <c r="G241">
-        <v>0.005313772050973845</v>
+        <v>0.006109078817683722</v>
       </c>
       <c r="H241">
-        <v>0.5313772050973845</v>
+        <v>0.6109078817683722</v>
       </c>
     </row>
     <row r="242">
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="G242">
-        <v>0.06707905998295503</v>
+        <v>0.06870436441541562</v>
       </c>
       <c r="H242">
-        <v>6.707905998295503</v>
+        <v>6.870436441541562</v>
       </c>
     </row>
     <row r="243">
@@ -7646,10 +7646,10 @@
         </is>
       </c>
       <c r="G243">
-        <v>0.046987912837392</v>
+        <v>0.04789980808974391</v>
       </c>
       <c r="H243">
-        <v>4.698791283739199</v>
+        <v>4.78998080897439</v>
       </c>
     </row>
     <row r="244">
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="G244">
-        <v>0.03681499321970169</v>
+        <v>0.03788083636903412</v>
       </c>
       <c r="H244">
-        <v>3.681499321970169</v>
+        <v>3.788083636903413</v>
       </c>
     </row>
     <row r="245">
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="G245">
-        <v>0.0189699463076345</v>
+        <v>0.01962063734067179</v>
       </c>
       <c r="H245">
-        <v>1.89699463076345</v>
+        <v>1.962063734067179</v>
       </c>
     </row>
     <row r="246">
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="G246">
-        <v>0.00924617356803667</v>
+        <v>0.01128431927216694</v>
       </c>
       <c r="H246">
-        <v>0.924617356803667</v>
+        <v>1.128431927216694</v>
       </c>
     </row>
     <row r="247">
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="G247">
-        <v>0.005726705260053935</v>
+        <v>0.006907819752440698</v>
       </c>
       <c r="H247">
-        <v>0.5726705260053935</v>
+        <v>0.6907819752440698</v>
       </c>
     </row>
     <row r="248">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="G248">
-        <v>0.02858422880109536</v>
+        <v>0.03186607465503481</v>
       </c>
       <c r="H248">
-        <v>2.858422880109536</v>
+        <v>3.186607465503481</v>
       </c>
     </row>
     <row r="249">
@@ -7844,10 +7844,10 @@
         </is>
       </c>
       <c r="G249">
-        <v>0.01092450419786477</v>
+        <v>0.01266921584794477</v>
       </c>
       <c r="H249">
-        <v>1.092450419786477</v>
+        <v>1.266921584794477</v>
       </c>
     </row>
     <row r="250">
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="G250">
-        <v>0.1341134733852655</v>
+        <v>0.136509162056313</v>
       </c>
       <c r="H250">
-        <v>13.41134733852655</v>
+        <v>13.6509162056313</v>
       </c>
     </row>
     <row r="251">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="G251">
-        <v>0.06930895792878752</v>
+        <v>0.07078481343416837</v>
       </c>
       <c r="H251">
-        <v>6.930895792878752</v>
+        <v>7.078481343416837</v>
       </c>
     </row>
     <row r="252">
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="G252">
-        <v>0.04855240159174905</v>
+        <v>0.05116282570769443</v>
       </c>
       <c r="H252">
-        <v>4.855240159174905</v>
+        <v>5.116282570769443</v>
       </c>
     </row>
     <row r="253">
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="G253">
-        <v>0.02610901614389487</v>
+        <v>0.02753207916180073</v>
       </c>
       <c r="H253">
-        <v>2.610901614389487</v>
+        <v>2.753207916180073</v>
       </c>
     </row>
     <row r="254">
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="G254">
-        <v>0.0913084243531764</v>
+        <v>0.09510277064480635</v>
       </c>
       <c r="H254">
-        <v>9.130842435317641</v>
+        <v>9.510277064480634</v>
       </c>
     </row>
     <row r="255">
@@ -8017,10 +8017,10 @@
         </is>
       </c>
       <c r="G255">
-        <v>0.07362617179275245</v>
+        <v>0.07711984082259096</v>
       </c>
       <c r="H255">
-        <v>7.362617179275246</v>
+        <v>7.711984082259097</v>
       </c>
     </row>
     <row r="256">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="G256">
-        <v>0.01951879683630452</v>
+        <v>0.02366166004455503</v>
       </c>
       <c r="H256">
-        <v>1.951879683630452</v>
+        <v>2.366166004455503</v>
       </c>
     </row>
     <row r="257">
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="G257">
-        <v>0.08707326035626158</v>
+        <v>0.08932352297983433</v>
       </c>
       <c r="H257">
-        <v>8.707326035626158</v>
+        <v>8.932352297983433</v>
       </c>
     </row>
     <row r="258">
@@ -8101,10 +8101,10 @@
         </is>
       </c>
       <c r="G258">
-        <v>0.05072446781729328</v>
+        <v>0.05212334441438046</v>
       </c>
       <c r="H258">
-        <v>5.072446781729328</v>
+        <v>5.212334441438046</v>
       </c>
     </row>
     <row r="259">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="G259">
-        <v>0.03709329159414409</v>
+        <v>0.0424891100749981</v>
       </c>
       <c r="H259">
-        <v>3.709329159414409</v>
+        <v>4.24891100749981</v>
       </c>
     </row>
     <row r="260">
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="G260">
-        <v>0.1467807881028241</v>
+        <v>0.1523374697179191</v>
       </c>
       <c r="H260">
-        <v>14.67807881028241</v>
+        <v>15.23374697179191</v>
       </c>
     </row>
     <row r="261">
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="G261">
-        <v>0.1344883408232813</v>
+        <v>0.1370038578038349</v>
       </c>
       <c r="H261">
-        <v>13.44883408232813</v>
+        <v>13.7003857803835</v>
       </c>
     </row>
     <row r="262">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="G262">
-        <v>0.08896325756343239</v>
+        <v>0.09321079022223203</v>
       </c>
       <c r="H262">
-        <v>8.89632575634324</v>
+        <v>9.321079022223202</v>
       </c>
     </row>
     <row r="263">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="G263">
-        <v>0.05863865519567614</v>
+        <v>0.06139564296677212</v>
       </c>
       <c r="H263">
-        <v>5.863865519567614</v>
+        <v>6.139564296677212</v>
       </c>
     </row>
     <row r="264">
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="G264">
-        <v>0.02828273766013877</v>
+        <v>0.03471631948245611</v>
       </c>
       <c r="H264">
-        <v>2.828273766013877</v>
+        <v>3.471631948245611</v>
       </c>
     </row>
     <row r="265">
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="G265">
-        <v>0.01020177447236553</v>
+        <v>0.01190935462864601</v>
       </c>
       <c r="H265">
-        <v>1.020177447236553</v>
+        <v>1.190935462864601</v>
       </c>
     </row>
     <row r="266">
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="G266">
-        <v>0.1036659422475905</v>
+        <v>0.1065263822249459</v>
       </c>
       <c r="H266">
-        <v>10.36659422475905</v>
+        <v>10.65263822249459</v>
       </c>
     </row>
     <row r="267">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="G267">
-        <v>0.0700182719017895</v>
+        <v>0.07164135636380316</v>
       </c>
       <c r="H267">
-        <v>7.00182719017895</v>
+        <v>7.164135636380315</v>
       </c>
     </row>
     <row r="268">
@@ -8416,10 +8416,10 @@
         </is>
       </c>
       <c r="G268">
-        <v>0.06874659717791619</v>
+        <v>0.07056343254651996</v>
       </c>
       <c r="H268">
-        <v>6.874659717791618</v>
+        <v>7.056343254651996</v>
       </c>
     </row>
     <row r="269">
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="G269">
-        <v>0.03406081633105155</v>
+        <v>0.03507323918758444</v>
       </c>
       <c r="H269">
-        <v>3.406081633105155</v>
+        <v>3.507323918758444</v>
       </c>
     </row>
     <row r="270">
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="G270">
-        <v>0.04699553990576575</v>
+        <v>0.05407553836426892</v>
       </c>
       <c r="H270">
-        <v>4.699553990576575</v>
+        <v>5.407553836426892</v>
       </c>
     </row>
     <row r="271">
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="G271">
-        <v>0.02726775186183486</v>
+        <v>0.03099243700347237</v>
       </c>
       <c r="H271">
-        <v>2.726775186183486</v>
+        <v>3.099243700347237</v>
       </c>
     </row>
     <row r="272">
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="G272">
-        <v>0.1990722269711983</v>
+        <v>0.205387111029732</v>
       </c>
       <c r="H272">
-        <v>19.90722269711983</v>
+        <v>20.5387111029732</v>
       </c>
     </row>
     <row r="273">
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="G273">
-        <v>0.09701522283940414</v>
+        <v>0.1018503260470506</v>
       </c>
       <c r="H273">
-        <v>9.701522283940415</v>
+        <v>10.18503260470506</v>
       </c>
     </row>
     <row r="274">
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="G274">
-        <v>0.1776508659365985</v>
+        <v>0.1807414995682882</v>
       </c>
       <c r="H274">
-        <v>17.76508659365984</v>
+        <v>18.07414995682882</v>
       </c>
     </row>
     <row r="275">
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="G275">
-        <v>0.0909450580491105</v>
+        <v>0.09288038499437737</v>
       </c>
       <c r="H275">
-        <v>9.09450580491105</v>
+        <v>9.288038499437738</v>
       </c>
     </row>
     <row r="276">
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="G276">
-        <v>0.1181513743821153</v>
+        <v>0.1228755118057232</v>
       </c>
       <c r="H276">
-        <v>11.81513743821153</v>
+        <v>12.28755118057232</v>
       </c>
     </row>
     <row r="277">
@@ -8703,10 +8703,10 @@
         </is>
       </c>
       <c r="G277">
-        <v>0.06481819992028583</v>
+        <v>0.06769497285521457</v>
       </c>
       <c r="H277">
-        <v>6.481819992028583</v>
+        <v>6.769497285521457</v>
       </c>
     </row>
     <row r="278">
@@ -8726,10 +8726,10 @@
         </is>
       </c>
       <c r="G278">
-        <v>0.04750778707163263</v>
+        <v>0.05000815449515845</v>
       </c>
       <c r="H278">
-        <v>4.750778707163263</v>
+        <v>5.000815449515845</v>
       </c>
     </row>
     <row r="279">
@@ -8754,10 +8754,10 @@
         </is>
       </c>
       <c r="G279">
-        <v>0.0343557309636072</v>
+        <v>0.0366107443922852</v>
       </c>
       <c r="H279">
-        <v>3.43557309636072</v>
+        <v>3.66107443922852</v>
       </c>
     </row>
     <row r="280">
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="G280">
-        <v>0.008730930299107013</v>
+        <v>0.01058144073031984</v>
       </c>
       <c r="H280">
-        <v>0.8730930299107013</v>
+        <v>1.058144073031984</v>
       </c>
     </row>
     <row r="281">
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="G281">
-        <v>0.05756918221863314</v>
+        <v>0.05884599382244876</v>
       </c>
       <c r="H281">
-        <v>5.756918221863313</v>
+        <v>5.884599382244876</v>
       </c>
     </row>
     <row r="282">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="G282">
-        <v>0.03403666033504212</v>
+        <v>0.0350152180466269</v>
       </c>
       <c r="H282">
-        <v>3.403666033504212</v>
+        <v>3.501521804662691</v>
       </c>
     </row>
     <row r="283">
@@ -8866,10 +8866,10 @@
         </is>
       </c>
       <c r="G283">
-        <v>0.007479596948654875</v>
+        <v>0.009087560827504178</v>
       </c>
       <c r="H283">
-        <v>0.7479596948654875</v>
+        <v>0.9087560827504177</v>
       </c>
     </row>
     <row r="284">
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="G284">
-        <v>0.05282520542482209</v>
+        <v>0.05717005400154073</v>
       </c>
       <c r="H284">
-        <v>5.282520542482209</v>
+        <v>5.717005400154073</v>
       </c>
     </row>
     <row r="285">
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="G285">
-        <v>0.1134874232142641</v>
+        <v>0.1155981044006074</v>
       </c>
       <c r="H285">
-        <v>11.34874232142641</v>
+        <v>11.55981044006074</v>
       </c>
     </row>
     <row r="286">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="G286">
-        <v>0.04295726567883017</v>
+        <v>0.04574557554043487</v>
       </c>
       <c r="H286">
-        <v>4.295726567883017</v>
+        <v>4.574557554043487</v>
       </c>
     </row>
     <row r="287">
@@ -8988,10 +8988,10 @@
         </is>
       </c>
       <c r="G287">
-        <v>0.02595024596911234</v>
+        <v>0.02768411807673611</v>
       </c>
       <c r="H287">
-        <v>2.595024596911234</v>
+        <v>2.768411807673611</v>
       </c>
     </row>
     <row r="288">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="G288">
-        <v>0.01194438878145985</v>
+        <v>0.01478735717325686</v>
       </c>
       <c r="H288">
-        <v>1.194438878145985</v>
+        <v>1.478735717325687</v>
       </c>
     </row>
     <row r="289">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="G289">
-        <v>0.005314674399221534</v>
+        <v>0.00611009406705488</v>
       </c>
       <c r="H289">
-        <v>0.5314674399221534</v>
+        <v>0.611009406705488</v>
       </c>
     </row>
     <row r="290">
@@ -9087,10 +9087,10 @@
         </is>
       </c>
       <c r="G290">
-        <v>0.06751413719402284</v>
+        <v>0.0691431802199188</v>
       </c>
       <c r="H290">
-        <v>6.751413719402284</v>
+        <v>6.91431802199188</v>
       </c>
     </row>
     <row r="291">
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="G291">
-        <v>0.04734714015235641</v>
+        <v>0.04826190643545619</v>
       </c>
       <c r="H291">
-        <v>4.734714015235641</v>
+        <v>4.826190643545619</v>
       </c>
     </row>
     <row r="292">
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="G292">
-        <v>0.0450219555376129</v>
+        <v>0.04623672692453614</v>
       </c>
       <c r="H292">
-        <v>4.50219555376129</v>
+        <v>4.623672692453614</v>
       </c>
     </row>
     <row r="293">
@@ -9186,10 +9186,10 @@
         </is>
       </c>
       <c r="G293">
-        <v>0.02387941825414331</v>
+        <v>0.02463956768092666</v>
       </c>
       <c r="H293">
-        <v>2.387941825414331</v>
+        <v>2.463956768092666</v>
       </c>
     </row>
     <row r="294">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="G294">
-        <v>0.00924617356803667</v>
+        <v>0.01128431927216694</v>
       </c>
       <c r="H294">
-        <v>0.924617356803667</v>
+        <v>1.128431927216694</v>
       </c>
     </row>
     <row r="295">
@@ -9252,10 +9252,10 @@
         </is>
       </c>
       <c r="G295">
-        <v>0.005726705260053935</v>
+        <v>0.006907819752440698</v>
       </c>
       <c r="H295">
-        <v>0.5726705260053935</v>
+        <v>0.6907819752440698</v>
       </c>
     </row>
     <row r="296">
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="G296">
-        <v>0.07520741449204843</v>
+        <v>0.08061129101199442</v>
       </c>
       <c r="H296">
-        <v>7.520741449204843</v>
+        <v>8.061129101199443</v>
       </c>
     </row>
     <row r="297">
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="G297">
-        <v>0.03152414142315379</v>
+        <v>0.03486111709820822</v>
       </c>
       <c r="H297">
-        <v>3.152414142315379</v>
+        <v>3.486111709820822</v>
       </c>
     </row>
     <row r="298">
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="G298">
-        <v>0.1486211886445423</v>
+        <v>0.1512011814318362</v>
       </c>
       <c r="H298">
-        <v>14.86211886445423</v>
+        <v>15.12011814318362</v>
       </c>
     </row>
     <row r="299">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="G299">
-        <v>0.07804372572354543</v>
+        <v>0.07968095528267878</v>
       </c>
       <c r="H299">
-        <v>7.804372572354542</v>
+        <v>7.968095528267878</v>
       </c>
     </row>
     <row r="300">
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="G300">
-        <v>0.06237962804588216</v>
+        <v>0.06553790130718659</v>
       </c>
       <c r="H300">
-        <v>6.237962804588216</v>
+        <v>6.553790130718659</v>
       </c>
     </row>
     <row r="301">
@@ -9440,10 +9440,10 @@
         </is>
       </c>
       <c r="G301">
-        <v>0.03283136720297412</v>
+        <v>0.03468247389771719</v>
       </c>
       <c r="H301">
-        <v>3.283136720297412</v>
+        <v>3.468247389771719</v>
       </c>
     </row>
     <row r="302">
@@ -9463,10 +9463,10 @@
         </is>
       </c>
       <c r="G302">
-        <v>0.0336599775919482</v>
+        <v>0.03539993800745347</v>
       </c>
       <c r="H302">
-        <v>3.36599775919482</v>
+        <v>3.539993800745347</v>
       </c>
     </row>
     <row r="303">
@@ -9491,10 +9491,10 @@
         </is>
       </c>
       <c r="G303">
-        <v>0.02152074427822405</v>
+        <v>0.02295392674371695</v>
       </c>
       <c r="H303">
-        <v>2.152074427822405</v>
+        <v>2.295392674371695</v>
       </c>
     </row>
     <row r="304">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="G304">
-        <v>0.004208681453276632</v>
+        <v>0.005018618144605364</v>
       </c>
       <c r="H304">
-        <v>0.4208681453276632</v>
+        <v>0.5018618144605363</v>
       </c>
     </row>
     <row r="305">
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="G305">
-        <v>0.04317302692724207</v>
+        <v>0.04398679978091349</v>
       </c>
       <c r="H305">
-        <v>4.317302692724208</v>
+        <v>4.39867997809135</v>
       </c>
     </row>
     <row r="306">
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="G306">
-        <v>0.0238363114122485</v>
+        <v>0.02457589491503455</v>
       </c>
       <c r="H306">
-        <v>2.38363114122485</v>
+        <v>2.457589491503455</v>
       </c>
     </row>
     <row r="307">
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="G307">
-        <v>0.00200225595833365</v>
+        <v>0.002539472188490489</v>
       </c>
       <c r="H307">
-        <v>0.200225595833365</v>
+        <v>0.2539472188490489</v>
       </c>
     </row>
     <row r="308">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="G308">
-        <v>0.03017396219004481</v>
+        <v>0.03347663977370036</v>
       </c>
       <c r="H308">
-        <v>3.017396219004481</v>
+        <v>3.347663977370036</v>
       </c>
     </row>
     <row r="309">
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="G309">
-        <v>0.1003973229077323</v>
+        <v>0.1023086166186901</v>
       </c>
       <c r="H309">
-        <v>10.03973229077323</v>
+        <v>10.23086166186901</v>
       </c>
     </row>
     <row r="310">
@@ -9692,10 +9692,10 @@
         </is>
       </c>
       <c r="G310">
-        <v>0.02726940398476657</v>
+        <v>0.02907590948755637</v>
       </c>
       <c r="H310">
-        <v>2.726940398476657</v>
+        <v>2.907590948755638</v>
       </c>
     </row>
     <row r="311">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="G311">
-        <v>0.01590311039060131</v>
+        <v>0.01697147875117118</v>
       </c>
       <c r="H311">
-        <v>1.590311039060131</v>
+        <v>1.697147875117118</v>
       </c>
     </row>
     <row r="312">
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="G312">
-        <v>0.005603008959978933</v>
+        <v>0.006853901646949125</v>
       </c>
       <c r="H312">
-        <v>0.5603008959978932</v>
+        <v>0.6853901646949125</v>
       </c>
     </row>
     <row r="313">
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="G313">
-        <v>0.002726359650364568</v>
+        <v>0.003067512154820286</v>
       </c>
       <c r="H313">
-        <v>0.2726359650364568</v>
+        <v>0.3067512154820287</v>
       </c>
     </row>
     <row r="314">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="G314">
-        <v>0.05122787150397955</v>
+        <v>0.05223570890374933</v>
       </c>
       <c r="H314">
-        <v>5.122787150397955</v>
+        <v>5.223570890374933</v>
       </c>
     </row>
     <row r="315">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="G315">
-        <v>0.03489375765910677</v>
+        <v>0.03550805892555634</v>
       </c>
       <c r="H315">
-        <v>3.489375765910677</v>
+        <v>3.550805892555633</v>
       </c>
     </row>
     <row r="316">
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="G316">
-        <v>0.03208302916585584</v>
+        <v>0.03299962737157226</v>
       </c>
       <c r="H316">
-        <v>3.208302916585584</v>
+        <v>3.299962737157226</v>
       </c>
     </row>
     <row r="317">
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="G317">
-        <v>0.0162112174068882</v>
+        <v>0.01678712927806239</v>
       </c>
       <c r="H317">
-        <v>1.62112174068882</v>
+        <v>1.678712927806239</v>
       </c>
     </row>
     <row r="318">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="G318">
-        <v>0.002374727376448203</v>
+        <v>0.003018840375127131</v>
       </c>
       <c r="H318">
-        <v>0.2374727376448204</v>
+        <v>0.3018840375127131</v>
       </c>
     </row>
     <row r="319">
@@ -9989,10 +9989,10 @@
         </is>
       </c>
       <c r="G319">
-        <v>0.001632669920631596</v>
+        <v>0.00206381746685768</v>
       </c>
       <c r="H319">
-        <v>0.1632669920631596</v>
+        <v>0.2063817466857681</v>
       </c>
     </row>
     <row r="320">
@@ -10022,10 +10022,10 @@
         </is>
       </c>
       <c r="G320">
-        <v>0.04380848933467273</v>
+        <v>0.04805882854052436</v>
       </c>
       <c r="H320">
-        <v>4.380848933467274</v>
+        <v>4.805882854052436</v>
       </c>
     </row>
     <row r="321">
@@ -10055,10 +10055,10 @@
         </is>
       </c>
       <c r="G321">
-        <v>0.0171980341005573</v>
+        <v>0.01959882569048938</v>
       </c>
       <c r="H321">
-        <v>1.71980341005573</v>
+        <v>1.959882569048938</v>
       </c>
     </row>
     <row r="322">
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="G322">
-        <v>0.1323639937523842</v>
+        <v>0.1347272457918911</v>
       </c>
       <c r="H322">
-        <v>13.23639937523842</v>
+        <v>13.47272457918911</v>
       </c>
     </row>
     <row r="323">
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="G323">
-        <v>0.06814865848684466</v>
+        <v>0.06960400692466305</v>
       </c>
       <c r="H323">
-        <v>6.814865848684466</v>
+        <v>6.960400692466305</v>
       </c>
     </row>
     <row r="324">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="G324">
-        <v>0.04459912215554464</v>
+        <v>0.04681844436647129</v>
       </c>
       <c r="H324">
-        <v>4.459912215554464</v>
+        <v>4.681844436647129</v>
       </c>
     </row>
     <row r="325">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="G325">
-        <v>0.02286457715045045</v>
+        <v>0.02413147474940329</v>
       </c>
       <c r="H325">
-        <v>2.286457715045045</v>
+        <v>2.413147474940329</v>
       </c>
     </row>
     <row r="326">
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="G326">
-        <v>0.07771601800788747</v>
+        <v>0.08125927722931438</v>
       </c>
       <c r="H326">
-        <v>7.771601800788747</v>
+        <v>8.125927722931438</v>
       </c>
     </row>
     <row r="327">
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="G327">
-        <v>0.05725253111171315</v>
+        <v>0.06061280925320186</v>
       </c>
       <c r="H327">
-        <v>5.725253111171315</v>
+        <v>6.061280925320186</v>
       </c>
     </row>
     <row r="328">
@@ -10256,10 +10256,10 @@
         </is>
       </c>
       <c r="G328">
-        <v>0.01878373620974255</v>
+        <v>0.02244430496405561</v>
       </c>
       <c r="H328">
-        <v>1.878373620974255</v>
+        <v>2.244430496405561</v>
       </c>
     </row>
     <row r="329">
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="G329">
-        <v>0.0820436746313319</v>
+        <v>0.08410508472347683</v>
       </c>
       <c r="H329">
-        <v>8.20436746313319</v>
+        <v>8.410508472347683</v>
       </c>
     </row>
     <row r="330">
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="G330">
-        <v>0.05114473509538969</v>
+        <v>0.05251825047528564</v>
       </c>
       <c r="H330">
-        <v>5.11447350953897</v>
+        <v>5.251825047528564</v>
       </c>
     </row>
     <row r="331">
@@ -10340,10 +10340,10 @@
         </is>
       </c>
       <c r="G331">
-        <v>0.01896026205588284</v>
+        <v>0.02228222515152268</v>
       </c>
       <c r="H331">
-        <v>1.896026205588284</v>
+        <v>2.228222515152268</v>
       </c>
     </row>
     <row r="332">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="G332">
-        <v>0.1133345417062603</v>
+        <v>0.1187402563551095</v>
       </c>
       <c r="H332">
-        <v>11.33345417062603</v>
+        <v>11.87402563551095</v>
       </c>
     </row>
     <row r="333">
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="G333">
-        <v>0.1403463143588518</v>
+        <v>0.1428791103285402</v>
       </c>
       <c r="H333">
-        <v>14.03463143588518</v>
+        <v>14.28791103285402</v>
       </c>
     </row>
     <row r="334">
@@ -10429,10 +10429,10 @@
         </is>
       </c>
       <c r="G334">
-        <v>0.07012947919815625</v>
+        <v>0.07419626449985138</v>
       </c>
       <c r="H334">
-        <v>7.012947919815625</v>
+        <v>7.419626449985138</v>
       </c>
     </row>
     <row r="335">
@@ -10462,10 +10462,10 @@
         </is>
       </c>
       <c r="G335">
-        <v>0.0446690797278653</v>
+        <v>0.04733895371123223</v>
       </c>
       <c r="H335">
-        <v>4.46690797278653</v>
+        <v>4.733895371123223</v>
       </c>
     </row>
     <row r="336">
@@ -10495,10 +10495,10 @@
         </is>
       </c>
       <c r="G336">
-        <v>0.02615094604227567</v>
+        <v>0.03174662300093235</v>
       </c>
       <c r="H336">
-        <v>2.615094604227568</v>
+        <v>3.174662300093235</v>
       </c>
     </row>
     <row r="337">
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="G337">
-        <v>0.01095159081427515</v>
+        <v>0.01255492906248094</v>
       </c>
       <c r="H337">
-        <v>1.095159081427515</v>
+        <v>1.255492906248094</v>
       </c>
     </row>
     <row r="338">
@@ -10561,10 +10561,10 @@
         </is>
       </c>
       <c r="G338">
-        <v>0.09649297419004679</v>
+        <v>0.09911829465307193</v>
       </c>
       <c r="H338">
-        <v>9.649297419004679</v>
+        <v>9.911829465307193</v>
       </c>
     </row>
     <row r="339">
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="G339">
-        <v>0.06719178759082467</v>
+        <v>0.06867357559850423</v>
       </c>
       <c r="H339">
-        <v>6.719178759082467</v>
+        <v>6.867357559850423</v>
       </c>
     </row>
     <row r="340">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="G340">
-        <v>0.06678801549198317</v>
+        <v>0.06851290048831299</v>
       </c>
       <c r="H340">
-        <v>6.678801549198317</v>
+        <v>6.851290048831299</v>
       </c>
     </row>
     <row r="341">
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="G341">
-        <v>0.03668061892940835</v>
+        <v>0.03772925034504314</v>
       </c>
       <c r="H341">
-        <v>3.668061892940835</v>
+        <v>3.772925034504314</v>
       </c>
     </row>
     <row r="342">
@@ -10693,10 +10693,10 @@
         </is>
       </c>
       <c r="G342">
-        <v>0.02384749124212585</v>
+        <v>0.02816547485280046</v>
       </c>
       <c r="H342">
-        <v>2.384749124212584</v>
+        <v>2.816547485280046</v>
       </c>
     </row>
     <row r="343">
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="G343">
-        <v>0.01411089219166985</v>
+        <v>0.01644455052694698</v>
       </c>
       <c r="H343">
-        <v>1.411089219166985</v>
+        <v>1.644455052694698</v>
       </c>
     </row>
     <row r="344">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="G344">
-        <v>0.1558150763613848</v>
+        <v>0.1621263507719552</v>
       </c>
       <c r="H344">
-        <v>15.58150763613848</v>
+        <v>16.21263507719552</v>
       </c>
     </row>
     <row r="345">
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="G345">
-        <v>0.07290597700131868</v>
+        <v>0.07744987383835925</v>
       </c>
       <c r="H345">
-        <v>7.290597700131868</v>
+        <v>7.744987383835925</v>
       </c>
     </row>
     <row r="346">
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="G346">
-        <v>0.1820193721886232</v>
+        <v>0.1850593805423867</v>
       </c>
       <c r="H346">
-        <v>18.20193721886232</v>
+        <v>18.50593805423867</v>
       </c>
     </row>
     <row r="347">
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="G347">
-        <v>0.09830563818473599</v>
+        <v>0.1003267474028186</v>
       </c>
       <c r="H347">
-        <v>9.8305638184736</v>
+        <v>10.03267474028186</v>
       </c>
     </row>
     <row r="348">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="G348">
-        <v>0.1007015180208867</v>
+        <v>0.1050976306781324</v>
       </c>
       <c r="H348">
-        <v>10.07015180208867</v>
+        <v>10.50976306781324</v>
       </c>
     </row>
     <row r="349">
@@ -10914,10 +10914,10 @@
         </is>
       </c>
       <c r="G349">
-        <v>0.05503255537095115</v>
+        <v>0.0577341679440459</v>
       </c>
       <c r="H349">
-        <v>5.503255537095115</v>
+        <v>5.77341679440459</v>
       </c>
     </row>
     <row r="350">
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="G350">
-        <v>0.04750778707163263</v>
+        <v>0.05000815449515845</v>
       </c>
       <c r="H350">
-        <v>4.750778707163263</v>
+        <v>5.000815449515845</v>
       </c>
     </row>
     <row r="351">
@@ -10965,10 +10965,10 @@
         </is>
       </c>
       <c r="G351">
-        <v>0.0343557309636072</v>
+        <v>0.0366107443922852</v>
       </c>
       <c r="H351">
-        <v>3.43557309636072</v>
+        <v>3.66107443922852</v>
       </c>
     </row>
     <row r="352">
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="G352">
-        <v>0.008730930299107013</v>
+        <v>0.01058144073031984</v>
       </c>
       <c r="H352">
-        <v>0.8730930299107013</v>
+        <v>1.058144073031984</v>
       </c>
     </row>
     <row r="353">
@@ -11021,10 +11021,10 @@
         </is>
       </c>
       <c r="G353">
-        <v>0.05756918221863314</v>
+        <v>0.05884599382244876</v>
       </c>
       <c r="H353">
-        <v>5.756918221863313</v>
+        <v>5.884599382244876</v>
       </c>
     </row>
     <row r="354">
@@ -11049,10 +11049,10 @@
         </is>
       </c>
       <c r="G354">
-        <v>0.03403666033504212</v>
+        <v>0.0350152180466269</v>
       </c>
       <c r="H354">
-        <v>3.403666033504212</v>
+        <v>3.501521804662691</v>
       </c>
     </row>
     <row r="355">
@@ -11077,10 +11077,10 @@
         </is>
       </c>
       <c r="G355">
-        <v>0.007479596948654875</v>
+        <v>0.009087560827504178</v>
       </c>
       <c r="H355">
-        <v>0.7479596948654875</v>
+        <v>0.9087560827504177</v>
       </c>
     </row>
     <row r="356">
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="G356">
-        <v>0.05282520542482209</v>
+        <v>0.05717005400154073</v>
       </c>
       <c r="H356">
-        <v>5.282520542482209</v>
+        <v>5.717005400154073</v>
       </c>
     </row>
     <row r="357">
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="G357">
-        <v>0.1134874232142641</v>
+        <v>0.1155981044006074</v>
       </c>
       <c r="H357">
-        <v>11.34874232142641</v>
+        <v>11.55981044006074</v>
       </c>
     </row>
     <row r="358">
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="G358">
-        <v>0.04295726567883017</v>
+        <v>0.04574557554043487</v>
       </c>
       <c r="H358">
-        <v>4.295726567883017</v>
+        <v>4.574557554043487</v>
       </c>
     </row>
     <row r="359">
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="G359">
-        <v>0.02595024596911234</v>
+        <v>0.02768411807673611</v>
       </c>
       <c r="H359">
-        <v>2.595024596911234</v>
+        <v>2.768411807673611</v>
       </c>
     </row>
     <row r="360">
@@ -11232,10 +11232,10 @@
         </is>
       </c>
       <c r="G360">
-        <v>0.01194438878145985</v>
+        <v>0.01478735717325686</v>
       </c>
       <c r="H360">
-        <v>1.194438878145985</v>
+        <v>1.478735717325687</v>
       </c>
     </row>
     <row r="361">
@@ -11265,10 +11265,10 @@
         </is>
       </c>
       <c r="G361">
-        <v>0.005314674399221534</v>
+        <v>0.00611009406705488</v>
       </c>
       <c r="H361">
-        <v>0.5314674399221534</v>
+        <v>0.611009406705488</v>
       </c>
     </row>
     <row r="362">
@@ -11298,10 +11298,10 @@
         </is>
       </c>
       <c r="G362">
-        <v>0.06751413719402284</v>
+        <v>0.0691431802199188</v>
       </c>
       <c r="H362">
-        <v>6.751413719402284</v>
+        <v>6.91431802199188</v>
       </c>
     </row>
     <row r="363">
@@ -11331,10 +11331,10 @@
         </is>
       </c>
       <c r="G363">
-        <v>0.04734714015235641</v>
+        <v>0.04826190643545619</v>
       </c>
       <c r="H363">
-        <v>4.734714015235641</v>
+        <v>4.826190643545619</v>
       </c>
     </row>
     <row r="364">
@@ -11364,10 +11364,10 @@
         </is>
       </c>
       <c r="G364">
-        <v>0.0450219555376129</v>
+        <v>0.04623672692453614</v>
       </c>
       <c r="H364">
-        <v>4.50219555376129</v>
+        <v>4.623672692453614</v>
       </c>
     </row>
     <row r="365">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="G365">
-        <v>0.02387941825414331</v>
+        <v>0.02463956768092666</v>
       </c>
       <c r="H365">
-        <v>2.387941825414331</v>
+        <v>2.463956768092666</v>
       </c>
     </row>
     <row r="366">
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="G366">
-        <v>0.00924617356803667</v>
+        <v>0.01128431927216694</v>
       </c>
       <c r="H366">
-        <v>0.924617356803667</v>
+        <v>1.128431927216694</v>
       </c>
     </row>
     <row r="367">
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="G367">
-        <v>0.005726705260053935</v>
+        <v>0.006907819752440698</v>
       </c>
       <c r="H367">
-        <v>0.5726705260053935</v>
+        <v>0.6907819752440698</v>
       </c>
     </row>
     <row r="368">
@@ -11496,10 +11496,10 @@
         </is>
       </c>
       <c r="G368">
-        <v>0.07520741449204843</v>
+        <v>0.08061129101199442</v>
       </c>
       <c r="H368">
-        <v>7.520741449204843</v>
+        <v>8.061129101199443</v>
       </c>
     </row>
     <row r="369">
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="G369">
-        <v>0.03152414142315379</v>
+        <v>0.03486111709820822</v>
       </c>
       <c r="H369">
-        <v>3.152414142315379</v>
+        <v>3.486111709820822</v>
       </c>
     </row>
     <row r="370">
@@ -11562,10 +11562,10 @@
         </is>
       </c>
       <c r="G370">
-        <v>0.1486211886445423</v>
+        <v>0.1512011814318362</v>
       </c>
       <c r="H370">
-        <v>14.86211886445423</v>
+        <v>15.12011814318362</v>
       </c>
     </row>
     <row r="371">
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="G371">
-        <v>0.07804372572354543</v>
+        <v>0.07968095528267878</v>
       </c>
       <c r="H371">
-        <v>7.804372572354542</v>
+        <v>7.968095528267878</v>
       </c>
     </row>
     <row r="372">
@@ -11623,10 +11623,10 @@
         </is>
       </c>
       <c r="G372">
-        <v>0.06237962804588216</v>
+        <v>0.06553790130718659</v>
       </c>
       <c r="H372">
-        <v>6.237962804588216</v>
+        <v>6.553790130718659</v>
       </c>
     </row>
     <row r="373">
@@ -11651,10 +11651,10 @@
         </is>
       </c>
       <c r="G373">
-        <v>0.03283136720297412</v>
+        <v>0.03468247389771719</v>
       </c>
       <c r="H373">
-        <v>3.283136720297412</v>
+        <v>3.468247389771719</v>
       </c>
     </row>
     <row r="374">
@@ -11674,10 +11674,10 @@
         </is>
       </c>
       <c r="G374">
-        <v>0.4867536026693062</v>
+        <v>0.4923211520331933</v>
       </c>
       <c r="H374">
-        <v>48.67536026693062</v>
+        <v>49.23211520331933</v>
       </c>
     </row>
     <row r="375">
@@ -11702,10 +11702,10 @@
         </is>
       </c>
       <c r="G375">
-        <v>0.4218575270444136</v>
+        <v>0.4284190651614254</v>
       </c>
       <c r="H375">
-        <v>42.18575270444136</v>
+        <v>42.84190651614254</v>
       </c>
     </row>
     <row r="376">
@@ -11730,10 +11730,10 @@
         </is>
       </c>
       <c r="G376">
-        <v>0.3970455996107945</v>
+        <v>0.4085448281559572</v>
       </c>
       <c r="H376">
-        <v>39.70455996107945</v>
+        <v>40.85448281559572</v>
       </c>
     </row>
     <row r="377">
@@ -11758,10 +11758,10 @@
         </is>
       </c>
       <c r="G377">
-        <v>0.4293666149785336</v>
+        <v>0.434384718903252</v>
       </c>
       <c r="H377">
-        <v>42.93666149785336</v>
+        <v>43.4384718903252</v>
       </c>
     </row>
     <row r="378">
@@ -11786,10 +11786,10 @@
         </is>
       </c>
       <c r="G378">
-        <v>0.3255566854055911</v>
+        <v>0.3294973946542892</v>
       </c>
       <c r="H378">
-        <v>32.55566854055911</v>
+        <v>32.94973946542892</v>
       </c>
     </row>
     <row r="379">
@@ -11814,10 +11814,10 @@
         </is>
       </c>
       <c r="G379">
-        <v>0.5028465821710844</v>
+        <v>0.5117459739019778</v>
       </c>
       <c r="H379">
-        <v>50.28465821710844</v>
+        <v>51.17459739019778</v>
       </c>
     </row>
     <row r="380">
@@ -11842,10 +11842,10 @@
         </is>
       </c>
       <c r="G380">
-        <v>0.7036475679940911</v>
+        <v>0.7050168861927343</v>
       </c>
       <c r="H380">
-        <v>70.36475679940911</v>
+        <v>70.50168861927342</v>
       </c>
     </row>
     <row r="381">
@@ -11870,10 +11870,10 @@
         </is>
       </c>
       <c r="G381">
-        <v>0.4300449925706414</v>
+        <v>0.4354515965694277</v>
       </c>
       <c r="H381">
-        <v>43.00449925706414</v>
+        <v>43.54515965694277</v>
       </c>
     </row>
     <row r="382">
@@ -11903,10 +11903,10 @@
         </is>
       </c>
       <c r="G382">
-        <v>0.4593612938766475</v>
+        <v>0.4669737030282159</v>
       </c>
       <c r="H382">
-        <v>45.93612938766475</v>
+        <v>46.69737030282159</v>
       </c>
     </row>
     <row r="383">
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="G383">
-        <v>0.3852085615071972</v>
+        <v>0.3907431804749452</v>
       </c>
       <c r="H383">
-        <v>38.52085615071972</v>
+        <v>39.07431804749451</v>
       </c>
     </row>
     <row r="384">
@@ -11969,10 +11969,10 @@
         </is>
       </c>
       <c r="G384">
-        <v>0.5064153239406116</v>
+        <v>0.5175620057178263</v>
       </c>
       <c r="H384">
-        <v>50.64153239406116</v>
+        <v>51.75620057178263</v>
       </c>
     </row>
     <row r="385">
@@ -12002,10 +12002,10 @@
         </is>
       </c>
       <c r="G385">
-        <v>0.2807736863240806</v>
+        <v>0.2926477104306627</v>
       </c>
       <c r="H385">
-        <v>28.07736863240806</v>
+        <v>29.26477104306627</v>
       </c>
     </row>
     <row r="386">
@@ -12035,10 +12035,10 @@
         </is>
       </c>
       <c r="G386">
-        <v>0.4886929474839843</v>
+        <v>0.4941113827786565</v>
       </c>
       <c r="H386">
-        <v>48.86929474839843</v>
+        <v>49.41113827786565</v>
       </c>
     </row>
     <row r="387">
@@ -12068,10 +12068,10 @@
         </is>
       </c>
       <c r="G387">
-        <v>0.3683873276907207</v>
+        <v>0.3729939461824484</v>
       </c>
       <c r="H387">
-        <v>36.83873276907207</v>
+        <v>37.29939461824484</v>
       </c>
     </row>
     <row r="388">
@@ -12101,10 +12101,10 @@
         </is>
       </c>
       <c r="G388">
-        <v>0.4233590624873606</v>
+        <v>0.4276889915312256</v>
       </c>
       <c r="H388">
-        <v>42.33590624873606</v>
+        <v>42.76889915312256</v>
       </c>
     </row>
     <row r="389">
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="G389">
-        <v>0.2351264874192478</v>
+        <v>0.2387073156079204</v>
       </c>
       <c r="H389">
-        <v>23.51264874192478</v>
+        <v>23.87073156079204</v>
       </c>
     </row>
     <row r="390">
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="G390">
-        <v>0.5767963540513349</v>
+        <v>0.5855760612858415</v>
       </c>
       <c r="H390">
-        <v>57.67963540513349</v>
+        <v>58.55760612858415</v>
       </c>
     </row>
     <row r="391">
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="G391">
-        <v>0.429469668268426</v>
+        <v>0.4384878173499315</v>
       </c>
       <c r="H391">
-        <v>42.9469668268426</v>
+        <v>43.84878173499315</v>
       </c>
     </row>
     <row r="392">
@@ -12233,10 +12233,10 @@
         </is>
       </c>
       <c r="G392">
-        <v>0.7678612748639118</v>
+        <v>0.7692389044880951</v>
       </c>
       <c r="H392">
-        <v>76.78612748639118</v>
+        <v>76.9238904488095</v>
       </c>
     </row>
     <row r="393">
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="G393">
-        <v>0.6425356252135522</v>
+        <v>0.6438970334598375</v>
       </c>
       <c r="H393">
-        <v>64.25356252135522</v>
+        <v>64.38970334598375</v>
       </c>
     </row>
     <row r="394">
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="G394">
-        <v>0.5069752733383867</v>
+        <v>0.5126969709996798</v>
       </c>
       <c r="H394">
-        <v>50.69752733383866</v>
+        <v>51.26969709996798</v>
       </c>
     </row>
     <row r="395">
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="G395">
-        <v>0.3524360723192926</v>
+        <v>0.3575248030608772</v>
       </c>
       <c r="H395">
-        <v>35.24360723192926</v>
+        <v>35.75248030608773</v>
       </c>
     </row>
     <row r="396">
@@ -12360,10 +12360,10 @@
         </is>
       </c>
       <c r="G396">
-        <v>0.5512535959666534</v>
+        <v>0.557239570950589</v>
       </c>
       <c r="H396">
-        <v>55.12535959666533</v>
+        <v>55.72395709505889</v>
       </c>
     </row>
     <row r="397">
@@ -12388,10 +12388,10 @@
         </is>
       </c>
       <c r="G397">
-        <v>0.4231011614687418</v>
+        <v>0.4282557834691492</v>
       </c>
       <c r="H397">
-        <v>42.31011614687418</v>
+        <v>42.82557834691492</v>
       </c>
     </row>
     <row r="398">
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="G398">
-        <v>0.3371361747783413</v>
+        <v>0.3433566278950076</v>
       </c>
       <c r="H398">
-        <v>33.71361747783413</v>
+        <v>34.33566278950076</v>
       </c>
     </row>
     <row r="399">
@@ -12439,10 +12439,10 @@
         </is>
       </c>
       <c r="G399">
-        <v>0.2719774453937699</v>
+        <v>0.278861911862859</v>
       </c>
       <c r="H399">
-        <v>27.19774453937699</v>
+        <v>27.8861911862859</v>
       </c>
     </row>
     <row r="400">
@@ -12467,10 +12467,10 @@
         </is>
       </c>
       <c r="G400">
-        <v>0.2324085134156456</v>
+        <v>0.2485370270194858</v>
       </c>
       <c r="H400">
-        <v>23.24085134156456</v>
+        <v>24.85370270194858</v>
       </c>
     </row>
     <row r="401">
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="G401">
-        <v>0.3044429773490794</v>
+        <v>0.3099102209332963</v>
       </c>
       <c r="H401">
-        <v>30.44429773490794</v>
+        <v>30.99102209332963</v>
       </c>
     </row>
     <row r="402">
@@ -12523,10 +12523,10 @@
         </is>
       </c>
       <c r="G402">
-        <v>0.2117182665669382</v>
+        <v>0.2154190921540964</v>
       </c>
       <c r="H402">
-        <v>21.17182665669382</v>
+        <v>21.54190921540964</v>
       </c>
     </row>
     <row r="403">
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="G403">
-        <v>0.2614406189300573</v>
+        <v>0.2750481468146767</v>
       </c>
       <c r="H403">
-        <v>26.14406189300573</v>
+        <v>27.50481468146767</v>
       </c>
     </row>
     <row r="404">
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="G404">
-        <v>0.5174967160927695</v>
+        <v>0.518319392590284</v>
       </c>
       <c r="H404">
-        <v>51.74967160927694</v>
+        <v>51.8319392590284</v>
       </c>
     </row>
     <row r="405">
@@ -12607,10 +12607,10 @@
         </is>
       </c>
       <c r="G405">
-        <v>0.3579828212245829</v>
+        <v>0.3625155209131835</v>
       </c>
       <c r="H405">
-        <v>35.79828212245829</v>
+        <v>36.25155209131835</v>
       </c>
     </row>
     <row r="406">
@@ -12640,10 +12640,10 @@
         </is>
       </c>
       <c r="G406">
-        <v>0.304398246446184</v>
+        <v>0.312651593402253</v>
       </c>
       <c r="H406">
-        <v>30.4398246446184</v>
+        <v>31.2651593402253</v>
       </c>
     </row>
     <row r="407">
@@ -12673,10 +12673,10 @@
         </is>
       </c>
       <c r="G407">
-        <v>0.2402955925875153</v>
+        <v>0.2458423786572918</v>
       </c>
       <c r="H407">
-        <v>24.02955925875153</v>
+        <v>24.58423786572918</v>
       </c>
     </row>
     <row r="408">
@@ -12706,10 +12706,10 @@
         </is>
       </c>
       <c r="G408">
-        <v>0.3105472942609205</v>
+        <v>0.3316699890880214</v>
       </c>
       <c r="H408">
-        <v>31.05472942609205</v>
+        <v>33.16699890880214</v>
       </c>
     </row>
     <row r="409">
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="G409">
-        <v>0.1493384900938957</v>
+        <v>0.1601576458321355</v>
       </c>
       <c r="H409">
-        <v>14.93384900938957</v>
+        <v>16.01576458321355</v>
       </c>
     </row>
     <row r="410">
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="G410">
-        <v>0.3521762737383036</v>
+        <v>0.3587004213154761</v>
       </c>
       <c r="H410">
-        <v>35.21762737383035</v>
+        <v>35.87004213154761</v>
       </c>
     </row>
     <row r="411">
@@ -12805,10 +12805,10 @@
         </is>
       </c>
       <c r="G411">
-        <v>0.2553797322303052</v>
+        <v>0.2597606242822372</v>
       </c>
       <c r="H411">
-        <v>25.53797322303052</v>
+        <v>25.97606242822372</v>
       </c>
     </row>
     <row r="412">
@@ -12838,10 +12838,10 @@
         </is>
       </c>
       <c r="G412">
-        <v>0.2834836886278324</v>
+        <v>0.2879802068513745</v>
       </c>
       <c r="H412">
-        <v>28.34836886278324</v>
+        <v>28.79802068513746</v>
       </c>
     </row>
     <row r="413">
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="G413">
-        <v>0.1453624016157816</v>
+        <v>0.1483275125425046</v>
       </c>
       <c r="H413">
-        <v>14.53624016157816</v>
+        <v>14.83275125425046</v>
       </c>
     </row>
     <row r="414">
@@ -12904,10 +12904,10 @@
         </is>
       </c>
       <c r="G414">
-        <v>0.3169913041836206</v>
+        <v>0.3332228259063935</v>
       </c>
       <c r="H414">
-        <v>31.69913041836206</v>
+        <v>33.32228259063935</v>
       </c>
     </row>
     <row r="415">
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="G415">
-        <v>0.2063202616193542</v>
+        <v>0.2173241226494622</v>
       </c>
       <c r="H415">
-        <v>20.63202616193542</v>
+        <v>21.73241226494622</v>
       </c>
     </row>
     <row r="416">
@@ -12970,10 +12970,10 @@
         </is>
       </c>
       <c r="G416">
-        <v>0.6033272653573122</v>
+        <v>0.6040355638704691</v>
       </c>
       <c r="H416">
-        <v>60.33272653573122</v>
+        <v>60.4035563870469</v>
       </c>
     </row>
     <row r="417">
@@ -13003,10 +13003,10 @@
         </is>
       </c>
       <c r="G417">
-        <v>0.4358121058878076</v>
+        <v>0.4367436354818985</v>
       </c>
       <c r="H417">
-        <v>43.58121058878076</v>
+        <v>43.67436354818985</v>
       </c>
     </row>
     <row r="418">
@@ -13036,10 +13036,10 @@
         </is>
       </c>
       <c r="G418">
-        <v>0.4242112091998612</v>
+        <v>0.4291325269838704</v>
       </c>
       <c r="H418">
-        <v>42.42112091998612</v>
+        <v>42.91325269838705</v>
       </c>
     </row>
     <row r="419">
@@ -13069,10 +13069,10 @@
         </is>
       </c>
       <c r="G419">
-        <v>0.2911702003755012</v>
+        <v>0.2953108537791562</v>
       </c>
       <c r="H419">
-        <v>29.11702003755012</v>
+        <v>29.53108537791562</v>
       </c>
     </row>
     <row r="420">
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="G420">
-        <v>0.3965478200615193</v>
+        <v>0.4041697665467757</v>
       </c>
       <c r="H420">
-        <v>39.65478200615193</v>
+        <v>40.41697665467757</v>
       </c>
     </row>
     <row r="421">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="G421">
-        <v>0.2785052189488965</v>
+        <v>0.2833425948018827</v>
       </c>
       <c r="H421">
-        <v>27.85052189488965</v>
+        <v>28.33425948018827</v>
       </c>
     </row>
     <row r="422">
@@ -13148,10 +13148,10 @@
         </is>
       </c>
       <c r="G422">
-        <v>0.2588712411075828</v>
+        <v>0.2648091114892482</v>
       </c>
       <c r="H422">
-        <v>25.88712411075828</v>
+        <v>26.48091114892483</v>
       </c>
     </row>
     <row r="423">
@@ -13176,10 +13176,10 @@
         </is>
       </c>
       <c r="G423">
-        <v>0.1967915338280743</v>
+        <v>0.2038175384425567</v>
       </c>
       <c r="H423">
-        <v>19.67915338280743</v>
+        <v>20.38175384425567</v>
       </c>
     </row>
     <row r="424">
@@ -13204,10 +13204,10 @@
         </is>
       </c>
       <c r="G424">
-        <v>0.1332626817450251</v>
+        <v>0.147344007592442</v>
       </c>
       <c r="H424">
-        <v>13.32626817450251</v>
+        <v>14.7344007592442</v>
       </c>
     </row>
     <row r="425">
@@ -13232,10 +13232,10 @@
         </is>
       </c>
       <c r="G425">
-        <v>0.2290200398969735</v>
+        <v>0.2340794457317354</v>
       </c>
       <c r="H425">
-        <v>22.90200398969735</v>
+        <v>23.40794457317354</v>
       </c>
     </row>
     <row r="426">
@@ -13260,10 +13260,10 @@
         </is>
       </c>
       <c r="G426">
-        <v>0.1497267785341401</v>
+        <v>0.1529969393818713</v>
       </c>
       <c r="H426">
-        <v>14.97267785341401</v>
+        <v>15.29969393818713</v>
       </c>
     </row>
     <row r="427">
@@ -13288,10 +13288,10 @@
         </is>
       </c>
       <c r="G427">
-        <v>0.1323919443075197</v>
+        <v>0.1447481709591939</v>
       </c>
       <c r="H427">
-        <v>13.23919443075197</v>
+        <v>14.47481709591939</v>
       </c>
     </row>
     <row r="428">
@@ -13316,10 +13316,10 @@
         </is>
       </c>
       <c r="G428">
-        <v>0.4234605868361386</v>
+        <v>0.4246996406969265</v>
       </c>
       <c r="H428">
-        <v>42.34605868361385</v>
+        <v>42.46996406969265</v>
       </c>
     </row>
     <row r="429">
@@ -13344,10 +13344,10 @@
         </is>
       </c>
       <c r="G429">
-        <v>0.3266355977019424</v>
+        <v>0.3307544695065041</v>
       </c>
       <c r="H429">
-        <v>32.66355977019425</v>
+        <v>33.0754469506504</v>
       </c>
     </row>
     <row r="430">
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="G430">
-        <v>0.2248060413819757</v>
+        <v>0.2332851108390843</v>
       </c>
       <c r="H430">
-        <v>22.48060413819757</v>
+        <v>23.32851108390843</v>
       </c>
     </row>
     <row r="431">
@@ -13410,10 +13410,10 @@
         </is>
       </c>
       <c r="G431">
-        <v>0.1694155444647186</v>
+        <v>0.1750216030887366</v>
       </c>
       <c r="H431">
-        <v>16.94155444647186</v>
+        <v>17.50216030887366</v>
       </c>
     </row>
     <row r="432">
@@ -13443,10 +13443,10 @@
         </is>
       </c>
       <c r="G432">
-        <v>0.1827710310623527</v>
+        <v>0.2028437650408863</v>
       </c>
       <c r="H432">
-        <v>18.27710310623527</v>
+        <v>20.28437650408863</v>
       </c>
     </row>
     <row r="433">
@@ -13476,10 +13476,10 @@
         </is>
       </c>
       <c r="G433">
-        <v>0.08062992131643135</v>
+        <v>0.08834172862519141</v>
       </c>
       <c r="H433">
-        <v>8.062992131643135</v>
+        <v>8.834172862519141</v>
       </c>
     </row>
     <row r="434">
@@ -13509,10 +13509,10 @@
         </is>
       </c>
       <c r="G434">
-        <v>0.2679206197150714</v>
+        <v>0.2742287050724087</v>
       </c>
       <c r="H434">
-        <v>26.79206197150713</v>
+        <v>27.42287050724087</v>
       </c>
     </row>
     <row r="435">
@@ -13542,10 +13542,10 @@
         </is>
       </c>
       <c r="G435">
-        <v>0.1890356091693137</v>
+        <v>0.1928115446777992</v>
       </c>
       <c r="H435">
-        <v>18.90356091693137</v>
+        <v>19.28115446777992</v>
       </c>
     </row>
     <row r="436">
@@ -13575,10 +13575,10 @@
         </is>
       </c>
       <c r="G436">
-        <v>0.2028023750738326</v>
+        <v>0.2070365324556894</v>
       </c>
       <c r="H436">
-        <v>20.28023750738326</v>
+        <v>20.70365324556894</v>
       </c>
     </row>
     <row r="437">
@@ -13608,10 +13608,10 @@
         </is>
       </c>
       <c r="G437">
-        <v>0.1006519314134533</v>
+        <v>0.1030307601684461</v>
       </c>
       <c r="H437">
-        <v>10.06519314134533</v>
+        <v>10.30307601684461</v>
       </c>
     </row>
     <row r="438">
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="G438">
-        <v>0.1653613027221257</v>
+        <v>0.1811890695504882</v>
       </c>
       <c r="H438">
-        <v>16.53613027221256</v>
+        <v>18.11890695504882</v>
       </c>
     </row>
     <row r="439">
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="G439">
-        <v>0.09967798573396386</v>
+        <v>0.1085895647798689</v>
       </c>
       <c r="H439">
-        <v>9.967798573396387</v>
+        <v>10.85895647798689</v>
       </c>
     </row>
     <row r="440">
@@ -13707,10 +13707,10 @@
         </is>
       </c>
       <c r="G440">
-        <v>0.5078740061223319</v>
+        <v>0.5089299090414948</v>
       </c>
       <c r="H440">
-        <v>50.78740061223319</v>
+        <v>50.89299090414949</v>
       </c>
     </row>
     <row r="441">
@@ -13740,10 +13740,10 @@
         </is>
       </c>
       <c r="G441">
-        <v>0.3431246538898328</v>
+        <v>0.3445380118113955</v>
       </c>
       <c r="H441">
-        <v>34.31246538898328</v>
+        <v>34.45380118113955</v>
       </c>
     </row>
     <row r="442">
@@ -13773,10 +13773,10 @@
         </is>
       </c>
       <c r="G442">
-        <v>0.3896753808356678</v>
+        <v>0.3941178110701279</v>
       </c>
       <c r="H442">
-        <v>38.96753808356678</v>
+        <v>39.41178110701279</v>
       </c>
     </row>
     <row r="443">
@@ -13806,10 +13806,10 @@
         </is>
       </c>
       <c r="G443">
-        <v>0.2630397099310656</v>
+        <v>0.2668321690391942</v>
       </c>
       <c r="H443">
-        <v>26.30397099310656</v>
+        <v>26.68321690391942</v>
       </c>
     </row>
     <row r="444">
@@ -13834,10 +13834,10 @@
         </is>
       </c>
       <c r="G444">
-        <v>0.3096382138439125</v>
+        <v>0.3171577488853852</v>
       </c>
       <c r="H444">
-        <v>30.96382138439126</v>
+        <v>31.71577488853852</v>
       </c>
     </row>
     <row r="445">
@@ -13862,10 +13862,10 @@
         </is>
       </c>
       <c r="G445">
-        <v>0.2087713638543764</v>
+        <v>0.2131483531938795</v>
       </c>
       <c r="H445">
-        <v>20.87713638543764</v>
+        <v>21.31483531938795</v>
       </c>
     </row>
     <row r="446">
@@ -13885,10 +13885,10 @@
         </is>
       </c>
       <c r="G446">
-        <v>0.4417343932280844</v>
+        <v>0.4473922054481046</v>
       </c>
       <c r="H446">
-        <v>44.17343932280844</v>
+        <v>44.73922054481046</v>
       </c>
     </row>
     <row r="447">
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="G447">
-        <v>0.3666741796196309</v>
+        <v>0.3728059957790312</v>
       </c>
       <c r="H447">
-        <v>36.66741796196309</v>
+        <v>37.28059957790312</v>
       </c>
     </row>
     <row r="448">
@@ -13941,10 +13941,10 @@
         </is>
       </c>
       <c r="G448">
-        <v>0.3498123345342897</v>
+        <v>0.3629840034919118</v>
       </c>
       <c r="H448">
-        <v>34.98123345342897</v>
+        <v>36.29840034919118</v>
       </c>
     </row>
     <row r="449">
@@ -13969,10 +13969,10 @@
         </is>
       </c>
       <c r="G449">
-        <v>0.4009347715568788</v>
+        <v>0.405957951985268</v>
       </c>
       <c r="H449">
-        <v>40.09347715568788</v>
+        <v>40.59579519852679</v>
       </c>
     </row>
     <row r="450">
@@ -13997,10 +13997,10 @@
         </is>
       </c>
       <c r="G450">
-        <v>0.3084387701037252</v>
+        <v>0.3124494786664635</v>
       </c>
       <c r="H450">
-        <v>30.84387701037252</v>
+        <v>31.24494786664635</v>
       </c>
     </row>
     <row r="451">
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="G451">
-        <v>0.3913297204777425</v>
+        <v>0.4029232097031061</v>
       </c>
       <c r="H451">
-        <v>39.13297204777425</v>
+        <v>40.29232097031061</v>
       </c>
     </row>
     <row r="452">
@@ -14053,10 +14053,10 @@
         </is>
       </c>
       <c r="G452">
-        <v>0.6546520624700295</v>
+        <v>0.6556704010773048</v>
       </c>
       <c r="H452">
-        <v>65.46520624700295</v>
+        <v>65.56704010773048</v>
       </c>
     </row>
     <row r="453">
@@ -14081,10 +14081,10 @@
         </is>
       </c>
       <c r="G453">
-        <v>0.4168494262160002</v>
+        <v>0.4220306318992985</v>
       </c>
       <c r="H453">
-        <v>41.68494262160002</v>
+        <v>42.20306318992985</v>
       </c>
     </row>
     <row r="454">
@@ -14114,10 +14114,10 @@
         </is>
       </c>
       <c r="G454">
-        <v>0.4026636626251893</v>
+        <v>0.4098483064980182</v>
       </c>
       <c r="H454">
-        <v>40.26636626251893</v>
+        <v>40.98483064980182</v>
       </c>
     </row>
     <row r="455">
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="G455">
-        <v>0.3315049837286401</v>
+        <v>0.3366079686573361</v>
       </c>
       <c r="H455">
-        <v>33.15049837286401</v>
+        <v>33.66079686573361</v>
       </c>
     </row>
     <row r="456">
@@ -14180,10 +14180,10 @@
         </is>
       </c>
       <c r="G456">
-        <v>0.4507179512562762</v>
+        <v>0.4652299856660724</v>
       </c>
       <c r="H456">
-        <v>45.07179512562762</v>
+        <v>46.52299856660724</v>
       </c>
     </row>
     <row r="457">
@@ -14213,10 +14213,10 @@
         </is>
       </c>
       <c r="G457">
-        <v>0.2425386882895554</v>
+        <v>0.2542854029777696</v>
       </c>
       <c r="H457">
-        <v>24.25386882895554</v>
+        <v>25.42854029777696</v>
       </c>
     </row>
     <row r="458">
@@ -14246,10 +14246,10 @@
         </is>
       </c>
       <c r="G458">
-        <v>0.4558230202449665</v>
+        <v>0.4613442900632316</v>
       </c>
       <c r="H458">
-        <v>45.58230202449665</v>
+        <v>46.13442900632316</v>
       </c>
     </row>
     <row r="459">
@@ -14279,10 +14279,10 @@
         </is>
       </c>
       <c r="G459">
-        <v>0.3445172223148394</v>
+        <v>0.3490284355489401</v>
       </c>
       <c r="H459">
-        <v>34.45172223148394</v>
+        <v>34.90284355489401</v>
       </c>
     </row>
     <row r="460">
@@ -14312,10 +14312,10 @@
         </is>
       </c>
       <c r="G460">
-        <v>0.4035632417287009</v>
+        <v>0.4080603072742512</v>
       </c>
       <c r="H460">
-        <v>40.3563241728701</v>
+        <v>40.80603072742512</v>
       </c>
     </row>
     <row r="461">
@@ -14345,10 +14345,10 @@
         </is>
       </c>
       <c r="G461">
-        <v>0.2204846215537287</v>
+        <v>0.2240456339070294</v>
       </c>
       <c r="H461">
-        <v>22.04846215537287</v>
+        <v>22.40456339070294</v>
       </c>
     </row>
     <row r="462">
@@ -14378,10 +14378,10 @@
         </is>
       </c>
       <c r="G462">
-        <v>0.4606223408083411</v>
+        <v>0.4732321979902833</v>
       </c>
       <c r="H462">
-        <v>46.06223408083412</v>
+        <v>47.32321979902833</v>
       </c>
     </row>
     <row r="463">
@@ -14411,10 +14411,10 @@
         </is>
       </c>
       <c r="G463">
-        <v>0.3225738811180023</v>
+        <v>0.3331588757645854</v>
       </c>
       <c r="H463">
-        <v>32.25738811180022</v>
+        <v>33.31588757645854</v>
       </c>
     </row>
     <row r="464">
@@ -14444,10 +14444,10 @@
         </is>
       </c>
       <c r="G464">
-        <v>0.7269418251173554</v>
+        <v>0.7279422468048973</v>
       </c>
       <c r="H464">
-        <v>72.69418251173553</v>
+        <v>72.79422468048973</v>
       </c>
     </row>
     <row r="465">
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="G465">
-        <v>0.5858541678479628</v>
+        <v>0.586889557920213</v>
       </c>
       <c r="H465">
-        <v>58.58541678479629</v>
+        <v>58.6889557920213</v>
       </c>
     </row>
     <row r="466">
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="G466">
-        <v>0.4886429937246221</v>
+        <v>0.4941732502116358</v>
       </c>
       <c r="H466">
-        <v>48.86429937246221</v>
+        <v>49.41732502116358</v>
       </c>
     </row>
     <row r="467">
@@ -14543,10 +14543,10 @@
         </is>
       </c>
       <c r="G467">
-        <v>0.3444225326738083</v>
+        <v>0.3492516084062092</v>
       </c>
       <c r="H467">
-        <v>34.44225326738083</v>
+        <v>34.92516084062092</v>
       </c>
     </row>
     <row r="468">
@@ -14571,10 +14571,10 @@
         </is>
       </c>
       <c r="G468">
-        <v>0.5051731231778195</v>
+        <v>0.5115394239205878</v>
       </c>
       <c r="H468">
-        <v>50.51731231778195</v>
+        <v>51.15394239205878</v>
       </c>
     </row>
     <row r="469">
@@ -14599,10 +14599,10 @@
         </is>
       </c>
       <c r="G469">
-        <v>0.3791292700097164</v>
+        <v>0.3840879034898663</v>
       </c>
       <c r="H469">
-        <v>37.91292700097164</v>
+        <v>38.40879034898663</v>
       </c>
     </row>
     <row r="470">
@@ -14622,10 +14622,10 @@
         </is>
       </c>
       <c r="G470">
-        <v>0.3371361747783413</v>
+        <v>0.3433566278950076</v>
       </c>
       <c r="H470">
-        <v>33.71361747783413</v>
+        <v>34.33566278950076</v>
       </c>
     </row>
     <row r="471">
@@ -14650,10 +14650,10 @@
         </is>
       </c>
       <c r="G471">
-        <v>0.2719774453937699</v>
+        <v>0.278861911862859</v>
       </c>
       <c r="H471">
-        <v>27.19774453937699</v>
+        <v>27.8861911862859</v>
       </c>
     </row>
     <row r="472">
@@ -14678,10 +14678,10 @@
         </is>
       </c>
       <c r="G472">
-        <v>0.2324085134156456</v>
+        <v>0.2485370270194858</v>
       </c>
       <c r="H472">
-        <v>23.24085134156456</v>
+        <v>24.85370270194858</v>
       </c>
     </row>
     <row r="473">
@@ -14706,10 +14706,10 @@
         </is>
       </c>
       <c r="G473">
-        <v>0.3044429773490794</v>
+        <v>0.3099102209332963</v>
       </c>
       <c r="H473">
-        <v>30.44429773490794</v>
+        <v>30.99102209332963</v>
       </c>
     </row>
     <row r="474">
@@ -14734,10 +14734,10 @@
         </is>
       </c>
       <c r="G474">
-        <v>0.2117182665669382</v>
+        <v>0.2154190921540964</v>
       </c>
       <c r="H474">
-        <v>21.17182665669382</v>
+        <v>21.54190921540964</v>
       </c>
     </row>
     <row r="475">
@@ -14762,10 +14762,10 @@
         </is>
       </c>
       <c r="G475">
-        <v>0.2614406189300573</v>
+        <v>0.2750481468146767</v>
       </c>
       <c r="H475">
-        <v>26.14406189300573</v>
+        <v>27.50481468146767</v>
       </c>
     </row>
     <row r="476">
@@ -14790,10 +14790,10 @@
         </is>
       </c>
       <c r="G476">
-        <v>0.5174967160927695</v>
+        <v>0.518319392590284</v>
       </c>
       <c r="H476">
-        <v>51.74967160927694</v>
+        <v>51.8319392590284</v>
       </c>
     </row>
     <row r="477">
@@ -14818,10 +14818,10 @@
         </is>
       </c>
       <c r="G477">
-        <v>0.3579828212245829</v>
+        <v>0.3625155209131835</v>
       </c>
       <c r="H477">
-        <v>35.79828212245829</v>
+        <v>36.25155209131835</v>
       </c>
     </row>
     <row r="478">
@@ -14851,10 +14851,10 @@
         </is>
       </c>
       <c r="G478">
-        <v>0.304398246446184</v>
+        <v>0.312651593402253</v>
       </c>
       <c r="H478">
-        <v>30.4398246446184</v>
+        <v>31.2651593402253</v>
       </c>
     </row>
     <row r="479">
@@ -14884,10 +14884,10 @@
         </is>
       </c>
       <c r="G479">
-        <v>0.2402955925875153</v>
+        <v>0.2458423786572918</v>
       </c>
       <c r="H479">
-        <v>24.02955925875153</v>
+        <v>24.58423786572918</v>
       </c>
     </row>
     <row r="480">
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="G480">
-        <v>0.3105472942609205</v>
+        <v>0.3316699890880214</v>
       </c>
       <c r="H480">
-        <v>31.05472942609205</v>
+        <v>33.16699890880214</v>
       </c>
     </row>
     <row r="481">
@@ -14950,10 +14950,10 @@
         </is>
       </c>
       <c r="G481">
-        <v>0.1493384900938957</v>
+        <v>0.1601576458321355</v>
       </c>
       <c r="H481">
-        <v>14.93384900938957</v>
+        <v>16.01576458321355</v>
       </c>
     </row>
     <row r="482">
@@ -14983,10 +14983,10 @@
         </is>
       </c>
       <c r="G482">
-        <v>0.3521762737383036</v>
+        <v>0.3587004213154761</v>
       </c>
       <c r="H482">
-        <v>35.21762737383035</v>
+        <v>35.87004213154761</v>
       </c>
     </row>
     <row r="483">
@@ -15016,10 +15016,10 @@
         </is>
       </c>
       <c r="G483">
-        <v>0.2553797322303052</v>
+        <v>0.2597606242822372</v>
       </c>
       <c r="H483">
-        <v>25.53797322303052</v>
+        <v>25.97606242822372</v>
       </c>
     </row>
     <row r="484">
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="G484">
-        <v>0.2834836886278324</v>
+        <v>0.2879802068513745</v>
       </c>
       <c r="H484">
-        <v>28.34836886278324</v>
+        <v>28.79802068513746</v>
       </c>
     </row>
     <row r="485">
@@ -15082,10 +15082,10 @@
         </is>
       </c>
       <c r="G485">
-        <v>0.1453624016157816</v>
+        <v>0.1483275125425046</v>
       </c>
       <c r="H485">
-        <v>14.53624016157816</v>
+        <v>14.83275125425046</v>
       </c>
     </row>
     <row r="486">
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="G486">
-        <v>0.3169913041836206</v>
+        <v>0.3332228259063935</v>
       </c>
       <c r="H486">
-        <v>31.69913041836206</v>
+        <v>33.32228259063935</v>
       </c>
     </row>
     <row r="487">
@@ -15148,10 +15148,10 @@
         </is>
       </c>
       <c r="G487">
-        <v>0.2063202616193542</v>
+        <v>0.2173241226494622</v>
       </c>
       <c r="H487">
-        <v>20.63202616193542</v>
+        <v>21.73241226494622</v>
       </c>
     </row>
     <row r="488">
@@ -15181,10 +15181,10 @@
         </is>
       </c>
       <c r="G488">
-        <v>0.6033272653573122</v>
+        <v>0.6040355638704691</v>
       </c>
       <c r="H488">
-        <v>60.33272653573122</v>
+        <v>60.4035563870469</v>
       </c>
     </row>
     <row r="489">
@@ -15214,10 +15214,10 @@
         </is>
       </c>
       <c r="G489">
-        <v>0.4358121058878076</v>
+        <v>0.4367436354818985</v>
       </c>
       <c r="H489">
-        <v>43.58121058878076</v>
+        <v>43.67436354818985</v>
       </c>
     </row>
     <row r="490">
@@ -15247,10 +15247,10 @@
         </is>
       </c>
       <c r="G490">
-        <v>0.4242112091998612</v>
+        <v>0.4291325269838704</v>
       </c>
       <c r="H490">
-        <v>42.42112091998612</v>
+        <v>42.91325269838705</v>
       </c>
     </row>
     <row r="491">
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="G491">
-        <v>0.2911702003755012</v>
+        <v>0.2953108537791562</v>
       </c>
       <c r="H491">
-        <v>29.11702003755012</v>
+        <v>29.53108537791562</v>
       </c>
     </row>
     <row r="492">
@@ -15308,10 +15308,10 @@
         </is>
       </c>
       <c r="G492">
-        <v>0.3965478200615193</v>
+        <v>0.4041697665467757</v>
       </c>
       <c r="H492">
-        <v>39.65478200615193</v>
+        <v>40.41697665467757</v>
       </c>
     </row>
     <row r="493">
@@ -15336,10 +15336,10 @@
         </is>
       </c>
       <c r="G493">
-        <v>0.2785052189488965</v>
+        <v>0.2833425948018827</v>
       </c>
       <c r="H493">
-        <v>27.85052189488965</v>
+        <v>28.33425948018827</v>
       </c>
     </row>
   </sheetData>
